--- a/Outputs/9_per_metric_diagnostic.xlsx
+++ b/Outputs/9_per_metric_diagnostic.xlsx
@@ -518,7 +518,7 @@
         <v>30.16129032258064</v>
       </c>
       <c r="P2">
-        <v>48.65591397849462</v>
+        <v>47.5268817204301</v>
       </c>
       <c r="Q2">
         <v>9.13978494623656</v>
@@ -595,7 +595,7 @@
         <v>82.20430107526882</v>
       </c>
       <c r="P3">
-        <v>66.93548387096774</v>
+        <v>65.48387096774194</v>
       </c>
       <c r="Q3">
         <v>51.45161290322581</v>
@@ -646,10 +646,10 @@
         </is>
       </c>
       <c r="H4">
-        <v>0.23</v>
+        <v>0.25</v>
       </c>
       <c r="I4">
-        <v>0.2309129474662947</v>
+        <v>0.2467859633393106</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -660,7 +660,7 @@
         <v>0</v>
       </c>
       <c r="L4">
-        <v>0.3888888888888888</v>
+        <v>0.4523809523809523</v>
       </c>
       <c r="M4">
         <v>0.06666666666666667</v>
@@ -672,7 +672,7 @@
         <v>0.2688172043010753</v>
       </c>
       <c r="P4">
-        <v>1.021505376344086</v>
+        <v>2.903225806451613</v>
       </c>
       <c r="Q4">
         <v>3.225806451612903</v>
@@ -689,7 +689,7 @@
         <v>0.2688172043010753</v>
       </c>
       <c r="U4">
-        <v>0.07999999999999999</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="5">
@@ -749,7 +749,7 @@
         <v>30.16129032258064</v>
       </c>
       <c r="P5">
-        <v>53.87096774193548</v>
+        <v>52.90322580645162</v>
       </c>
       <c r="Q5">
         <v>77.68817204301075</v>
@@ -826,7 +826,7 @@
         <v>82.20430107526882</v>
       </c>
       <c r="P6">
-        <v>45.96774193548387</v>
+        <v>44.56989247311828</v>
       </c>
       <c r="Q6">
         <v>96.93548387096774</v>
@@ -903,7 +903,7 @@
         <v>82.20430107526882</v>
       </c>
       <c r="P7">
-        <v>60.86021505376344</v>
+        <v>59.78494623655914</v>
       </c>
       <c r="Q7">
         <v>92.31182795698925</v>
@@ -980,7 +980,7 @@
         <v>7.365591397849462</v>
       </c>
       <c r="P8">
-        <v>7.903225806451613</v>
+        <v>7.795698924731183</v>
       </c>
       <c r="Q8">
         <v>3.225806451612903</v>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="H9">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="I9">
-        <v>0.3028475598775436</v>
+        <v>0.3139586709886548</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -1045,7 +1045,7 @@
         <v>0.1666666666666667</v>
       </c>
       <c r="L9">
-        <v>0.3888888888888888</v>
+        <v>0.4333333333333333</v>
       </c>
       <c r="M9">
         <v>0.2</v>
@@ -1057,7 +1057,7 @@
         <v>1.827956989247312</v>
       </c>
       <c r="P9">
-        <v>1.021505376344086</v>
+        <v>1.827956989247312</v>
       </c>
       <c r="Q9">
         <v>18.44086021505376</v>
@@ -1067,14 +1067,14 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>ASPT</t>
+          <t>DSFI</t>
         </is>
       </c>
       <c r="T9">
-        <v>1.021505376344086</v>
+        <v>1.827956989247312</v>
       </c>
       <c r="U9">
-        <v>0.06</v>
+        <v>0.04999999999999999</v>
       </c>
     </row>
     <row r="10">
@@ -1111,7 +1111,7 @@
         <v>0.42</v>
       </c>
       <c r="I10">
-        <v>0.4197777956758305</v>
+        <v>0.4235972401202749</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>0.5</v>
       </c>
       <c r="L10">
-        <v>0.5888888888888889</v>
+        <v>0.6041666666666666</v>
       </c>
       <c r="M10">
         <v>0.2</v>
@@ -1134,7 +1134,7 @@
         <v>30.16129032258064</v>
       </c>
       <c r="P10">
-        <v>15.64516129032258</v>
+        <v>17.79569892473118</v>
       </c>
       <c r="Q10">
         <v>18.44086021505376</v>
@@ -1211,7 +1211,7 @@
         <v>60.21505376344086</v>
       </c>
       <c r="P11">
-        <v>72.31182795698925</v>
+        <v>71.12903225806451</v>
       </c>
       <c r="Q11">
         <v>98.60215053763442</v>
@@ -1288,7 +1288,7 @@
         <v>30.16129032258064</v>
       </c>
       <c r="P12">
-        <v>28.38709677419355</v>
+        <v>28.06451612903226</v>
       </c>
       <c r="Q12">
         <v>70.3225806451613</v>
@@ -1365,7 +1365,7 @@
         <v>30.16129032258064</v>
       </c>
       <c r="P13">
-        <v>65.21505376344086</v>
+        <v>63.97849462365591</v>
       </c>
       <c r="Q13">
         <v>40.80645161290322</v>
@@ -1442,7 +1442,7 @@
         <v>60.21505376344086</v>
       </c>
       <c r="P14">
-        <v>97.58064516129032</v>
+        <v>97.31182795698925</v>
       </c>
       <c r="Q14">
         <v>29.35483870967742</v>
@@ -1519,7 +1519,7 @@
         <v>30.16129032258064</v>
       </c>
       <c r="P15">
-        <v>41.34408602150538</v>
+        <v>40.21505376344086</v>
       </c>
       <c r="Q15">
         <v>40.80645161290322</v>
@@ -1573,7 +1573,7 @@
         <v>0.65</v>
       </c>
       <c r="I16">
-        <v>0.6496491683991684</v>
+        <v>0.6500646479813146</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
         <v>0.6666666666666666</v>
       </c>
       <c r="L16">
-        <v>0.7884615384615384</v>
+        <v>0.7901234567901233</v>
       </c>
       <c r="M16">
         <v>0.4666666666666667</v>
@@ -1596,7 +1596,7 @@
         <v>60.21505376344086</v>
       </c>
       <c r="P16">
-        <v>68.70967741935483</v>
+        <v>68.27956989247312</v>
       </c>
       <c r="Q16">
         <v>61.02150537634409</v>
@@ -1673,7 +1673,7 @@
         <v>7.365591397849462</v>
       </c>
       <c r="P17">
-        <v>25.21505376344086</v>
+        <v>24.94623655913978</v>
       </c>
       <c r="Q17">
         <v>29.35483870967742</v>
@@ -1750,7 +1750,7 @@
         <v>30.16129032258064</v>
       </c>
       <c r="P18">
-        <v>22.58064516129032</v>
+        <v>21.82795698924731</v>
       </c>
       <c r="Q18">
         <v>29.35483870967742</v>
@@ -1764,7 +1764,7 @@
         </is>
       </c>
       <c r="T18">
-        <v>22.58064516129032</v>
+        <v>21.82795698924731</v>
       </c>
       <c r="U18">
         <v>0.03000000000000003</v>
@@ -1827,7 +1827,7 @@
         <v>82.20430107526882</v>
       </c>
       <c r="P19">
-        <v>88.65591397849462</v>
+        <v>87.25806451612904</v>
       </c>
       <c r="Q19">
         <v>18.44086021505376</v>
@@ -1904,7 +1904,7 @@
         <v>30.16129032258064</v>
       </c>
       <c r="P20">
-        <v>57.90322580645162</v>
+        <v>56.61290322580645</v>
       </c>
       <c r="Q20">
         <v>77.68817204301075</v>
@@ -1981,7 +1981,7 @@
         <v>30.16129032258064</v>
       </c>
       <c r="P21">
-        <v>12.74193548387097</v>
+        <v>12.41935483870968</v>
       </c>
       <c r="Q21">
         <v>40.80645161290322</v>
@@ -1995,7 +1995,7 @@
         </is>
       </c>
       <c r="T21">
-        <v>12.74193548387097</v>
+        <v>12.41935483870968</v>
       </c>
       <c r="U21">
         <v>0.03000000000000003</v>
@@ -2035,7 +2035,7 @@
         <v>0.72</v>
       </c>
       <c r="I22">
-        <v>0.7222390965732087</v>
+        <v>0.7227519170860293</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -2046,7 +2046,7 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="L22">
-        <v>0.7799999999999999</v>
+        <v>0.7820512820512823</v>
       </c>
       <c r="M22">
         <v>0.6</v>
@@ -2058,7 +2058,7 @@
         <v>82.20430107526882</v>
       </c>
       <c r="P22">
-        <v>66.0752688172043</v>
+        <v>65.48387096774194</v>
       </c>
       <c r="Q22">
         <v>77.68817204301075</v>
@@ -2135,7 +2135,7 @@
         <v>82.20430107526882</v>
       </c>
       <c r="P23">
-        <v>75.26881720430107</v>
+        <v>74.3010752688172</v>
       </c>
       <c r="Q23">
         <v>77.68817204301075</v>
@@ -2212,7 +2212,7 @@
         <v>30.16129032258064</v>
       </c>
       <c r="P24">
-        <v>42.79569892473118</v>
+        <v>41.55913978494624</v>
       </c>
       <c r="Q24">
         <v>51.45161290322581</v>
@@ -2289,7 +2289,7 @@
         <v>1.827956989247312</v>
       </c>
       <c r="P25">
-        <v>1.344086021505376</v>
+        <v>1.021505376344086</v>
       </c>
       <c r="Q25">
         <v>18.44086021505376</v>
@@ -2303,7 +2303,7 @@
         </is>
       </c>
       <c r="T25">
-        <v>1.344086021505376</v>
+        <v>1.021505376344086</v>
       </c>
       <c r="U25">
         <v>0.01999999999999996</v>
@@ -2366,7 +2366,7 @@
         <v>96.34408602150538</v>
       </c>
       <c r="P26">
-        <v>71.93548387096774</v>
+        <v>70.75268817204301</v>
       </c>
       <c r="Q26">
         <v>97.84946236559139</v>
@@ -2520,7 +2520,7 @@
         <v>7.365591397849462</v>
       </c>
       <c r="P28">
-        <v>12.04301075268817</v>
+        <v>11.66666666666667</v>
       </c>
       <c r="Q28">
         <v>0.4838709677419355</v>
@@ -2597,7 +2597,7 @@
         <v>1.827956989247312</v>
       </c>
       <c r="P29">
-        <v>2.311827956989247</v>
+        <v>1.827956989247312</v>
       </c>
       <c r="Q29">
         <v>18.44086021505376</v>
@@ -2674,7 +2674,7 @@
         <v>7.365591397849462</v>
       </c>
       <c r="P30">
-        <v>2.150537634408602</v>
+        <v>1.612903225806452</v>
       </c>
       <c r="Q30">
         <v>9.13978494623656</v>
@@ -2688,7 +2688,7 @@
         </is>
       </c>
       <c r="T30">
-        <v>2.150537634408602</v>
+        <v>1.612903225806452</v>
       </c>
       <c r="U30">
         <v>0.02000000000000002</v>
@@ -2751,7 +2751,7 @@
         <v>60.21505376344086</v>
       </c>
       <c r="P31">
-        <v>81.0752688172043</v>
+        <v>79.6236559139785</v>
       </c>
       <c r="Q31">
         <v>51.45161290322581</v>
@@ -2828,7 +2828,7 @@
         <v>30.16129032258064</v>
       </c>
       <c r="P32">
-        <v>17.1505376344086</v>
+        <v>16.93548387096774</v>
       </c>
       <c r="Q32">
         <v>18.44086021505376</v>
@@ -2842,7 +2842,7 @@
         </is>
       </c>
       <c r="T32">
-        <v>17.1505376344086</v>
+        <v>16.93548387096774</v>
       </c>
       <c r="U32">
         <v>0.02000000000000002</v>
@@ -2905,7 +2905,7 @@
         <v>82.20430107526882</v>
       </c>
       <c r="P33">
-        <v>89.51612903225806</v>
+        <v>88.38709677419355</v>
       </c>
       <c r="Q33">
         <v>61.02150537634409</v>
@@ -2982,7 +2982,7 @@
         <v>60.21505376344086</v>
       </c>
       <c r="P34">
-        <v>30</v>
+        <v>29.46236559139785</v>
       </c>
       <c r="Q34">
         <v>29.35483870967742</v>
@@ -3059,7 +3059,7 @@
         <v>82.20430107526882</v>
       </c>
       <c r="P35">
-        <v>44.13978494623656</v>
+        <v>42.74193548387097</v>
       </c>
       <c r="Q35">
         <v>92.31182795698925</v>
@@ -3136,7 +3136,7 @@
         <v>82.20430107526882</v>
       </c>
       <c r="P36">
-        <v>51.61290322580645</v>
+        <v>50.53763440860215</v>
       </c>
       <c r="Q36">
         <v>92.31182795698925</v>
@@ -3150,7 +3150,7 @@
         </is>
       </c>
       <c r="T36">
-        <v>51.61290322580645</v>
+        <v>50.53763440860215</v>
       </c>
       <c r="U36">
         <v>0.01000000000000001</v>
@@ -3213,7 +3213,7 @@
         <v>30.16129032258064</v>
       </c>
       <c r="P37">
-        <v>13.60215053763441</v>
+        <v>13.33333333333333</v>
       </c>
       <c r="Q37">
         <v>51.45161290322581</v>
@@ -3227,7 +3227,7 @@
         </is>
       </c>
       <c r="T37">
-        <v>13.60215053763441</v>
+        <v>13.33333333333333</v>
       </c>
       <c r="U37">
         <v>0.01000000000000001</v>
@@ -3290,7 +3290,7 @@
         <v>7.365591397849462</v>
       </c>
       <c r="P38">
-        <v>1.774193548387097</v>
+        <v>1.290322580645161</v>
       </c>
       <c r="Q38">
         <v>9.13978494623656</v>
@@ -3304,7 +3304,7 @@
         </is>
       </c>
       <c r="T38">
-        <v>1.774193548387097</v>
+        <v>1.290322580645161</v>
       </c>
       <c r="U38">
         <v>0.01000000000000001</v>
@@ -3344,7 +3344,7 @@
         <v>0.41</v>
       </c>
       <c r="I39">
-        <v>0.4086387725310993</v>
+        <v>0.4110129415719349</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
@@ -3355,7 +3355,7 @@
         <v>0.3333333333333333</v>
       </c>
       <c r="L39">
-        <v>0.576923076923077</v>
+        <v>0.5864197530864197</v>
       </c>
       <c r="M39">
         <v>0.1333333333333333</v>
@@ -3367,7 +3367,7 @@
         <v>7.365591397849462</v>
       </c>
       <c r="P39">
-        <v>13.60215053763441</v>
+        <v>14.73118279569892</v>
       </c>
       <c r="Q39">
         <v>9.13978494623656</v>
@@ -3421,7 +3421,7 @@
         <v>0.52</v>
       </c>
       <c r="I40">
-        <v>0.5189073883917656</v>
+        <v>0.5208137064745544</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
@@ -3432,7 +3432,7 @@
         <v>0.5</v>
       </c>
       <c r="L40">
-        <v>0.6960784313725491</v>
+        <v>0.7037037037037037</v>
       </c>
       <c r="M40">
         <v>0.2</v>
@@ -3444,7 +3444,7 @@
         <v>30.16129032258064</v>
       </c>
       <c r="P40">
-        <v>38.54838709677419</v>
+        <v>39.46236559139785</v>
       </c>
       <c r="Q40">
         <v>18.44086021505376</v>
@@ -3521,7 +3521,7 @@
         <v>30.16129032258064</v>
       </c>
       <c r="P41">
-        <v>57.04301075268818</v>
+        <v>55.96774193548387</v>
       </c>
       <c r="Q41">
         <v>9.13978494623656</v>
@@ -3575,7 +3575,7 @@
         <v>0.77</v>
       </c>
       <c r="I42">
-        <v>0.7730004174812642</v>
+        <v>0.7733717781467425</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
@@ -3586,7 +3586,7 @@
         <v>0.6666666666666666</v>
       </c>
       <c r="L42">
-        <v>0.7828282828282829</v>
+        <v>0.7843137254901961</v>
       </c>
       <c r="M42">
         <v>0.6</v>
@@ -3598,7 +3598,7 @@
         <v>60.21505376344086</v>
       </c>
       <c r="P42">
-        <v>67.20430107526882</v>
+        <v>66.18279569892474</v>
       </c>
       <c r="Q42">
         <v>77.68817204301075</v>
@@ -3675,7 +3675,7 @@
         <v>7.365591397849462</v>
       </c>
       <c r="P43">
-        <v>19.78494623655914</v>
+        <v>19.24731182795699</v>
       </c>
       <c r="Q43">
         <v>18.44086021505376</v>
@@ -3752,7 +3752,7 @@
         <v>60.21505376344086</v>
       </c>
       <c r="P44">
-        <v>31.72043010752688</v>
+        <v>31.12903225806452</v>
       </c>
       <c r="Q44">
         <v>29.35483870967742</v>
@@ -3829,7 +3829,7 @@
         <v>30.16129032258064</v>
       </c>
       <c r="P45">
-        <v>41.0752688172043</v>
+        <v>39.89247311827957</v>
       </c>
       <c r="Q45">
         <v>29.35483870967742</v>
@@ -3883,7 +3883,7 @@
         <v>0.74</v>
       </c>
       <c r="I46">
-        <v>0.7370394736842105</v>
+        <v>0.7419112685560054</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
@@ -3894,7 +3894,7 @@
         <v>0.6666666666666666</v>
       </c>
       <c r="L46">
-        <v>0.8266666666666667</v>
+        <v>0.8461538461538461</v>
       </c>
       <c r="M46">
         <v>0.7333333333333333</v>
@@ -3906,7 +3906,7 @@
         <v>60.21505376344086</v>
       </c>
       <c r="P46">
-        <v>79.6236559139785</v>
+        <v>82.47311827956989</v>
       </c>
       <c r="Q46">
         <v>87.84946236559139</v>
@@ -3957,10 +3957,10 @@
         </is>
       </c>
       <c r="H47">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="I47">
-        <v>0.4938128140703517</v>
+        <v>0.4994946322521699</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
@@ -3971,7 +3971,7 @@
         <v>0.5</v>
       </c>
       <c r="L47">
-        <v>0.6666666666666666</v>
+        <v>0.6893939393939394</v>
       </c>
       <c r="M47">
         <v>0.1333333333333333</v>
@@ -3983,7 +3983,7 @@
         <v>30.16129032258064</v>
       </c>
       <c r="P47">
-        <v>31.72043010752688</v>
+        <v>35.64516129032258</v>
       </c>
       <c r="Q47">
         <v>9.13978494623656</v>
@@ -4000,7 +4000,7 @@
         <v>9.13978494623656</v>
       </c>
       <c r="U47">
-        <v>-0.01000000000000001</v>
+        <v>-0.02000000000000002</v>
       </c>
     </row>
   </sheetData>

--- a/Outputs/9_per_metric_diagnostic.xlsx
+++ b/Outputs/9_per_metric_diagnostic.xlsx
@@ -1,20 +1,390 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30203"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_F21D1DDD8F79A8D366075C52F37BD272AAC41930" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191028"/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="116">
+  <si>
+    <t>site_code</t>
+  </si>
+  <si>
+    <t>site_id</t>
+  </si>
+  <si>
+    <t>year</t>
+  </si>
+  <si>
+    <t>waterbody_name</t>
+  </si>
+  <si>
+    <t>river_type</t>
+  </si>
+  <si>
+    <t>EQR</t>
+  </si>
+  <si>
+    <t>EQC</t>
+  </si>
+  <si>
+    <t>LRMI</t>
+  </si>
+  <si>
+    <t>LRMI_raw</t>
+  </si>
+  <si>
+    <t>LRMI_class</t>
+  </si>
+  <si>
+    <t>DSFI_EQR</t>
+  </si>
+  <si>
+    <t>ASPT_EQR</t>
+  </si>
+  <si>
+    <t>DEP_EQR</t>
+  </si>
+  <si>
+    <t>EHP_minus_CrHi_EQR</t>
+  </si>
+  <si>
+    <t>DSFI_pct</t>
+  </si>
+  <si>
+    <t>ASPT_pct</t>
+  </si>
+  <si>
+    <t>DEP_pct</t>
+  </si>
+  <si>
+    <t>EHP_minus_CrHi_pct</t>
+  </si>
+  <si>
+    <t>lowest_metric</t>
+  </si>
+  <si>
+    <t>lowest_pct</t>
+  </si>
+  <si>
+    <t>residual</t>
+  </si>
+  <si>
+    <t>LTR1492_2022</t>
+  </si>
+  <si>
+    <t>LTR1492</t>
+  </si>
+  <si>
+    <t>Mūša</t>
+  </si>
+  <si>
+    <t>Moderate</t>
+  </si>
+  <si>
+    <t>Poor</t>
+  </si>
+  <si>
+    <t>EHP-CrHi</t>
+  </si>
+  <si>
+    <t>LTR163_2019</t>
+  </si>
+  <si>
+    <t>LTR163</t>
+  </si>
+  <si>
+    <t>Geluža</t>
+  </si>
+  <si>
+    <t>Good</t>
+  </si>
+  <si>
+    <t>LTR127_2015</t>
+  </si>
+  <si>
+    <t>LTR127</t>
+  </si>
+  <si>
+    <t>Skirvytė</t>
+  </si>
+  <si>
+    <t>Bad</t>
+  </si>
+  <si>
+    <t>DSFI</t>
+  </si>
+  <si>
+    <t>LTR386_2019</t>
+  </si>
+  <si>
+    <t>LTR386</t>
+  </si>
+  <si>
+    <t>Viešinta</t>
+  </si>
+  <si>
+    <t>LTR1466_2019</t>
+  </si>
+  <si>
+    <t>LTR1466</t>
+  </si>
+  <si>
+    <t>Įpiltis</t>
+  </si>
+  <si>
+    <t>High</t>
+  </si>
+  <si>
+    <t>LTR163_2022</t>
+  </si>
+  <si>
+    <t>LTR450_2015</t>
+  </si>
+  <si>
+    <t>LTR450</t>
+  </si>
+  <si>
+    <t>Ringuva</t>
+  </si>
+  <si>
+    <t>LTR127_2017</t>
+  </si>
+  <si>
+    <t>LTR127_2020</t>
+  </si>
+  <si>
+    <t>LTR625_2022</t>
+  </si>
+  <si>
+    <t>LTR625</t>
+  </si>
+  <si>
+    <t>Luoba</t>
+  </si>
+  <si>
+    <t>LTR1466_2016</t>
+  </si>
+  <si>
+    <t>LTR1687_2016</t>
+  </si>
+  <si>
+    <t>LTR1687</t>
+  </si>
+  <si>
+    <t>Šalpė</t>
+  </si>
+  <si>
+    <t>LTR1687_2022</t>
+  </si>
+  <si>
+    <t>DEP</t>
+  </si>
+  <si>
+    <t>LTR297_2021</t>
+  </si>
+  <si>
+    <t>LTR297</t>
+  </si>
+  <si>
+    <t>Lokysta</t>
+  </si>
+  <si>
+    <t>LTR1447_2015</t>
+  </si>
+  <si>
+    <t>LTR1447</t>
+  </si>
+  <si>
+    <t>Merkys</t>
+  </si>
+  <si>
+    <t>LTR86_2015</t>
+  </si>
+  <si>
+    <t>LTR86</t>
+  </si>
+  <si>
+    <t>LTR1461_2022</t>
+  </si>
+  <si>
+    <t>LTR1461</t>
+  </si>
+  <si>
+    <t>Nemunėlis</t>
+  </si>
+  <si>
+    <t>ASPT</t>
+  </si>
+  <si>
+    <t>LTR1461_2016</t>
+  </si>
+  <si>
+    <t>LTR1461_2019</t>
+  </si>
+  <si>
+    <t>LTR1466_2022</t>
+  </si>
+  <si>
+    <t>LTR386_2016</t>
+  </si>
+  <si>
+    <t>LTR386_2022</t>
+  </si>
+  <si>
+    <t>LTR1488_2015</t>
+  </si>
+  <si>
+    <t>LTR1488</t>
+  </si>
+  <si>
+    <t>Neris</t>
+  </si>
+  <si>
+    <t>LTR1063_2021</t>
+  </si>
+  <si>
+    <t>LTR1063</t>
+  </si>
+  <si>
+    <t>PentaII</t>
+  </si>
+  <si>
+    <t>LTR163_2016</t>
+  </si>
+  <si>
+    <t>LTR308_2018</t>
+  </si>
+  <si>
+    <t>LTR308</t>
+  </si>
+  <si>
+    <t>Eketė</t>
+  </si>
+  <si>
+    <t>LTR450_2020</t>
+  </si>
+  <si>
+    <t>LTR297_2018</t>
+  </si>
+  <si>
+    <t>LTR706_2015</t>
+  </si>
+  <si>
+    <t>LTR706</t>
+  </si>
+  <si>
+    <t>Liaudė</t>
+  </si>
+  <si>
+    <t>LTR1488_2016</t>
+  </si>
+  <si>
+    <t>LTR1492_2019</t>
+  </si>
+  <si>
+    <t>LTR1502_2015</t>
+  </si>
+  <si>
+    <t>LTR1502</t>
+  </si>
+  <si>
+    <t>Lėvuo</t>
+  </si>
+  <si>
+    <t>LTR337_2019</t>
+  </si>
+  <si>
+    <t>LTR337</t>
+  </si>
+  <si>
+    <t>Svyla</t>
+  </si>
+  <si>
+    <t>LTR337_2022</t>
+  </si>
+  <si>
+    <t>LTR337_2016</t>
+  </si>
+  <si>
+    <t>LTR1687_2017</t>
+  </si>
+  <si>
+    <t>LTR297_2015</t>
+  </si>
+  <si>
+    <t>LTR1488_2022</t>
+  </si>
+  <si>
+    <t>LTR1488_2019</t>
+  </si>
+  <si>
+    <t>LTR1501_2016</t>
+  </si>
+  <si>
+    <t>LTR1501</t>
+  </si>
+  <si>
+    <t>LTR1447_2022</t>
+  </si>
+  <si>
+    <t>LTR1492_2016</t>
+  </si>
+  <si>
+    <t>LTR1502_2019</t>
+  </si>
+  <si>
+    <t>LTR351_2019</t>
+  </si>
+  <si>
+    <t>LTR351</t>
+  </si>
+  <si>
+    <t>Šventoji</t>
+  </si>
+  <si>
+    <t>LTR411_2022</t>
+  </si>
+  <si>
+    <t>LTR411</t>
+  </si>
+  <si>
+    <t>Šešupė</t>
+  </si>
+  <si>
+    <t>LTR86_2016</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="2">
     <font>
       <sz val="11"/>
@@ -59,17 +429,25 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Įprastas" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -107,7 +485,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -141,6 +519,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -175,9 +554,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -350,135 +730,87 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:U47"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>site_code</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>site_id</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>year</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>waterbody_name</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>river_type</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>EQR</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>EQC</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>LRMI</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>LRMI_raw</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>LRMI_class</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>DSFI_EQR</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>ASPT_EQR</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>DEP_EQR</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>EHP_minus_CrHi_EQR</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>DSFI_pct</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>ASPT_pct</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>DEP_pct</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>EHP_minus_CrHi_pct</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>lowest_metric</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>lowest_pct</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>residual</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>LTR1492_2022</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>LTR1492</t>
-        </is>
+    <row r="1" spans="1:21" s="1" customFormat="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21">
+      <c r="A2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B2" t="s">
+        <v>22</v>
       </c>
       <c r="C2">
         <v>2022</v>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Mūša</t>
-        </is>
+      <c r="D2" t="s">
+        <v>23</v>
       </c>
       <c r="E2">
         <v>5</v>
@@ -486,50 +818,44 @@
       <c r="F2">
         <v>0.5</v>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
+      <c r="G2" t="s">
+        <v>24</v>
       </c>
       <c r="H2">
         <v>0.39</v>
       </c>
       <c r="I2">
-        <v>0.3932091346153846</v>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Poor</t>
-        </is>
+        <v>0.39320913461538459</v>
+      </c>
+      <c r="J2" t="s">
+        <v>25</v>
       </c>
       <c r="K2">
         <v>0.5</v>
       </c>
       <c r="L2">
-        <v>0.7291666666666666</v>
+        <v>0.72916666666666663</v>
       </c>
       <c r="M2">
         <v>0.1333333333333333</v>
       </c>
       <c r="N2">
-        <v>0.2103365384615385</v>
+        <v>0.21033653846153849</v>
       </c>
       <c r="O2">
-        <v>30.16129032258064</v>
+        <v>30.161290322580641</v>
       </c>
       <c r="P2">
-        <v>47.5268817204301</v>
+        <v>47.526881720430097</v>
       </c>
       <c r="Q2">
-        <v>9.13978494623656</v>
+        <v>9.1397849462365599</v>
       </c>
       <c r="R2">
         <v>0.967741935483871</v>
       </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>EHP-CrHi</t>
-        </is>
+      <c r="S2" t="s">
+        <v>26</v>
       </c>
       <c r="T2">
         <v>0.967741935483871</v>
@@ -538,24 +864,18 @@
         <v>0.11</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>LTR163_2019</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>LTR163</t>
-        </is>
+    <row r="3" spans="1:21">
+      <c r="A3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B3" t="s">
+        <v>28</v>
       </c>
       <c r="C3">
         <v>2019</v>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Geluža</t>
-        </is>
+      <c r="D3" t="s">
+        <v>29</v>
       </c>
       <c r="E3">
         <v>1</v>
@@ -563,76 +883,64 @@
       <c r="F3">
         <v>0.68</v>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Good</t>
-        </is>
+      <c r="G3" t="s">
+        <v>30</v>
       </c>
       <c r="H3">
         <v>0.6</v>
       </c>
       <c r="I3">
-        <v>0.6010903521583901</v>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Good</t>
-        </is>
+        <v>0.60109035215839013</v>
+      </c>
+      <c r="J3" t="s">
+        <v>30</v>
       </c>
       <c r="K3">
-        <v>0.8333333333333334</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="L3">
-        <v>0.7820512820512823</v>
+        <v>0.78205128205128227</v>
       </c>
       <c r="M3">
         <v>0.4</v>
       </c>
       <c r="N3">
-        <v>0.3889767932489451</v>
+        <v>0.38897679324894507</v>
       </c>
       <c r="O3">
-        <v>82.20430107526882</v>
+        <v>82.204301075268816</v>
       </c>
       <c r="P3">
-        <v>65.48387096774194</v>
+        <v>65.483870967741936</v>
       </c>
       <c r="Q3">
-        <v>51.45161290322581</v>
+        <v>51.451612903225808</v>
       </c>
       <c r="R3">
         <v>3.225806451612903</v>
       </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>EHP-CrHi</t>
-        </is>
+      <c r="S3" t="s">
+        <v>26</v>
       </c>
       <c r="T3">
         <v>3.225806451612903</v>
       </c>
       <c r="U3">
-        <v>0.08000000000000007</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>LTR127_2015</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>LTR127</t>
-        </is>
+        <v>8.0000000000000071E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21">
+      <c r="A4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B4" t="s">
+        <v>32</v>
       </c>
       <c r="C4">
         <v>2015</v>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Skirvytė</t>
-        </is>
+      <c r="D4" t="s">
+        <v>33</v>
       </c>
       <c r="E4">
         <v>4</v>
@@ -640,10 +948,8 @@
       <c r="F4">
         <v>0.31</v>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Poor</t>
-        </is>
+      <c r="G4" t="s">
+        <v>25</v>
       </c>
       <c r="H4">
         <v>0.25</v>
@@ -651,25 +957,23 @@
       <c r="I4">
         <v>0.2467859633393106</v>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Bad</t>
-        </is>
+      <c r="J4" t="s">
+        <v>34</v>
       </c>
       <c r="K4">
         <v>0</v>
       </c>
       <c r="L4">
-        <v>0.4523809523809523</v>
+        <v>0.45238095238095227</v>
       </c>
       <c r="M4">
-        <v>0.06666666666666667</v>
+        <v>6.6666666666666666E-2</v>
       </c>
       <c r="N4">
-        <v>0.4680962343096234</v>
+        <v>0.46809623430962338</v>
       </c>
       <c r="O4">
-        <v>0.2688172043010753</v>
+        <v>0.26881720430107531</v>
       </c>
       <c r="P4">
         <v>2.903225806451613</v>
@@ -680,36 +984,28 @@
       <c r="R4">
         <v>5.913978494623656</v>
       </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>DSFI</t>
-        </is>
+      <c r="S4" t="s">
+        <v>35</v>
       </c>
       <c r="T4">
-        <v>0.2688172043010753</v>
+        <v>0.26881720430107531</v>
       </c>
       <c r="U4">
         <v>0.06</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>LTR386_2019</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>LTR386</t>
-        </is>
+    <row r="5" spans="1:21">
+      <c r="A5" t="s">
+        <v>36</v>
+      </c>
+      <c r="B5" t="s">
+        <v>37</v>
       </c>
       <c r="C5">
         <v>2019</v>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Viešinta</t>
-        </is>
+      <c r="D5" t="s">
+        <v>38</v>
       </c>
       <c r="E5">
         <v>1</v>
@@ -717,76 +1013,64 @@
       <c r="F5">
         <v>0.66</v>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Good</t>
-        </is>
+      <c r="G5" t="s">
+        <v>30</v>
       </c>
       <c r="H5">
         <v>0.59</v>
       </c>
       <c r="I5">
-        <v>0.5914584315574415</v>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
+        <v>0.59145843155744149</v>
+      </c>
+      <c r="J5" t="s">
+        <v>24</v>
       </c>
       <c r="K5">
         <v>0.5</v>
       </c>
       <c r="L5">
-        <v>0.746031746031746</v>
+        <v>0.74603174603174605</v>
       </c>
       <c r="M5">
         <v>0.6</v>
       </c>
       <c r="N5">
-        <v>0.5198019801980198</v>
+        <v>0.51980198019801982</v>
       </c>
       <c r="O5">
-        <v>30.16129032258064</v>
+        <v>30.161290322580641</v>
       </c>
       <c r="P5">
-        <v>52.90322580645162</v>
+        <v>52.903225806451623</v>
       </c>
       <c r="Q5">
-        <v>77.68817204301075</v>
+        <v>77.688172043010752</v>
       </c>
       <c r="R5">
         <v>9.89247311827957</v>
       </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>EHP-CrHi</t>
-        </is>
+      <c r="S5" t="s">
+        <v>26</v>
       </c>
       <c r="T5">
         <v>9.89247311827957</v>
       </c>
       <c r="U5">
-        <v>0.07000000000000006</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>LTR1466_2019</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>LTR1466</t>
-        </is>
+        <v>7.0000000000000062E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21">
+      <c r="A6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B6" t="s">
+        <v>40</v>
       </c>
       <c r="C6">
         <v>2019</v>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Įpiltis</t>
-        </is>
+      <c r="D6" t="s">
+        <v>41</v>
       </c>
       <c r="E6">
         <v>3</v>
@@ -794,76 +1078,64 @@
       <c r="F6">
         <v>0.83</v>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
+      <c r="G6" t="s">
+        <v>42</v>
       </c>
       <c r="H6">
         <v>0.77</v>
       </c>
       <c r="I6">
-        <v>0.772332659478886</v>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Good</t>
-        </is>
+        <v>0.77233265947888596</v>
+      </c>
+      <c r="J6" t="s">
+        <v>30</v>
       </c>
       <c r="K6">
-        <v>0.8333333333333334</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="L6">
-        <v>0.7202380952380952</v>
+        <v>0.72023809523809523</v>
       </c>
       <c r="M6">
-        <v>0.9333333333333333</v>
+        <v>0.93333333333333335</v>
       </c>
       <c r="N6">
-        <v>0.6024258760107817</v>
+        <v>0.60242587601078168</v>
       </c>
       <c r="O6">
-        <v>82.20430107526882</v>
+        <v>82.204301075268816</v>
       </c>
       <c r="P6">
         <v>44.56989247311828</v>
       </c>
       <c r="Q6">
-        <v>96.93548387096774</v>
+        <v>96.935483870967744</v>
       </c>
       <c r="R6">
-        <v>23.33333333333333</v>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>EHP-CrHi</t>
-        </is>
+        <v>23.333333333333329</v>
+      </c>
+      <c r="S6" t="s">
+        <v>26</v>
       </c>
       <c r="T6">
-        <v>23.33333333333333</v>
+        <v>23.333333333333329</v>
       </c>
       <c r="U6">
-        <v>0.05999999999999994</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>LTR163_2022</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>LTR163</t>
-        </is>
+        <v>5.9999999999999942E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21">
+      <c r="A7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B7" t="s">
+        <v>28</v>
       </c>
       <c r="C7">
         <v>2022</v>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Geluža</t>
-        </is>
+      <c r="D7" t="s">
+        <v>29</v>
       </c>
       <c r="E7">
         <v>1</v>
@@ -871,76 +1143,64 @@
       <c r="F7">
         <v>0.79</v>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Good</t>
-        </is>
+      <c r="G7" t="s">
+        <v>30</v>
       </c>
       <c r="H7">
         <v>0.73</v>
       </c>
       <c r="I7">
-        <v>0.7273446599114838</v>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>Good</t>
-        </is>
+        <v>0.72734465991148378</v>
+      </c>
+      <c r="J7" t="s">
+        <v>30</v>
       </c>
       <c r="K7">
-        <v>0.8333333333333334</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="L7">
-        <v>0.7654320987654321</v>
+        <v>0.76543209876543206</v>
       </c>
       <c r="M7">
         <v>0.8</v>
       </c>
       <c r="N7">
-        <v>0.5106132075471698</v>
+        <v>0.51061320754716977</v>
       </c>
       <c r="O7">
-        <v>82.20430107526882</v>
+        <v>82.204301075268816</v>
       </c>
       <c r="P7">
-        <v>59.78494623655914</v>
+        <v>59.784946236559144</v>
       </c>
       <c r="Q7">
-        <v>92.31182795698925</v>
+        <v>92.311827956989248</v>
       </c>
       <c r="R7">
-        <v>9.03225806451613</v>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>EHP-CrHi</t>
-        </is>
+        <v>9.0322580645161299</v>
+      </c>
+      <c r="S7" t="s">
+        <v>26</v>
       </c>
       <c r="T7">
-        <v>9.03225806451613</v>
+        <v>9.0322580645161299</v>
       </c>
       <c r="U7">
-        <v>0.06000000000000005</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>LTR450_2015</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>LTR450</t>
-        </is>
+        <v>6.0000000000000053E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21">
+      <c r="A8" t="s">
+        <v>44</v>
+      </c>
+      <c r="B8" t="s">
+        <v>45</v>
       </c>
       <c r="C8">
         <v>2015</v>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Ringuva</t>
-        </is>
+      <c r="D8" t="s">
+        <v>46</v>
       </c>
       <c r="E8">
         <v>2</v>
@@ -948,33 +1208,29 @@
       <c r="F8">
         <v>0.38</v>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Poor</t>
-        </is>
+      <c r="G8" t="s">
+        <v>25</v>
       </c>
       <c r="H8">
         <v>0.32</v>
       </c>
       <c r="I8">
-        <v>0.3176745329400197</v>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>Poor</t>
-        </is>
+        <v>0.31767453294001968</v>
+      </c>
+      <c r="J8" t="s">
+        <v>25</v>
       </c>
       <c r="K8">
-        <v>0.3333333333333333</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="L8">
-        <v>0.5277777777777778</v>
+        <v>0.52777777777777779</v>
       </c>
       <c r="M8">
-        <v>0.06666666666666667</v>
+        <v>6.6666666666666666E-2</v>
       </c>
       <c r="N8">
-        <v>0.3429203539823009</v>
+        <v>0.34292035398230092</v>
       </c>
       <c r="O8">
         <v>7.365591397849462</v>
@@ -988,10 +1244,8 @@
       <c r="R8">
         <v>1.935483870967742</v>
       </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>EHP-CrHi</t>
-        </is>
+      <c r="S8" t="s">
+        <v>26</v>
       </c>
       <c r="T8">
         <v>1.935483870967742</v>
@@ -1000,24 +1254,18 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>LTR127_2017</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>LTR127</t>
-        </is>
+    <row r="9" spans="1:21">
+      <c r="A9" t="s">
+        <v>47</v>
+      </c>
+      <c r="B9" t="s">
+        <v>32</v>
       </c>
       <c r="C9">
         <v>2017</v>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Skirvytė</t>
-        </is>
+      <c r="D9" t="s">
+        <v>33</v>
       </c>
       <c r="E9">
         <v>4</v>
@@ -1025,33 +1273,29 @@
       <c r="F9">
         <v>0.36</v>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Poor</t>
-        </is>
+      <c r="G9" t="s">
+        <v>25</v>
       </c>
       <c r="H9">
         <v>0.31</v>
       </c>
       <c r="I9">
-        <v>0.3139586709886548</v>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>Poor</t>
-        </is>
+        <v>0.31395867098865482</v>
+      </c>
+      <c r="J9" t="s">
+        <v>25</v>
       </c>
       <c r="K9">
-        <v>0.1666666666666667</v>
+        <v>0.16666666666666671</v>
       </c>
       <c r="L9">
-        <v>0.4333333333333333</v>
+        <v>0.43333333333333329</v>
       </c>
       <c r="M9">
         <v>0.2</v>
       </c>
       <c r="N9">
-        <v>0.4558346839546191</v>
+        <v>0.45583468395461912</v>
       </c>
       <c r="O9">
         <v>1.827956989247312</v>
@@ -1065,36 +1309,28 @@
       <c r="R9">
         <v>5.591397849462366</v>
       </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>DSFI</t>
-        </is>
+      <c r="S9" t="s">
+        <v>35</v>
       </c>
       <c r="T9">
         <v>1.827956989247312</v>
       </c>
       <c r="U9">
-        <v>0.04999999999999999</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>LTR127_2020</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>LTR127</t>
-        </is>
+        <v>4.9999999999999989E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21">
+      <c r="A10" t="s">
+        <v>48</v>
+      </c>
+      <c r="B10" t="s">
+        <v>32</v>
       </c>
       <c r="C10">
         <v>2020</v>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Skirvytė</t>
-        </is>
+      <c r="D10" t="s">
+        <v>33</v>
       </c>
       <c r="E10">
         <v>4</v>
@@ -1102,36 +1338,32 @@
       <c r="F10">
         <v>0.48</v>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
+      <c r="G10" t="s">
+        <v>24</v>
       </c>
       <c r="H10">
         <v>0.42</v>
       </c>
       <c r="I10">
-        <v>0.4235972401202749</v>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
+        <v>0.42359724012027489</v>
+      </c>
+      <c r="J10" t="s">
+        <v>24</v>
       </c>
       <c r="K10">
         <v>0.5</v>
       </c>
       <c r="L10">
-        <v>0.6041666666666666</v>
+        <v>0.60416666666666663</v>
       </c>
       <c r="M10">
         <v>0.2</v>
       </c>
       <c r="N10">
-        <v>0.390222293814433</v>
+        <v>0.39022229381443302</v>
       </c>
       <c r="O10">
-        <v>30.16129032258064</v>
+        <v>30.161290322580641</v>
       </c>
       <c r="P10">
         <v>17.79569892473118</v>
@@ -1142,10 +1374,8 @@
       <c r="R10">
         <v>3.440860215053763</v>
       </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>EHP-CrHi</t>
-        </is>
+      <c r="S10" t="s">
+        <v>26</v>
       </c>
       <c r="T10">
         <v>3.440860215053763</v>
@@ -1154,24 +1384,18 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>LTR625_2022</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>LTR625</t>
-        </is>
+    <row r="11" spans="1:21">
+      <c r="A11" t="s">
+        <v>49</v>
+      </c>
+      <c r="B11" t="s">
+        <v>50</v>
       </c>
       <c r="C11">
         <v>2022</v>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Luoba</t>
-        </is>
+      <c r="D11" t="s">
+        <v>51</v>
       </c>
       <c r="E11">
         <v>3</v>
@@ -1179,76 +1403,64 @@
       <c r="F11">
         <v>0.83</v>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
+      <c r="G11" t="s">
+        <v>42</v>
       </c>
       <c r="H11">
         <v>0.78</v>
       </c>
       <c r="I11">
-        <v>0.7794520935069633</v>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>Good</t>
-        </is>
+        <v>0.77945209350696332</v>
+      </c>
+      <c r="J11" t="s">
+        <v>30</v>
       </c>
       <c r="K11">
-        <v>0.6666666666666666</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="L11">
-        <v>0.7999999999999999</v>
+        <v>0.79999999999999993</v>
       </c>
       <c r="M11">
-        <v>1.066666666666667</v>
+        <v>1.0666666666666671</v>
       </c>
       <c r="N11">
-        <v>0.5844750406945198</v>
+        <v>0.58447504069451983</v>
       </c>
       <c r="O11">
-        <v>60.21505376344086</v>
+        <v>60.215053763440856</v>
       </c>
       <c r="P11">
-        <v>71.12903225806451</v>
+        <v>71.129032258064512</v>
       </c>
       <c r="Q11">
-        <v>98.60215053763442</v>
+        <v>98.602150537634415</v>
       </c>
       <c r="R11">
         <v>19.78494623655914</v>
       </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>EHP-CrHi</t>
-        </is>
+      <c r="S11" t="s">
+        <v>26</v>
       </c>
       <c r="T11">
         <v>19.78494623655914</v>
       </c>
       <c r="U11">
-        <v>0.04999999999999993</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>LTR1466_2016</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>LTR1466</t>
-        </is>
+        <v>4.9999999999999933E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21">
+      <c r="A12" t="s">
+        <v>52</v>
+      </c>
+      <c r="B12" t="s">
+        <v>40</v>
       </c>
       <c r="C12">
         <v>2016</v>
       </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Įpiltis</t>
-        </is>
+      <c r="D12" t="s">
+        <v>41</v>
       </c>
       <c r="E12">
         <v>3</v>
@@ -1256,76 +1468,64 @@
       <c r="F12">
         <v>0.6</v>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Good</t>
-        </is>
+      <c r="G12" t="s">
+        <v>30</v>
       </c>
       <c r="H12">
-        <v>0.5600000000000001</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="I12">
-        <v>0.5627091284987278</v>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
+        <v>0.56270912849872778</v>
+      </c>
+      <c r="J12" t="s">
+        <v>24</v>
       </c>
       <c r="K12">
         <v>0.5</v>
       </c>
       <c r="L12">
-        <v>0.6533333333333333</v>
+        <v>0.65333333333333332</v>
       </c>
       <c r="M12">
-        <v>0.5333333333333333</v>
+        <v>0.53333333333333333</v>
       </c>
       <c r="N12">
-        <v>0.5641698473282443</v>
+        <v>0.56416984732824427</v>
       </c>
       <c r="O12">
-        <v>30.16129032258064</v>
+        <v>30.161290322580641</v>
       </c>
       <c r="P12">
         <v>28.06451612903226</v>
       </c>
       <c r="Q12">
-        <v>70.3225806451613</v>
+        <v>70.322580645161295</v>
       </c>
       <c r="R12">
         <v>15.6989247311828</v>
       </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>EHP-CrHi</t>
-        </is>
+      <c r="S12" t="s">
+        <v>26</v>
       </c>
       <c r="T12">
         <v>15.6989247311828</v>
       </c>
       <c r="U12">
-        <v>0.03999999999999992</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>LTR1687_2016</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>LTR1687</t>
-        </is>
+        <v>3.9999999999999918E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21">
+      <c r="A13" t="s">
+        <v>53</v>
+      </c>
+      <c r="B13" t="s">
+        <v>54</v>
       </c>
       <c r="C13">
         <v>2016</v>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Šalpė</t>
-        </is>
+      <c r="D13" t="s">
+        <v>55</v>
       </c>
       <c r="E13">
         <v>3</v>
@@ -1333,76 +1533,64 @@
       <c r="F13">
         <v>0.59</v>
       </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
+      <c r="G13" t="s">
+        <v>24</v>
       </c>
       <c r="H13">
-        <v>0.55</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="I13">
         <v>0.545704134366925</v>
       </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
+      <c r="J13" t="s">
+        <v>24</v>
       </c>
       <c r="K13">
         <v>0.5</v>
       </c>
       <c r="L13">
-        <v>0.7777777777777778</v>
+        <v>0.77777777777777779</v>
       </c>
       <c r="M13">
-        <v>0.3333333333333333</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="N13">
-        <v>0.5717054263565891</v>
+        <v>0.57170542635658905</v>
       </c>
       <c r="O13">
-        <v>30.16129032258064</v>
+        <v>30.161290322580641</v>
       </c>
       <c r="P13">
-        <v>63.97849462365591</v>
+        <v>63.978494623655912</v>
       </c>
       <c r="Q13">
-        <v>40.80645161290322</v>
+        <v>40.806451612903217</v>
       </c>
       <c r="R13">
-        <v>17.09677419354839</v>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>EHP-CrHi</t>
-        </is>
+        <v>17.096774193548391</v>
+      </c>
+      <c r="S13" t="s">
+        <v>26</v>
       </c>
       <c r="T13">
-        <v>17.09677419354839</v>
+        <v>17.096774193548391</v>
       </c>
       <c r="U13">
-        <v>0.03999999999999992</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>LTR1687_2022</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>LTR1687</t>
-        </is>
+        <v>3.9999999999999918E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21">
+      <c r="A14" t="s">
+        <v>56</v>
+      </c>
+      <c r="B14" t="s">
+        <v>54</v>
       </c>
       <c r="C14">
         <v>2022</v>
       </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Šalpė</t>
-        </is>
+      <c r="D14" t="s">
+        <v>55</v>
       </c>
       <c r="E14">
         <v>3</v>
@@ -1410,76 +1598,64 @@
       <c r="F14">
         <v>0.7</v>
       </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Good</t>
-        </is>
+      <c r="G14" t="s">
+        <v>30</v>
       </c>
       <c r="H14">
         <v>0.66</v>
       </c>
       <c r="I14">
-        <v>0.6608108108108108</v>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>Good</t>
-        </is>
+        <v>0.66081081081081083</v>
+      </c>
+      <c r="J14" t="s">
+        <v>30</v>
       </c>
       <c r="K14">
-        <v>0.6666666666666666</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="L14">
-        <v>0.9666666666666667</v>
+        <v>0.96666666666666667</v>
       </c>
       <c r="M14">
-        <v>0.2666666666666667</v>
+        <v>0.26666666666666672</v>
       </c>
       <c r="N14">
         <v>0.7432432432432432</v>
       </c>
       <c r="O14">
-        <v>60.21505376344086</v>
+        <v>60.215053763440856</v>
       </c>
       <c r="P14">
-        <v>97.31182795698925</v>
+        <v>97.311827956989248</v>
       </c>
       <c r="Q14">
         <v>29.35483870967742</v>
       </c>
       <c r="R14">
-        <v>73.87096774193549</v>
-      </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>DEP</t>
-        </is>
+        <v>73.870967741935488</v>
+      </c>
+      <c r="S14" t="s">
+        <v>57</v>
       </c>
       <c r="T14">
         <v>29.35483870967742</v>
       </c>
       <c r="U14">
-        <v>0.03999999999999992</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>LTR297_2021</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>LTR297</t>
-        </is>
+        <v>3.9999999999999918E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21">
+      <c r="A15" t="s">
+        <v>58</v>
+      </c>
+      <c r="B15" t="s">
+        <v>59</v>
       </c>
       <c r="C15">
         <v>2021</v>
       </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Lokysta</t>
-        </is>
+      <c r="D15" t="s">
+        <v>60</v>
       </c>
       <c r="E15">
         <v>3</v>
@@ -1487,153 +1663,129 @@
       <c r="F15">
         <v>0.5</v>
       </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
+      <c r="G15" t="s">
+        <v>24</v>
       </c>
       <c r="H15">
         <v>0.54</v>
       </c>
       <c r="I15">
-        <v>0.5408653846153846</v>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
+        <v>0.54086538461538458</v>
+      </c>
+      <c r="J15" t="s">
+        <v>24</v>
       </c>
       <c r="K15">
         <v>0.5</v>
       </c>
       <c r="L15">
-        <v>0.7051282051282052</v>
+        <v>0.70512820512820518</v>
       </c>
       <c r="M15">
-        <v>0.3333333333333333</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="N15">
         <v>0.625</v>
       </c>
       <c r="O15">
-        <v>30.16129032258064</v>
+        <v>30.161290322580641</v>
       </c>
       <c r="P15">
-        <v>40.21505376344086</v>
+        <v>40.215053763440856</v>
       </c>
       <c r="Q15">
-        <v>40.80645161290322</v>
+        <v>40.806451612903217</v>
       </c>
       <c r="R15">
-        <v>31.66666666666667</v>
-      </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>DSFI</t>
-        </is>
+        <v>31.666666666666671</v>
+      </c>
+      <c r="S15" t="s">
+        <v>35</v>
       </c>
       <c r="T15">
-        <v>30.16129032258064</v>
+        <v>30.161290322580641</v>
       </c>
       <c r="U15">
-        <v>-0.04000000000000004</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>LTR1447_2015</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>LTR1447</t>
-        </is>
+        <v>-4.0000000000000042E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21">
+      <c r="A16" t="s">
+        <v>61</v>
+      </c>
+      <c r="B16" t="s">
+        <v>62</v>
       </c>
       <c r="C16">
         <v>2015</v>
       </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Merkys</t>
-        </is>
+      <c r="D16" t="s">
+        <v>63</v>
       </c>
       <c r="E16">
         <v>5</v>
       </c>
       <c r="F16">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Good</t>
-        </is>
+        <v>0.69</v>
+      </c>
+      <c r="G16" t="s">
+        <v>30</v>
       </c>
       <c r="H16">
         <v>0.65</v>
       </c>
       <c r="I16">
-        <v>0.6500646479813146</v>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>Good</t>
-        </is>
+        <v>0.65006464798131458</v>
+      </c>
+      <c r="J16" t="s">
+        <v>30</v>
       </c>
       <c r="K16">
-        <v>0.6666666666666666</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="L16">
         <v>0.7901234567901233</v>
       </c>
       <c r="M16">
-        <v>0.4666666666666667</v>
+        <v>0.46666666666666667</v>
       </c>
       <c r="N16">
-        <v>0.6768018018018018</v>
+        <v>0.67680180180180183</v>
       </c>
       <c r="O16">
-        <v>60.21505376344086</v>
+        <v>60.215053763440856</v>
       </c>
       <c r="P16">
         <v>68.27956989247312</v>
       </c>
       <c r="Q16">
-        <v>61.02150537634409</v>
+        <v>61.021505376344088</v>
       </c>
       <c r="R16">
         <v>50.86021505376344</v>
       </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>EHP-CrHi</t>
-        </is>
+      <c r="S16" t="s">
+        <v>26</v>
       </c>
       <c r="T16">
         <v>50.86021505376344</v>
       </c>
       <c r="U16">
-        <v>0.03999999999999992</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>LTR86_2015</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>LTR86</t>
-        </is>
+        <v>3.9999999999999918E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:21">
+      <c r="A17" t="s">
+        <v>64</v>
+      </c>
+      <c r="B17" t="s">
+        <v>65</v>
       </c>
       <c r="C17">
         <v>2015</v>
       </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Mūša</t>
-        </is>
+      <c r="D17" t="s">
+        <v>23</v>
       </c>
       <c r="E17">
         <v>5</v>
@@ -1641,39 +1793,35 @@
       <c r="F17">
         <v>0.5</v>
       </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
+      <c r="G17" t="s">
+        <v>24</v>
       </c>
       <c r="H17">
         <v>0.46</v>
       </c>
       <c r="I17">
-        <v>0.4592948717948718</v>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
+        <v>0.45929487179487177</v>
+      </c>
+      <c r="J17" t="s">
+        <v>24</v>
       </c>
       <c r="K17">
-        <v>0.3333333333333333</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="L17">
-        <v>0.6388888888888888</v>
+        <v>0.63888888888888884</v>
       </c>
       <c r="M17">
-        <v>0.2666666666666667</v>
+        <v>0.26666666666666672</v>
       </c>
       <c r="N17">
-        <v>0.5982905982905983</v>
+        <v>0.59829059829059827</v>
       </c>
       <c r="O17">
         <v>7.365591397849462</v>
       </c>
       <c r="P17">
-        <v>24.94623655913978</v>
+        <v>24.946236559139781</v>
       </c>
       <c r="Q17">
         <v>29.35483870967742</v>
@@ -1681,36 +1829,28 @@
       <c r="R17">
         <v>22.36559139784946</v>
       </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>DSFI</t>
-        </is>
+      <c r="S17" t="s">
+        <v>35</v>
       </c>
       <c r="T17">
         <v>7.365591397849462</v>
       </c>
       <c r="U17">
-        <v>0.03999999999999998</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>LTR1461_2022</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>LTR1461</t>
-        </is>
+        <v>3.999999999999998E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:21">
+      <c r="A18" t="s">
+        <v>66</v>
+      </c>
+      <c r="B18" t="s">
+        <v>67</v>
       </c>
       <c r="C18">
         <v>2022</v>
       </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Nemunėlis</t>
-        </is>
+      <c r="D18" t="s">
+        <v>68</v>
       </c>
       <c r="E18">
         <v>1</v>
@@ -1718,10 +1858,8 @@
       <c r="F18">
         <v>0.54</v>
       </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
+      <c r="G18" t="s">
+        <v>24</v>
       </c>
       <c r="H18">
         <v>0.51</v>
@@ -1729,65 +1867,55 @@
       <c r="I18">
         <v>0.5133803291958986</v>
       </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
+      <c r="J18" t="s">
+        <v>24</v>
       </c>
       <c r="K18">
         <v>0.5</v>
       </c>
       <c r="L18">
-        <v>0.6274509803921569</v>
+        <v>0.62745098039215685</v>
       </c>
       <c r="M18">
-        <v>0.2666666666666667</v>
+        <v>0.26666666666666672</v>
       </c>
       <c r="N18">
-        <v>0.6594036697247707</v>
+        <v>0.65940366972477071</v>
       </c>
       <c r="O18">
-        <v>30.16129032258064</v>
+        <v>30.161290322580641</v>
       </c>
       <c r="P18">
-        <v>21.82795698924731</v>
+        <v>21.827956989247308</v>
       </c>
       <c r="Q18">
         <v>29.35483870967742</v>
       </c>
       <c r="R18">
-        <v>44.51612903225806</v>
-      </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>ASPT</t>
-        </is>
+        <v>44.516129032258057</v>
+      </c>
+      <c r="S18" t="s">
+        <v>69</v>
       </c>
       <c r="T18">
-        <v>21.82795698924731</v>
+        <v>21.827956989247308</v>
       </c>
       <c r="U18">
-        <v>0.03000000000000003</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>LTR1461_2016</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>LTR1461</t>
-        </is>
+        <v>3.000000000000003E-2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:21">
+      <c r="A19" t="s">
+        <v>70</v>
+      </c>
+      <c r="B19" t="s">
+        <v>67</v>
       </c>
       <c r="C19">
         <v>2016</v>
       </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Nemunėlis</t>
-        </is>
+      <c r="D19" t="s">
+        <v>68</v>
       </c>
       <c r="E19">
         <v>1</v>
@@ -1795,76 +1923,64 @@
       <c r="F19">
         <v>0.64</v>
       </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>Good</t>
-        </is>
+      <c r="G19" t="s">
+        <v>30</v>
       </c>
       <c r="H19">
         <v>0.67</v>
       </c>
       <c r="I19">
-        <v>0.673630007558579</v>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>Good</t>
-        </is>
+        <v>0.67363000755857905</v>
+      </c>
+      <c r="J19" t="s">
+        <v>30</v>
       </c>
       <c r="K19">
-        <v>0.8333333333333334</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="L19">
-        <v>0.8703703703703703</v>
+        <v>0.87037037037037035</v>
       </c>
       <c r="M19">
         <v>0.2</v>
       </c>
       <c r="N19">
-        <v>0.7908163265306123</v>
+        <v>0.79081632653061229</v>
       </c>
       <c r="O19">
-        <v>82.20430107526882</v>
+        <v>82.204301075268816</v>
       </c>
       <c r="P19">
-        <v>87.25806451612904</v>
+        <v>87.258064516129039</v>
       </c>
       <c r="Q19">
         <v>18.44086021505376</v>
       </c>
       <c r="R19">
-        <v>84.08602150537635</v>
-      </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>DEP</t>
-        </is>
+        <v>84.086021505376351</v>
+      </c>
+      <c r="S19" t="s">
+        <v>57</v>
       </c>
       <c r="T19">
         <v>18.44086021505376</v>
       </c>
       <c r="U19">
-        <v>-0.03000000000000003</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>LTR1461_2019</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>LTR1461</t>
-        </is>
+        <v>-3.000000000000003E-2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:21">
+      <c r="A20" t="s">
+        <v>71</v>
+      </c>
+      <c r="B20" t="s">
+        <v>67</v>
       </c>
       <c r="C20">
         <v>2019</v>
       </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Nemunėlis</t>
-        </is>
+      <c r="D20" t="s">
+        <v>68</v>
       </c>
       <c r="E20">
         <v>1</v>
@@ -1872,76 +1988,64 @@
       <c r="F20">
         <v>0.66</v>
       </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>Good</t>
-        </is>
+      <c r="G20" t="s">
+        <v>30</v>
       </c>
       <c r="H20">
         <v>0.63</v>
       </c>
       <c r="I20">
-        <v>0.6307583166569837</v>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>Good</t>
-        </is>
+        <v>0.63075831665698368</v>
+      </c>
+      <c r="J20" t="s">
+        <v>30</v>
       </c>
       <c r="K20">
         <v>0.5</v>
       </c>
       <c r="L20">
-        <v>0.7559523809523809</v>
+        <v>0.75595238095238093</v>
       </c>
       <c r="M20">
         <v>0.6</v>
       </c>
       <c r="N20">
-        <v>0.6670808856755536</v>
+        <v>0.66708088567555357</v>
       </c>
       <c r="O20">
-        <v>30.16129032258064</v>
+        <v>30.161290322580641</v>
       </c>
       <c r="P20">
-        <v>56.61290322580645</v>
+        <v>56.612903225806448</v>
       </c>
       <c r="Q20">
-        <v>77.68817204301075</v>
+        <v>77.688172043010752</v>
       </c>
       <c r="R20">
         <v>47.41935483870968</v>
       </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>DSFI</t>
-        </is>
+      <c r="S20" t="s">
+        <v>35</v>
       </c>
       <c r="T20">
-        <v>30.16129032258064</v>
+        <v>30.161290322580641</v>
       </c>
       <c r="U20">
-        <v>0.03000000000000003</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>LTR1466_2022</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>LTR1466</t>
-        </is>
+        <v>3.000000000000003E-2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:21">
+      <c r="A21" t="s">
+        <v>72</v>
+      </c>
+      <c r="B21" t="s">
+        <v>40</v>
       </c>
       <c r="C21">
         <v>2022</v>
       </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Įpiltis</t>
-        </is>
+      <c r="D21" t="s">
+        <v>41</v>
       </c>
       <c r="E21">
         <v>3</v>
@@ -1949,153 +2053,129 @@
       <c r="F21">
         <v>0.52</v>
       </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
+      <c r="G21" t="s">
+        <v>24</v>
       </c>
       <c r="H21">
         <v>0.49</v>
       </c>
       <c r="I21">
-        <v>0.4912507289161018</v>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
+        <v>0.49125072891610178</v>
+      </c>
+      <c r="J21" t="s">
+        <v>24</v>
       </c>
       <c r="K21">
         <v>0.5</v>
       </c>
       <c r="L21">
-        <v>0.5686274509803922</v>
+        <v>0.56862745098039225</v>
       </c>
       <c r="M21">
-        <v>0.3333333333333333</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="N21">
-        <v>0.5630421313506815</v>
+        <v>0.56304213135068149</v>
       </c>
       <c r="O21">
-        <v>30.16129032258064</v>
+        <v>30.161290322580641</v>
       </c>
       <c r="P21">
         <v>12.41935483870968</v>
       </c>
       <c r="Q21">
-        <v>40.80645161290322</v>
+        <v>40.806451612903217</v>
       </c>
       <c r="R21">
-        <v>15.26881720430108</v>
-      </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>ASPT</t>
-        </is>
+        <v>15.268817204301079</v>
+      </c>
+      <c r="S21" t="s">
+        <v>69</v>
       </c>
       <c r="T21">
         <v>12.41935483870968</v>
       </c>
       <c r="U21">
-        <v>0.03000000000000003</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>LTR386_2016</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>LTR386</t>
-        </is>
+        <v>3.000000000000003E-2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:21">
+      <c r="A22" t="s">
+        <v>73</v>
+      </c>
+      <c r="B22" t="s">
+        <v>37</v>
       </c>
       <c r="C22">
         <v>2016</v>
       </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Viešinta</t>
-        </is>
+      <c r="D22" t="s">
+        <v>38</v>
       </c>
       <c r="E22">
         <v>1</v>
       </c>
       <c r="F22">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>Good</t>
-        </is>
+        <v>0.69</v>
+      </c>
+      <c r="G22" t="s">
+        <v>30</v>
       </c>
       <c r="H22">
         <v>0.72</v>
       </c>
       <c r="I22">
-        <v>0.7227519170860293</v>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>Good</t>
-        </is>
+        <v>0.72275191708602926</v>
+      </c>
+      <c r="J22" t="s">
+        <v>30</v>
       </c>
       <c r="K22">
-        <v>0.8333333333333334</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="L22">
-        <v>0.7820512820512823</v>
+        <v>0.78205128205128227</v>
       </c>
       <c r="M22">
         <v>0.6</v>
       </c>
       <c r="N22">
-        <v>0.6756230529595015</v>
+        <v>0.67562305295950154</v>
       </c>
       <c r="O22">
-        <v>82.20430107526882</v>
+        <v>82.204301075268816</v>
       </c>
       <c r="P22">
-        <v>65.48387096774194</v>
+        <v>65.483870967741936</v>
       </c>
       <c r="Q22">
-        <v>77.68817204301075</v>
+        <v>77.688172043010752</v>
       </c>
       <c r="R22">
         <v>50.43010752688172</v>
       </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>EHP-CrHi</t>
-        </is>
+      <c r="S22" t="s">
+        <v>26</v>
       </c>
       <c r="T22">
         <v>50.43010752688172</v>
       </c>
       <c r="U22">
-        <v>-0.03000000000000003</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>LTR386_2022</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>LTR386</t>
-        </is>
+        <v>-3.000000000000003E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:21">
+      <c r="A23" t="s">
+        <v>74</v>
+      </c>
+      <c r="B23" t="s">
+        <v>37</v>
       </c>
       <c r="C23">
         <v>2022</v>
       </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Viešinta</t>
-        </is>
+      <c r="D23" t="s">
+        <v>38</v>
       </c>
       <c r="E23">
         <v>1</v>
@@ -2103,76 +2183,64 @@
       <c r="F23">
         <v>0.74</v>
       </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>Good</t>
-        </is>
+      <c r="G23" t="s">
+        <v>30</v>
       </c>
       <c r="H23">
         <v>0.71</v>
       </c>
       <c r="I23">
-        <v>0.7054495487711214</v>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>Good</t>
-        </is>
+        <v>0.70544954877112143</v>
+      </c>
+      <c r="J23" t="s">
+        <v>30</v>
       </c>
       <c r="K23">
-        <v>0.8333333333333334</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="L23">
-        <v>0.8118279569892474</v>
+        <v>0.81182795698924737</v>
       </c>
       <c r="M23">
         <v>0.6</v>
       </c>
       <c r="N23">
-        <v>0.5766369047619048</v>
+        <v>0.57663690476190477</v>
       </c>
       <c r="O23">
-        <v>82.20430107526882</v>
+        <v>82.204301075268816</v>
       </c>
       <c r="P23">
         <v>74.3010752688172</v>
       </c>
       <c r="Q23">
-        <v>77.68817204301075</v>
+        <v>77.688172043010752</v>
       </c>
       <c r="R23">
-        <v>17.95698924731183</v>
-      </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>EHP-CrHi</t>
-        </is>
+        <v>17.956989247311832</v>
+      </c>
+      <c r="S23" t="s">
+        <v>26</v>
       </c>
       <c r="T23">
-        <v>17.95698924731183</v>
+        <v>17.956989247311832</v>
       </c>
       <c r="U23">
-        <v>0.03000000000000003</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>LTR1488_2015</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>LTR1488</t>
-        </is>
+        <v>3.000000000000003E-2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:21">
+      <c r="A24" t="s">
+        <v>75</v>
+      </c>
+      <c r="B24" t="s">
+        <v>76</v>
       </c>
       <c r="C24">
         <v>2015</v>
       </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Neris</t>
-        </is>
+      <c r="D24" t="s">
+        <v>77</v>
       </c>
       <c r="E24">
         <v>4</v>
@@ -2180,76 +2248,64 @@
       <c r="F24">
         <v>0.62</v>
       </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>Good</t>
-        </is>
+      <c r="G24" t="s">
+        <v>30</v>
       </c>
       <c r="H24">
         <v>0.59</v>
       </c>
       <c r="I24">
-        <v>0.5924559591126577</v>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
+        <v>0.59245595911265769</v>
+      </c>
+      <c r="J24" t="s">
+        <v>24</v>
       </c>
       <c r="K24">
         <v>0.5</v>
       </c>
       <c r="L24">
-        <v>0.7105263157894736</v>
+        <v>0.71052631578947356</v>
       </c>
       <c r="M24">
         <v>0.4</v>
       </c>
       <c r="N24">
-        <v>0.759297520661157</v>
+        <v>0.75929752066115697</v>
       </c>
       <c r="O24">
-        <v>30.16129032258064</v>
+        <v>30.161290322580641</v>
       </c>
       <c r="P24">
         <v>41.55913978494624</v>
       </c>
       <c r="Q24">
-        <v>51.45161290322581</v>
+        <v>51.451612903225808</v>
       </c>
       <c r="R24">
         <v>77.41935483870968</v>
       </c>
-      <c r="S24" t="inlineStr">
-        <is>
-          <t>DSFI</t>
-        </is>
+      <c r="S24" t="s">
+        <v>35</v>
       </c>
       <c r="T24">
-        <v>30.16129032258064</v>
+        <v>30.161290322580641</v>
       </c>
       <c r="U24">
-        <v>0.03000000000000003</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>LTR1063_2021</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>LTR1063</t>
-        </is>
+        <v>3.000000000000003E-2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:21">
+      <c r="A25" t="s">
+        <v>78</v>
+      </c>
+      <c r="B25" t="s">
+        <v>79</v>
       </c>
       <c r="C25">
         <v>2021</v>
       </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>PentaII</t>
-        </is>
+      <c r="D25" t="s">
+        <v>80</v>
       </c>
       <c r="E25">
         <v>1</v>
@@ -2257,33 +2313,29 @@
       <c r="F25">
         <v>0.35</v>
       </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>Poor</t>
-        </is>
+      <c r="G25" t="s">
+        <v>25</v>
       </c>
       <c r="H25">
         <v>0.33</v>
       </c>
       <c r="I25">
-        <v>0.3324177046263345</v>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>Poor</t>
-        </is>
+        <v>0.33241770462633452</v>
+      </c>
+      <c r="J25" t="s">
+        <v>25</v>
       </c>
       <c r="K25">
-        <v>0.1666666666666667</v>
+        <v>0.16666666666666671</v>
       </c>
       <c r="L25">
-        <v>0.3958333333333333</v>
+        <v>0.39583333333333331</v>
       </c>
       <c r="M25">
         <v>0.2</v>
       </c>
       <c r="N25">
-        <v>0.567170818505338</v>
+        <v>0.56717081850533801</v>
       </c>
       <c r="O25">
         <v>1.827956989247312</v>
@@ -2295,38 +2347,30 @@
         <v>18.44086021505376</v>
       </c>
       <c r="R25">
-        <v>16.23655913978495</v>
-      </c>
-      <c r="S25" t="inlineStr">
-        <is>
-          <t>ASPT</t>
-        </is>
+        <v>16.236559139784951</v>
+      </c>
+      <c r="S25" t="s">
+        <v>69</v>
       </c>
       <c r="T25">
         <v>1.021505376344086</v>
       </c>
       <c r="U25">
-        <v>0.01999999999999996</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>LTR163_2016</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>LTR163</t>
-        </is>
+        <v>1.9999999999999959E-2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:21">
+      <c r="A26" t="s">
+        <v>81</v>
+      </c>
+      <c r="B26" t="s">
+        <v>28</v>
       </c>
       <c r="C26">
         <v>2016</v>
       </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Geluža</t>
-        </is>
+      <c r="D26" t="s">
+        <v>29</v>
       </c>
       <c r="E26">
         <v>1</v>
@@ -2334,76 +2378,64 @@
       <c r="F26">
         <v>0.88</v>
       </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
+      <c r="G26" t="s">
+        <v>42</v>
       </c>
       <c r="H26">
         <v>0.86</v>
       </c>
       <c r="I26">
-        <v>0.8632449413069425</v>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
+        <v>0.86324494130694251</v>
+      </c>
+      <c r="J26" t="s">
+        <v>42</v>
       </c>
       <c r="K26">
         <v>1</v>
       </c>
       <c r="L26">
-        <v>0.7988505747126436</v>
+        <v>0.79885057471264365</v>
       </c>
       <c r="M26">
         <v>1</v>
       </c>
       <c r="N26">
-        <v>0.6541291905151266</v>
+        <v>0.65412919051512664</v>
       </c>
       <c r="O26">
-        <v>96.34408602150538</v>
+        <v>96.344086021505376</v>
       </c>
       <c r="P26">
-        <v>70.75268817204301</v>
+        <v>70.752688172043008</v>
       </c>
       <c r="Q26">
-        <v>97.84946236559139</v>
+        <v>97.849462365591393</v>
       </c>
       <c r="R26">
-        <v>43.11827956989247</v>
-      </c>
-      <c r="S26" t="inlineStr">
-        <is>
-          <t>EHP-CrHi</t>
-        </is>
+        <v>43.118279569892472</v>
+      </c>
+      <c r="S26" t="s">
+        <v>26</v>
       </c>
       <c r="T26">
-        <v>43.11827956989247</v>
+        <v>43.118279569892472</v>
       </c>
       <c r="U26">
-        <v>0.02000000000000002</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>LTR308_2018</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>LTR308</t>
-        </is>
+        <v>2.0000000000000021E-2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:21">
+      <c r="A27" t="s">
+        <v>82</v>
+      </c>
+      <c r="B27" t="s">
+        <v>83</v>
       </c>
       <c r="C27">
         <v>2018</v>
       </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Eketė</t>
-        </is>
+      <c r="D27" t="s">
+        <v>84</v>
       </c>
       <c r="E27">
         <v>1</v>
@@ -2411,33 +2443,29 @@
       <c r="F27">
         <v>0.36</v>
       </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>Poor</t>
-        </is>
+      <c r="G27" t="s">
+        <v>25</v>
       </c>
       <c r="H27">
         <v>0.34</v>
       </c>
       <c r="I27">
-        <v>0.3383101851851852</v>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>Poor</t>
-        </is>
+        <v>0.33831018518518519</v>
+      </c>
+      <c r="J27" t="s">
+        <v>25</v>
       </c>
       <c r="K27">
-        <v>0.3333333333333333</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="L27">
-        <v>0.3541666666666667</v>
+        <v>0.35416666666666669</v>
       </c>
       <c r="M27">
         <v>0.1333333333333333</v>
       </c>
       <c r="N27">
-        <v>0.5324074074074073</v>
+        <v>0.53240740740740733</v>
       </c>
       <c r="O27">
         <v>7.365591397849462</v>
@@ -2446,41 +2474,33 @@
         <v>0.4838709677419355</v>
       </c>
       <c r="Q27">
-        <v>9.13978494623656</v>
+        <v>9.1397849462365599</v>
       </c>
       <c r="R27">
         <v>11.0752688172043</v>
       </c>
-      <c r="S27" t="inlineStr">
-        <is>
-          <t>ASPT</t>
-        </is>
+      <c r="S27" t="s">
+        <v>69</v>
       </c>
       <c r="T27">
         <v>0.4838709677419355</v>
       </c>
       <c r="U27">
-        <v>0.01999999999999996</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>LTR450_2020</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>LTR450</t>
-        </is>
+        <v>1.9999999999999959E-2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:21">
+      <c r="A28" t="s">
+        <v>85</v>
+      </c>
+      <c r="B28" t="s">
+        <v>45</v>
       </c>
       <c r="C28">
         <v>2020</v>
       </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Ringuva</t>
-        </is>
+      <c r="D28" t="s">
+        <v>46</v>
       </c>
       <c r="E28">
         <v>2</v>
@@ -2488,24 +2508,20 @@
       <c r="F28">
         <v>0.38</v>
       </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>Poor</t>
-        </is>
+      <c r="G28" t="s">
+        <v>25</v>
       </c>
       <c r="H28">
         <v>0.36</v>
       </c>
       <c r="I28">
-        <v>0.3591239959839357</v>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>Poor</t>
-        </is>
+        <v>0.35912399598393568</v>
+      </c>
+      <c r="J28" t="s">
+        <v>25</v>
       </c>
       <c r="K28">
-        <v>0.3333333333333333</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="L28">
         <v>0.5625</v>
@@ -2514,7 +2530,7 @@
         <v>0</v>
       </c>
       <c r="N28">
-        <v>0.5406626506024096</v>
+        <v>0.54066265060240959</v>
       </c>
       <c r="O28">
         <v>7.365591397849462</v>
@@ -2528,36 +2544,28 @@
       <c r="R28">
         <v>11.93548387096774</v>
       </c>
-      <c r="S28" t="inlineStr">
-        <is>
-          <t>DEP</t>
-        </is>
+      <c r="S28" t="s">
+        <v>57</v>
       </c>
       <c r="T28">
         <v>0.4838709677419355</v>
       </c>
       <c r="U28">
-        <v>0.02000000000000002</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>LTR297_2018</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>LTR297</t>
-        </is>
+        <v>2.0000000000000021E-2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:21">
+      <c r="A29" t="s">
+        <v>86</v>
+      </c>
+      <c r="B29" t="s">
+        <v>59</v>
       </c>
       <c r="C29">
         <v>2018</v>
       </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>Lokysta</t>
-        </is>
+      <c r="D29" t="s">
+        <v>60</v>
       </c>
       <c r="E29">
         <v>3</v>
@@ -2565,33 +2573,29 @@
       <c r="F29">
         <v>0.39</v>
       </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>Poor</t>
-        </is>
+      <c r="G29" t="s">
+        <v>25</v>
       </c>
       <c r="H29">
         <v>0.37</v>
       </c>
       <c r="I29">
-        <v>0.3661392405063291</v>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>Poor</t>
-        </is>
+        <v>0.36613924050632912</v>
+      </c>
+      <c r="J29" t="s">
+        <v>25</v>
       </c>
       <c r="K29">
-        <v>0.1666666666666667</v>
+        <v>0.16666666666666671</v>
       </c>
       <c r="L29">
-        <v>0.4333333333333333</v>
+        <v>0.43333333333333329</v>
       </c>
       <c r="M29">
         <v>0.2</v>
       </c>
       <c r="N29">
-        <v>0.6645569620253163</v>
+        <v>0.66455696202531633</v>
       </c>
       <c r="O29">
         <v>1.827956989247312</v>
@@ -2603,38 +2607,30 @@
         <v>18.44086021505376</v>
       </c>
       <c r="R29">
-        <v>46.7741935483871</v>
-      </c>
-      <c r="S29" t="inlineStr">
-        <is>
-          <t>DSFI</t>
-        </is>
+        <v>46.774193548387103</v>
+      </c>
+      <c r="S29" t="s">
+        <v>35</v>
       </c>
       <c r="T29">
         <v>1.827956989247312</v>
       </c>
       <c r="U29">
-        <v>0.02000000000000002</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>LTR706_2015</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>LTR706</t>
-        </is>
+        <v>2.0000000000000021E-2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:21">
+      <c r="A30" t="s">
+        <v>87</v>
+      </c>
+      <c r="B30" t="s">
+        <v>88</v>
       </c>
       <c r="C30">
         <v>2015</v>
       </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>Liaudė</t>
-        </is>
+      <c r="D30" t="s">
+        <v>89</v>
       </c>
       <c r="E30">
         <v>3</v>
@@ -2642,33 +2638,29 @@
       <c r="F30">
         <v>0.39</v>
       </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>Poor</t>
-        </is>
+      <c r="G30" t="s">
+        <v>25</v>
       </c>
       <c r="H30">
         <v>0.37</v>
       </c>
       <c r="I30">
-        <v>0.3700697899391929</v>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>Poor</t>
-        </is>
+        <v>0.37006978993919287</v>
+      </c>
+      <c r="J30" t="s">
+        <v>25</v>
       </c>
       <c r="K30">
-        <v>0.3333333333333333</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="L30">
-        <v>0.4259259259259258</v>
+        <v>0.42592592592592582</v>
       </c>
       <c r="M30">
         <v>0.1333333333333333</v>
       </c>
       <c r="N30">
-        <v>0.5876865671641791</v>
+        <v>0.58768656716417911</v>
       </c>
       <c r="O30">
         <v>7.365591397849462</v>
@@ -2677,41 +2669,33 @@
         <v>1.612903225806452</v>
       </c>
       <c r="Q30">
-        <v>9.13978494623656</v>
+        <v>9.1397849462365599</v>
       </c>
       <c r="R30">
-        <v>20.10752688172043</v>
-      </c>
-      <c r="S30" t="inlineStr">
-        <is>
-          <t>ASPT</t>
-        </is>
+        <v>20.107526881720428</v>
+      </c>
+      <c r="S30" t="s">
+        <v>69</v>
       </c>
       <c r="T30">
         <v>1.612903225806452</v>
       </c>
       <c r="U30">
-        <v>0.02000000000000002</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>LTR1488_2016</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>LTR1488</t>
-        </is>
+        <v>2.0000000000000021E-2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:21">
+      <c r="A31" t="s">
+        <v>90</v>
+      </c>
+      <c r="B31" t="s">
+        <v>76</v>
       </c>
       <c r="C31">
         <v>2016</v>
       </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>Neris</t>
-        </is>
+      <c r="D31" t="s">
+        <v>77</v>
       </c>
       <c r="E31">
         <v>4</v>
@@ -2719,76 +2703,64 @@
       <c r="F31">
         <v>0.68</v>
       </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>Good</t>
-        </is>
+      <c r="G31" t="s">
+        <v>30</v>
       </c>
       <c r="H31">
         <v>0.66</v>
       </c>
       <c r="I31">
-        <v>0.6647599750623441</v>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>Good</t>
-        </is>
+        <v>0.66475997506234408</v>
+      </c>
+      <c r="J31" t="s">
+        <v>30</v>
       </c>
       <c r="K31">
-        <v>0.6666666666666666</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="L31">
-        <v>0.8333333333333334</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="M31">
         <v>0.4</v>
       </c>
       <c r="N31">
-        <v>0.7590399002493765</v>
+        <v>0.75903990024937651</v>
       </c>
       <c r="O31">
-        <v>60.21505376344086</v>
+        <v>60.215053763440856</v>
       </c>
       <c r="P31">
-        <v>79.6236559139785</v>
+        <v>79.623655913978496</v>
       </c>
       <c r="Q31">
-        <v>51.45161290322581</v>
+        <v>51.451612903225808</v>
       </c>
       <c r="R31">
-        <v>77.20430107526882</v>
-      </c>
-      <c r="S31" t="inlineStr">
-        <is>
-          <t>DEP</t>
-        </is>
+        <v>77.204301075268816</v>
+      </c>
+      <c r="S31" t="s">
+        <v>57</v>
       </c>
       <c r="T31">
-        <v>51.45161290322581</v>
+        <v>51.451612903225808</v>
       </c>
       <c r="U31">
-        <v>0.02000000000000002</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>LTR1492_2019</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>LTR1492</t>
-        </is>
+        <v>2.0000000000000021E-2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:21">
+      <c r="A32" t="s">
+        <v>91</v>
+      </c>
+      <c r="B32" t="s">
+        <v>22</v>
       </c>
       <c r="C32">
         <v>2019</v>
       </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>Mūša</t>
-        </is>
+      <c r="D32" t="s">
+        <v>23</v>
       </c>
       <c r="E32">
         <v>5</v>
@@ -2796,27 +2768,23 @@
       <c r="F32">
         <v>0.49</v>
       </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
+      <c r="G32" t="s">
+        <v>24</v>
       </c>
       <c r="H32">
         <v>0.47</v>
       </c>
       <c r="I32">
-        <v>0.4692314540872233</v>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
+        <v>0.46923145408722328</v>
+      </c>
+      <c r="J32" t="s">
+        <v>24</v>
       </c>
       <c r="K32">
         <v>0.5</v>
       </c>
       <c r="L32">
-        <v>0.6018518518518517</v>
+        <v>0.60185185185185175</v>
       </c>
       <c r="M32">
         <v>0.2</v>
@@ -2825,7 +2793,7 @@
         <v>0.5750739644970414</v>
       </c>
       <c r="O32">
-        <v>30.16129032258064</v>
+        <v>30.161290322580641</v>
       </c>
       <c r="P32">
         <v>16.93548387096774</v>
@@ -2834,38 +2802,30 @@
         <v>18.44086021505376</v>
       </c>
       <c r="R32">
-        <v>17.52688172043011</v>
-      </c>
-      <c r="S32" t="inlineStr">
-        <is>
-          <t>ASPT</t>
-        </is>
+        <v>17.526881720430111</v>
+      </c>
+      <c r="S32" t="s">
+        <v>69</v>
       </c>
       <c r="T32">
         <v>16.93548387096774</v>
       </c>
       <c r="U32">
-        <v>0.02000000000000002</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>LTR1502_2015</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>LTR1502</t>
-        </is>
+        <v>2.0000000000000021E-2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:21">
+      <c r="A33" t="s">
+        <v>92</v>
+      </c>
+      <c r="B33" t="s">
+        <v>93</v>
       </c>
       <c r="C33">
         <v>2015</v>
       </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>Lėvuo</t>
-        </is>
+      <c r="D33" t="s">
+        <v>94</v>
       </c>
       <c r="E33">
         <v>5</v>
@@ -2873,116 +2833,100 @@
       <c r="F33">
         <v>0.72</v>
       </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>Good</t>
-        </is>
+      <c r="G33" t="s">
+        <v>30</v>
       </c>
       <c r="H33">
         <v>0.7</v>
       </c>
       <c r="I33">
-        <v>0.7023915816326531</v>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>Good</t>
-        </is>
+        <v>0.70239158163265314</v>
+      </c>
+      <c r="J33" t="s">
+        <v>30</v>
       </c>
       <c r="K33">
-        <v>0.8333333333333334</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="L33">
         <v>0.875</v>
       </c>
       <c r="M33">
-        <v>0.4666666666666667</v>
+        <v>0.46666666666666667</v>
       </c>
       <c r="N33">
-        <v>0.6345663265306123</v>
+        <v>0.63456632653061229</v>
       </c>
       <c r="O33">
-        <v>82.20430107526882</v>
+        <v>82.204301075268816</v>
       </c>
       <c r="P33">
-        <v>88.38709677419355</v>
+        <v>88.387096774193552</v>
       </c>
       <c r="Q33">
-        <v>61.02150537634409</v>
+        <v>61.021505376344088</v>
       </c>
       <c r="R33">
-        <v>35.16129032258065</v>
-      </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>EHP-CrHi</t>
-        </is>
+        <v>35.161290322580648</v>
+      </c>
+      <c r="S33" t="s">
+        <v>26</v>
       </c>
       <c r="T33">
-        <v>35.16129032258065</v>
+        <v>35.161290322580648</v>
       </c>
       <c r="U33">
-        <v>0.02000000000000002</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>LTR337_2019</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>LTR337</t>
-        </is>
+        <v>2.0000000000000021E-2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:21">
+      <c r="A34" t="s">
+        <v>95</v>
+      </c>
+      <c r="B34" t="s">
+        <v>96</v>
       </c>
       <c r="C34">
         <v>2019</v>
       </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>Svyla</t>
-        </is>
+      <c r="D34" t="s">
+        <v>97</v>
       </c>
       <c r="E34">
         <v>1</v>
       </c>
       <c r="F34">
-        <v>0.57</v>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="G34" t="s">
+        <v>24</v>
       </c>
       <c r="H34">
-        <v>0.5600000000000001</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="I34">
-        <v>0.5583831224617307</v>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
+        <v>0.55838312246173072</v>
+      </c>
+      <c r="J34" t="s">
+        <v>24</v>
       </c>
       <c r="K34">
-        <v>0.6666666666666666</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="L34">
-        <v>0.6590909090909091</v>
+        <v>0.65909090909090906</v>
       </c>
       <c r="M34">
-        <v>0.2666666666666667</v>
+        <v>0.26666666666666672</v>
       </c>
       <c r="N34">
-        <v>0.6411082474226804</v>
+        <v>0.64110824742268036</v>
       </c>
       <c r="O34">
-        <v>60.21505376344086</v>
+        <v>60.215053763440856</v>
       </c>
       <c r="P34">
-        <v>29.46236559139785</v>
+        <v>29.462365591397852</v>
       </c>
       <c r="Q34">
         <v>29.35483870967742</v>
@@ -2990,36 +2934,28 @@
       <c r="R34">
         <v>38.27956989247312</v>
       </c>
-      <c r="S34" t="inlineStr">
-        <is>
-          <t>DEP</t>
-        </is>
+      <c r="S34" t="s">
+        <v>57</v>
       </c>
       <c r="T34">
         <v>29.35483870967742</v>
       </c>
       <c r="U34">
-        <v>0.009999999999999898</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>LTR337_2022</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>LTR337</t>
-        </is>
+        <v>9.9999999999998979E-3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:21">
+      <c r="A35" t="s">
+        <v>98</v>
+      </c>
+      <c r="B35" t="s">
+        <v>96</v>
       </c>
       <c r="C35">
         <v>2022</v>
       </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>Svyla</t>
-        </is>
+      <c r="D35" t="s">
+        <v>97</v>
       </c>
       <c r="E35">
         <v>1</v>
@@ -3027,76 +2963,64 @@
       <c r="F35">
         <v>0.74</v>
       </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>Good</t>
-        </is>
+      <c r="G35" t="s">
+        <v>30</v>
       </c>
       <c r="H35">
         <v>0.75</v>
       </c>
       <c r="I35">
-        <v>0.7495145173453998</v>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>Good</t>
-        </is>
+        <v>0.74951451734539976</v>
+      </c>
+      <c r="J35" t="s">
+        <v>30</v>
       </c>
       <c r="K35">
-        <v>0.8333333333333334</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="L35">
-        <v>0.7156862745098039</v>
+        <v>0.71568627450980393</v>
       </c>
       <c r="M35">
         <v>0.8</v>
       </c>
       <c r="N35">
-        <v>0.6490384615384616</v>
+        <v>0.64903846153846156</v>
       </c>
       <c r="O35">
-        <v>82.20430107526882</v>
+        <v>82.204301075268816</v>
       </c>
       <c r="P35">
-        <v>42.74193548387097</v>
+        <v>42.741935483870968</v>
       </c>
       <c r="Q35">
-        <v>92.31182795698925</v>
+        <v>92.311827956989248</v>
       </c>
       <c r="R35">
-        <v>41.18279569892473</v>
-      </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>EHP-CrHi</t>
-        </is>
+        <v>41.182795698924728</v>
+      </c>
+      <c r="S35" t="s">
+        <v>26</v>
       </c>
       <c r="T35">
-        <v>41.18279569892473</v>
+        <v>41.182795698924728</v>
       </c>
       <c r="U35">
-        <v>-0.01000000000000001</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>LTR337_2016</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>LTR337</t>
-        </is>
+        <v>-1.0000000000000011E-2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:21">
+      <c r="A36" t="s">
+        <v>99</v>
+      </c>
+      <c r="B36" t="s">
+        <v>96</v>
       </c>
       <c r="C36">
         <v>2016</v>
       </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>Svyla</t>
-        </is>
+      <c r="D36" t="s">
+        <v>97</v>
       </c>
       <c r="E36">
         <v>1</v>
@@ -3104,76 +3028,64 @@
       <c r="F36">
         <v>0.78</v>
       </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>Good</t>
-        </is>
+      <c r="G36" t="s">
+        <v>30</v>
       </c>
       <c r="H36">
         <v>0.77</v>
       </c>
       <c r="I36">
-        <v>0.7728788177988415</v>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>Good</t>
-        </is>
+        <v>0.77287881779884149</v>
+      </c>
+      <c r="J36" t="s">
+        <v>30</v>
       </c>
       <c r="K36">
-        <v>0.8333333333333334</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="L36">
-        <v>0.7388888888888889</v>
+        <v>0.73888888888888893</v>
       </c>
       <c r="M36">
         <v>0.8</v>
       </c>
       <c r="N36">
-        <v>0.7192930489731437</v>
+        <v>0.71929304897314372</v>
       </c>
       <c r="O36">
-        <v>82.20430107526882</v>
+        <v>82.204301075268816</v>
       </c>
       <c r="P36">
-        <v>50.53763440860215</v>
+        <v>50.537634408602152</v>
       </c>
       <c r="Q36">
-        <v>92.31182795698925</v>
+        <v>92.311827956989248</v>
       </c>
       <c r="R36">
-        <v>65.59139784946237</v>
-      </c>
-      <c r="S36" t="inlineStr">
-        <is>
-          <t>ASPT</t>
-        </is>
+        <v>65.591397849462368</v>
+      </c>
+      <c r="S36" t="s">
+        <v>69</v>
       </c>
       <c r="T36">
-        <v>50.53763440860215</v>
+        <v>50.537634408602152</v>
       </c>
       <c r="U36">
-        <v>0.01000000000000001</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>LTR1687_2017</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>LTR1687</t>
-        </is>
+        <v>1.0000000000000011E-2</v>
+      </c>
+    </row>
+    <row r="37" spans="1:21">
+      <c r="A37" t="s">
+        <v>100</v>
+      </c>
+      <c r="B37" t="s">
+        <v>54</v>
       </c>
       <c r="C37">
         <v>2017</v>
       </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>Šalpė</t>
-        </is>
+      <c r="D37" t="s">
+        <v>55</v>
       </c>
       <c r="E37">
         <v>3</v>
@@ -3181,27 +3093,23 @@
       <c r="F37">
         <v>0.54</v>
       </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
+      <c r="G37" t="s">
+        <v>24</v>
       </c>
       <c r="H37">
         <v>0.53</v>
       </c>
       <c r="I37">
-        <v>0.5254807692307693</v>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
+        <v>0.52548076923076925</v>
+      </c>
+      <c r="J37" t="s">
+        <v>24</v>
       </c>
       <c r="K37">
         <v>0.5</v>
       </c>
       <c r="L37">
-        <v>0.576923076923077</v>
+        <v>0.57692307692307698</v>
       </c>
       <c r="M37">
         <v>0.4</v>
@@ -3210,47 +3118,39 @@
         <v>0.625</v>
       </c>
       <c r="O37">
-        <v>30.16129032258064</v>
+        <v>30.161290322580641</v>
       </c>
       <c r="P37">
         <v>13.33333333333333</v>
       </c>
       <c r="Q37">
-        <v>51.45161290322581</v>
+        <v>51.451612903225808</v>
       </c>
       <c r="R37">
-        <v>31.66666666666667</v>
-      </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t>ASPT</t>
-        </is>
+        <v>31.666666666666671</v>
+      </c>
+      <c r="S37" t="s">
+        <v>69</v>
       </c>
       <c r="T37">
         <v>13.33333333333333</v>
       </c>
       <c r="U37">
-        <v>0.01000000000000001</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>LTR297_2015</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>LTR297</t>
-        </is>
+        <v>1.0000000000000011E-2</v>
+      </c>
+    </row>
+    <row r="38" spans="1:21">
+      <c r="A38" t="s">
+        <v>101</v>
+      </c>
+      <c r="B38" t="s">
+        <v>59</v>
       </c>
       <c r="C38">
         <v>2015</v>
       </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>Lokysta</t>
-        </is>
+      <c r="D38" t="s">
+        <v>60</v>
       </c>
       <c r="E38">
         <v>3</v>
@@ -3258,33 +3158,29 @@
       <c r="F38">
         <v>0.36</v>
       </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>Poor</t>
-        </is>
+      <c r="G38" t="s">
+        <v>25</v>
       </c>
       <c r="H38">
         <v>0.35</v>
       </c>
       <c r="I38">
-        <v>0.3489071038251366</v>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>Poor</t>
-        </is>
+        <v>0.34890710382513662</v>
+      </c>
+      <c r="J38" t="s">
+        <v>25</v>
       </c>
       <c r="K38">
-        <v>0.3333333333333333</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="L38">
-        <v>0.4166666666666667</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="M38">
         <v>0.1333333333333333</v>
       </c>
       <c r="N38">
-        <v>0.5122950819672131</v>
+        <v>0.51229508196721307</v>
       </c>
       <c r="O38">
         <v>7.365591397849462</v>
@@ -3293,41 +3189,33 @@
         <v>1.290322580645161</v>
       </c>
       <c r="Q38">
-        <v>9.13978494623656</v>
+        <v>9.1397849462365599</v>
       </c>
       <c r="R38">
-        <v>9.24731182795699</v>
-      </c>
-      <c r="S38" t="inlineStr">
-        <is>
-          <t>ASPT</t>
-        </is>
+        <v>9.2473118279569899</v>
+      </c>
+      <c r="S38" t="s">
+        <v>69</v>
       </c>
       <c r="T38">
         <v>1.290322580645161</v>
       </c>
       <c r="U38">
-        <v>0.01000000000000001</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>LTR1488_2022</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>LTR1488</t>
-        </is>
+        <v>1.0000000000000011E-2</v>
+      </c>
+    </row>
+    <row r="39" spans="1:21">
+      <c r="A39" t="s">
+        <v>102</v>
+      </c>
+      <c r="B39" t="s">
+        <v>76</v>
       </c>
       <c r="C39">
         <v>2022</v>
       </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>Neris</t>
-        </is>
+      <c r="D39" t="s">
+        <v>77</v>
       </c>
       <c r="E39">
         <v>4</v>
@@ -3335,76 +3223,64 @@
       <c r="F39">
         <v>0.42</v>
       </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
+      <c r="G39" t="s">
+        <v>24</v>
       </c>
       <c r="H39">
         <v>0.41</v>
       </c>
       <c r="I39">
-        <v>0.4110129415719349</v>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
+        <v>0.41101294157193491</v>
+      </c>
+      <c r="J39" t="s">
+        <v>24</v>
       </c>
       <c r="K39">
-        <v>0.3333333333333333</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="L39">
-        <v>0.5864197530864197</v>
+        <v>0.58641975308641969</v>
       </c>
       <c r="M39">
         <v>0.1333333333333333</v>
       </c>
       <c r="N39">
-        <v>0.5909653465346534</v>
+        <v>0.59096534653465338</v>
       </c>
       <c r="O39">
         <v>7.365591397849462</v>
       </c>
       <c r="P39">
-        <v>14.73118279569892</v>
+        <v>14.731182795698921</v>
       </c>
       <c r="Q39">
-        <v>9.13978494623656</v>
+        <v>9.1397849462365599</v>
       </c>
       <c r="R39">
         <v>21.29032258064516</v>
       </c>
-      <c r="S39" t="inlineStr">
-        <is>
-          <t>DSFI</t>
-        </is>
+      <c r="S39" t="s">
+        <v>35</v>
       </c>
       <c r="T39">
         <v>7.365591397849462</v>
       </c>
       <c r="U39">
-        <v>0.01000000000000001</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>LTR1488_2019</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>LTR1488</t>
-        </is>
+        <v>1.0000000000000011E-2</v>
+      </c>
+    </row>
+    <row r="40" spans="1:21">
+      <c r="A40" t="s">
+        <v>103</v>
+      </c>
+      <c r="B40" t="s">
+        <v>76</v>
       </c>
       <c r="C40">
         <v>2019</v>
       </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>Neris</t>
-        </is>
+      <c r="D40" t="s">
+        <v>77</v>
       </c>
       <c r="E40">
         <v>4</v>
@@ -3412,76 +3288,64 @@
       <c r="F40">
         <v>0.51</v>
       </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
+      <c r="G40" t="s">
+        <v>24</v>
       </c>
       <c r="H40">
         <v>0.52</v>
       </c>
       <c r="I40">
-        <v>0.5208137064745544</v>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
+        <v>0.52081370647455438</v>
+      </c>
+      <c r="J40" t="s">
+        <v>24</v>
       </c>
       <c r="K40">
         <v>0.5</v>
       </c>
       <c r="L40">
-        <v>0.7037037037037037</v>
+        <v>0.70370370370370372</v>
       </c>
       <c r="M40">
         <v>0.2</v>
       </c>
       <c r="N40">
-        <v>0.6795511221945136</v>
+        <v>0.67955112219451363</v>
       </c>
       <c r="O40">
-        <v>30.16129032258064</v>
+        <v>30.161290322580641</v>
       </c>
       <c r="P40">
-        <v>39.46236559139785</v>
+        <v>39.462365591397848</v>
       </c>
       <c r="Q40">
         <v>18.44086021505376</v>
       </c>
       <c r="R40">
-        <v>52.25806451612903</v>
-      </c>
-      <c r="S40" t="inlineStr">
-        <is>
-          <t>DEP</t>
-        </is>
+        <v>52.258064516129032</v>
+      </c>
+      <c r="S40" t="s">
+        <v>57</v>
       </c>
       <c r="T40">
         <v>18.44086021505376</v>
       </c>
       <c r="U40">
-        <v>-0.01000000000000001</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>LTR1501_2016</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>LTR1501</t>
-        </is>
+        <v>-1.0000000000000011E-2</v>
+      </c>
+    </row>
+    <row r="41" spans="1:21">
+      <c r="A41" t="s">
+        <v>104</v>
+      </c>
+      <c r="B41" t="s">
+        <v>105</v>
       </c>
       <c r="C41">
         <v>2016</v>
       </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>Mūša</t>
-        </is>
+      <c r="D41" t="s">
+        <v>23</v>
       </c>
       <c r="E41">
         <v>4</v>
@@ -3489,10 +3353,8 @@
       <c r="F41">
         <v>0.46</v>
       </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
+      <c r="G41" t="s">
+        <v>24</v>
       </c>
       <c r="H41">
         <v>0.45</v>
@@ -3500,65 +3362,55 @@
       <c r="I41">
         <v>0.449387600616866</v>
       </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
+      <c r="J41" t="s">
+        <v>24</v>
       </c>
       <c r="K41">
         <v>0.5</v>
       </c>
       <c r="L41">
-        <v>0.753968253968254</v>
+        <v>0.75396825396825395</v>
       </c>
       <c r="M41">
         <v>0.1333333333333333</v>
       </c>
       <c r="N41">
-        <v>0.4102488151658767</v>
+        <v>0.41024881516587669</v>
       </c>
       <c r="O41">
-        <v>30.16129032258064</v>
+        <v>30.161290322580641</v>
       </c>
       <c r="P41">
-        <v>55.96774193548387</v>
+        <v>55.967741935483872</v>
       </c>
       <c r="Q41">
-        <v>9.13978494623656</v>
+        <v>9.1397849462365599</v>
       </c>
       <c r="R41">
         <v>3.978494623655914</v>
       </c>
-      <c r="S41" t="inlineStr">
-        <is>
-          <t>EHP-CrHi</t>
-        </is>
+      <c r="S41" t="s">
+        <v>26</v>
       </c>
       <c r="T41">
         <v>3.978494623655914</v>
       </c>
       <c r="U41">
-        <v>0.01000000000000001</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>LTR1447_2022</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>LTR1447</t>
-        </is>
+        <v>1.0000000000000011E-2</v>
+      </c>
+    </row>
+    <row r="42" spans="1:21">
+      <c r="A42" t="s">
+        <v>106</v>
+      </c>
+      <c r="B42" t="s">
+        <v>62</v>
       </c>
       <c r="C42">
         <v>2022</v>
       </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>Merkys</t>
-        </is>
+      <c r="D42" t="s">
+        <v>63</v>
       </c>
       <c r="E42">
         <v>5</v>
@@ -3566,76 +3418,64 @@
       <c r="F42">
         <v>0.78</v>
       </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>Good</t>
-        </is>
+      <c r="G42" t="s">
+        <v>30</v>
       </c>
       <c r="H42">
         <v>0.77</v>
       </c>
       <c r="I42">
-        <v>0.7733717781467425</v>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>Good</t>
-        </is>
+        <v>0.77337177814674252</v>
+      </c>
+      <c r="J42" t="s">
+        <v>30</v>
       </c>
       <c r="K42">
-        <v>0.6666666666666666</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="L42">
-        <v>0.7843137254901961</v>
+        <v>0.78431372549019607</v>
       </c>
       <c r="M42">
         <v>0.6</v>
       </c>
       <c r="N42">
-        <v>1.042506720430108</v>
+        <v>1.0425067204301079</v>
       </c>
       <c r="O42">
-        <v>60.21505376344086</v>
+        <v>60.215053763440856</v>
       </c>
       <c r="P42">
-        <v>66.18279569892474</v>
+        <v>66.182795698924735</v>
       </c>
       <c r="Q42">
-        <v>77.68817204301075</v>
+        <v>77.688172043010752</v>
       </c>
       <c r="R42">
-        <v>99.24731182795699</v>
-      </c>
-      <c r="S42" t="inlineStr">
-        <is>
-          <t>DSFI</t>
-        </is>
+        <v>99.247311827956992</v>
+      </c>
+      <c r="S42" t="s">
+        <v>35</v>
       </c>
       <c r="T42">
-        <v>60.21505376344086</v>
+        <v>60.215053763440856</v>
       </c>
       <c r="U42">
-        <v>0.01000000000000001</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>LTR1492_2016</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>LTR1492</t>
-        </is>
+        <v>1.0000000000000011E-2</v>
+      </c>
+    </row>
+    <row r="43" spans="1:21">
+      <c r="A43" t="s">
+        <v>107</v>
+      </c>
+      <c r="B43" t="s">
+        <v>22</v>
       </c>
       <c r="C43">
         <v>2016</v>
       </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>Mūša</t>
-        </is>
+      <c r="D43" t="s">
+        <v>23</v>
       </c>
       <c r="E43">
         <v>5</v>
@@ -3643,113 +3483,97 @@
       <c r="F43">
         <v>0.45</v>
       </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
+      <c r="G43" t="s">
+        <v>24</v>
       </c>
       <c r="H43">
         <v>0.44</v>
       </c>
       <c r="I43">
-        <v>0.4446645509145509</v>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
+        <v>0.44466455091455093</v>
+      </c>
+      <c r="J43" t="s">
+        <v>24</v>
       </c>
       <c r="K43">
-        <v>0.3333333333333333</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="L43">
-        <v>0.6111111111111112</v>
+        <v>0.61111111111111116</v>
       </c>
       <c r="M43">
         <v>0.2</v>
       </c>
       <c r="N43">
-        <v>0.6342137592137592</v>
+        <v>0.63421375921375922</v>
       </c>
       <c r="O43">
         <v>7.365591397849462</v>
       </c>
       <c r="P43">
-        <v>19.24731182795699</v>
+        <v>19.247311827956992</v>
       </c>
       <c r="Q43">
         <v>18.44086021505376</v>
       </c>
       <c r="R43">
-        <v>35.05376344086022</v>
-      </c>
-      <c r="S43" t="inlineStr">
-        <is>
-          <t>DSFI</t>
-        </is>
+        <v>35.053763440860223</v>
+      </c>
+      <c r="S43" t="s">
+        <v>35</v>
       </c>
       <c r="T43">
         <v>7.365591397849462</v>
       </c>
       <c r="U43">
-        <v>0.01000000000000001</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>LTR1502_2019</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>LTR1502</t>
-        </is>
+        <v>1.0000000000000011E-2</v>
+      </c>
+    </row>
+    <row r="44" spans="1:21">
+      <c r="A44" t="s">
+        <v>108</v>
+      </c>
+      <c r="B44" t="s">
+        <v>93</v>
       </c>
       <c r="C44">
         <v>2019</v>
       </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>Lėvuo</t>
-        </is>
+      <c r="D44" t="s">
+        <v>94</v>
       </c>
       <c r="E44">
         <v>5</v>
       </c>
       <c r="F44">
-        <v>0.57</v>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="G44" t="s">
+        <v>24</v>
       </c>
       <c r="H44">
-        <v>0.5600000000000001</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="I44">
-        <v>0.558179012345679</v>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
+        <v>0.55817901234567902</v>
+      </c>
+      <c r="J44" t="s">
+        <v>24</v>
       </c>
       <c r="K44">
-        <v>0.6666666666666666</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="L44">
-        <v>0.6666666666666666</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="M44">
-        <v>0.2666666666666667</v>
+        <v>0.26666666666666672</v>
       </c>
       <c r="N44">
-        <v>0.6327160493827161</v>
+        <v>0.63271604938271608</v>
       </c>
       <c r="O44">
-        <v>60.21505376344086</v>
+        <v>60.215053763440856</v>
       </c>
       <c r="P44">
         <v>31.12903225806452</v>
@@ -3758,38 +3582,30 @@
         <v>29.35483870967742</v>
       </c>
       <c r="R44">
-        <v>34.30107526881721</v>
-      </c>
-      <c r="S44" t="inlineStr">
-        <is>
-          <t>DEP</t>
-        </is>
+        <v>34.301075268817208</v>
+      </c>
+      <c r="S44" t="s">
+        <v>57</v>
       </c>
       <c r="T44">
         <v>29.35483870967742</v>
       </c>
       <c r="U44">
-        <v>0.009999999999999898</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>LTR351_2019</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>LTR351</t>
-        </is>
+        <v>9.9999999999998979E-3</v>
+      </c>
+    </row>
+    <row r="45" spans="1:21">
+      <c r="A45" t="s">
+        <v>109</v>
+      </c>
+      <c r="B45" t="s">
+        <v>110</v>
       </c>
       <c r="C45">
         <v>2019</v>
       </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>Šventoji</t>
-        </is>
+      <c r="D45" t="s">
+        <v>111</v>
       </c>
       <c r="E45">
         <v>5</v>
@@ -3797,21 +3613,17 @@
       <c r="F45">
         <v>0.54</v>
       </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
+      <c r="G45" t="s">
+        <v>24</v>
       </c>
       <c r="H45">
         <v>0.53</v>
       </c>
       <c r="I45">
-        <v>0.5345474332881049</v>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
+        <v>0.53454743328810495</v>
+      </c>
+      <c r="J45" t="s">
+        <v>24</v>
       </c>
       <c r="K45">
         <v>0.5</v>
@@ -3820,53 +3632,45 @@
         <v>0.7045454545454547</v>
       </c>
       <c r="M45">
-        <v>0.2666666666666667</v>
+        <v>0.26666666666666672</v>
       </c>
       <c r="N45">
-        <v>0.6669776119402985</v>
+        <v>0.66697761194029848</v>
       </c>
       <c r="O45">
-        <v>30.16129032258064</v>
+        <v>30.161290322580641</v>
       </c>
       <c r="P45">
-        <v>39.89247311827957</v>
+        <v>39.892473118279568</v>
       </c>
       <c r="Q45">
         <v>29.35483870967742</v>
       </c>
       <c r="R45">
-        <v>47.31182795698925</v>
-      </c>
-      <c r="S45" t="inlineStr">
-        <is>
-          <t>DEP</t>
-        </is>
+        <v>47.311827956989248</v>
+      </c>
+      <c r="S45" t="s">
+        <v>57</v>
       </c>
       <c r="T45">
         <v>29.35483870967742</v>
       </c>
       <c r="U45">
-        <v>0.01000000000000001</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>LTR411_2022</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>LTR411</t>
-        </is>
+        <v>1.0000000000000011E-2</v>
+      </c>
+    </row>
+    <row r="46" spans="1:21">
+      <c r="A46" t="s">
+        <v>112</v>
+      </c>
+      <c r="B46" t="s">
+        <v>113</v>
       </c>
       <c r="C46">
         <v>2022</v>
       </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>Šešupė</t>
-        </is>
+      <c r="D46" t="s">
+        <v>114</v>
       </c>
       <c r="E46">
         <v>5</v>
@@ -3874,76 +3678,64 @@
       <c r="F46">
         <v>0.75</v>
       </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>Good</t>
-        </is>
+      <c r="G46" t="s">
+        <v>30</v>
       </c>
       <c r="H46">
         <v>0.74</v>
       </c>
       <c r="I46">
-        <v>0.7419112685560054</v>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>Good</t>
-        </is>
+        <v>0.74191126855600542</v>
+      </c>
+      <c r="J46" t="s">
+        <v>30</v>
       </c>
       <c r="K46">
-        <v>0.6666666666666666</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="L46">
-        <v>0.8461538461538461</v>
+        <v>0.84615384615384615</v>
       </c>
       <c r="M46">
-        <v>0.7333333333333333</v>
+        <v>0.73333333333333328</v>
       </c>
       <c r="N46">
-        <v>0.7214912280701754</v>
+        <v>0.72149122807017541</v>
       </c>
       <c r="O46">
-        <v>60.21505376344086</v>
+        <v>60.215053763440856</v>
       </c>
       <c r="P46">
-        <v>82.47311827956989</v>
+        <v>82.473118279569889</v>
       </c>
       <c r="Q46">
-        <v>87.84946236559139</v>
+        <v>87.849462365591393</v>
       </c>
       <c r="R46">
-        <v>66.23655913978494</v>
-      </c>
-      <c r="S46" t="inlineStr">
-        <is>
-          <t>DSFI</t>
-        </is>
+        <v>66.236559139784944</v>
+      </c>
+      <c r="S46" t="s">
+        <v>35</v>
       </c>
       <c r="T46">
-        <v>60.21505376344086</v>
+        <v>60.215053763440856</v>
       </c>
       <c r="U46">
-        <v>0.01000000000000001</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>LTR86_2016</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>LTR86</t>
-        </is>
+        <v>1.0000000000000011E-2</v>
+      </c>
+    </row>
+    <row r="47" spans="1:21">
+      <c r="A47" t="s">
+        <v>115</v>
+      </c>
+      <c r="B47" t="s">
+        <v>65</v>
       </c>
       <c r="C47">
         <v>2016</v>
       </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>Mūša</t>
-        </is>
+      <c r="D47" t="s">
+        <v>23</v>
       </c>
       <c r="E47">
         <v>5</v>
@@ -3951,56 +3743,50 @@
       <c r="F47">
         <v>0.48</v>
       </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
+      <c r="G47" t="s">
+        <v>24</v>
       </c>
       <c r="H47">
         <v>0.5</v>
       </c>
       <c r="I47">
-        <v>0.4994946322521699</v>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
+        <v>0.49949463225216989</v>
+      </c>
+      <c r="J47" t="s">
+        <v>24</v>
       </c>
       <c r="K47">
         <v>0.5</v>
       </c>
       <c r="L47">
-        <v>0.6893939393939394</v>
+        <v>0.68939393939393945</v>
       </c>
       <c r="M47">
         <v>0.1333333333333333</v>
       </c>
       <c r="N47">
-        <v>0.6752512562814069</v>
+        <v>0.67525125628140692</v>
       </c>
       <c r="O47">
-        <v>30.16129032258064</v>
+        <v>30.161290322580641</v>
       </c>
       <c r="P47">
-        <v>35.64516129032258</v>
+        <v>35.645161290322577</v>
       </c>
       <c r="Q47">
-        <v>9.13978494623656</v>
+        <v>9.1397849462365599</v>
       </c>
       <c r="R47">
-        <v>50.21505376344086</v>
-      </c>
-      <c r="S47" t="inlineStr">
-        <is>
-          <t>DEP</t>
-        </is>
+        <v>50.215053763440856</v>
+      </c>
+      <c r="S47" t="s">
+        <v>57</v>
       </c>
       <c r="T47">
-        <v>9.13978494623656</v>
+        <v>9.1397849462365599</v>
       </c>
       <c r="U47">
-        <v>-0.02000000000000002</v>
+        <v>-2.0000000000000021E-2</v>
       </c>
     </row>
   </sheetData>

--- a/Outputs/9_per_metric_diagnostic.xlsx
+++ b/Outputs/9_per_metric_diagnostic.xlsx
@@ -1,390 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30203"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_F21D1DDD8F79A8D366075C52F37BD272AAC41930" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191028"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="116">
-  <si>
-    <t>site_code</t>
-  </si>
-  <si>
-    <t>site_id</t>
-  </si>
-  <si>
-    <t>year</t>
-  </si>
-  <si>
-    <t>waterbody_name</t>
-  </si>
-  <si>
-    <t>river_type</t>
-  </si>
-  <si>
-    <t>EQR</t>
-  </si>
-  <si>
-    <t>EQC</t>
-  </si>
-  <si>
-    <t>LRMI</t>
-  </si>
-  <si>
-    <t>LRMI_raw</t>
-  </si>
-  <si>
-    <t>LRMI_class</t>
-  </si>
-  <si>
-    <t>DSFI_EQR</t>
-  </si>
-  <si>
-    <t>ASPT_EQR</t>
-  </si>
-  <si>
-    <t>DEP_EQR</t>
-  </si>
-  <si>
-    <t>EHP_minus_CrHi_EQR</t>
-  </si>
-  <si>
-    <t>DSFI_pct</t>
-  </si>
-  <si>
-    <t>ASPT_pct</t>
-  </si>
-  <si>
-    <t>DEP_pct</t>
-  </si>
-  <si>
-    <t>EHP_minus_CrHi_pct</t>
-  </si>
-  <si>
-    <t>lowest_metric</t>
-  </si>
-  <si>
-    <t>lowest_pct</t>
-  </si>
-  <si>
-    <t>residual</t>
-  </si>
-  <si>
-    <t>LTR1492_2022</t>
-  </si>
-  <si>
-    <t>LTR1492</t>
-  </si>
-  <si>
-    <t>Mūša</t>
-  </si>
-  <si>
-    <t>Moderate</t>
-  </si>
-  <si>
-    <t>Poor</t>
-  </si>
-  <si>
-    <t>EHP-CrHi</t>
-  </si>
-  <si>
-    <t>LTR163_2019</t>
-  </si>
-  <si>
-    <t>LTR163</t>
-  </si>
-  <si>
-    <t>Geluža</t>
-  </si>
-  <si>
-    <t>Good</t>
-  </si>
-  <si>
-    <t>LTR127_2015</t>
-  </si>
-  <si>
-    <t>LTR127</t>
-  </si>
-  <si>
-    <t>Skirvytė</t>
-  </si>
-  <si>
-    <t>Bad</t>
-  </si>
-  <si>
-    <t>DSFI</t>
-  </si>
-  <si>
-    <t>LTR386_2019</t>
-  </si>
-  <si>
-    <t>LTR386</t>
-  </si>
-  <si>
-    <t>Viešinta</t>
-  </si>
-  <si>
-    <t>LTR1466_2019</t>
-  </si>
-  <si>
-    <t>LTR1466</t>
-  </si>
-  <si>
-    <t>Įpiltis</t>
-  </si>
-  <si>
-    <t>High</t>
-  </si>
-  <si>
-    <t>LTR163_2022</t>
-  </si>
-  <si>
-    <t>LTR450_2015</t>
-  </si>
-  <si>
-    <t>LTR450</t>
-  </si>
-  <si>
-    <t>Ringuva</t>
-  </si>
-  <si>
-    <t>LTR127_2017</t>
-  </si>
-  <si>
-    <t>LTR127_2020</t>
-  </si>
-  <si>
-    <t>LTR625_2022</t>
-  </si>
-  <si>
-    <t>LTR625</t>
-  </si>
-  <si>
-    <t>Luoba</t>
-  </si>
-  <si>
-    <t>LTR1466_2016</t>
-  </si>
-  <si>
-    <t>LTR1687_2016</t>
-  </si>
-  <si>
-    <t>LTR1687</t>
-  </si>
-  <si>
-    <t>Šalpė</t>
-  </si>
-  <si>
-    <t>LTR1687_2022</t>
-  </si>
-  <si>
-    <t>DEP</t>
-  </si>
-  <si>
-    <t>LTR297_2021</t>
-  </si>
-  <si>
-    <t>LTR297</t>
-  </si>
-  <si>
-    <t>Lokysta</t>
-  </si>
-  <si>
-    <t>LTR1447_2015</t>
-  </si>
-  <si>
-    <t>LTR1447</t>
-  </si>
-  <si>
-    <t>Merkys</t>
-  </si>
-  <si>
-    <t>LTR86_2015</t>
-  </si>
-  <si>
-    <t>LTR86</t>
-  </si>
-  <si>
-    <t>LTR1461_2022</t>
-  </si>
-  <si>
-    <t>LTR1461</t>
-  </si>
-  <si>
-    <t>Nemunėlis</t>
-  </si>
-  <si>
-    <t>ASPT</t>
-  </si>
-  <si>
-    <t>LTR1461_2016</t>
-  </si>
-  <si>
-    <t>LTR1461_2019</t>
-  </si>
-  <si>
-    <t>LTR1466_2022</t>
-  </si>
-  <si>
-    <t>LTR386_2016</t>
-  </si>
-  <si>
-    <t>LTR386_2022</t>
-  </si>
-  <si>
-    <t>LTR1488_2015</t>
-  </si>
-  <si>
-    <t>LTR1488</t>
-  </si>
-  <si>
-    <t>Neris</t>
-  </si>
-  <si>
-    <t>LTR1063_2021</t>
-  </si>
-  <si>
-    <t>LTR1063</t>
-  </si>
-  <si>
-    <t>PentaII</t>
-  </si>
-  <si>
-    <t>LTR163_2016</t>
-  </si>
-  <si>
-    <t>LTR308_2018</t>
-  </si>
-  <si>
-    <t>LTR308</t>
-  </si>
-  <si>
-    <t>Eketė</t>
-  </si>
-  <si>
-    <t>LTR450_2020</t>
-  </si>
-  <si>
-    <t>LTR297_2018</t>
-  </si>
-  <si>
-    <t>LTR706_2015</t>
-  </si>
-  <si>
-    <t>LTR706</t>
-  </si>
-  <si>
-    <t>Liaudė</t>
-  </si>
-  <si>
-    <t>LTR1488_2016</t>
-  </si>
-  <si>
-    <t>LTR1492_2019</t>
-  </si>
-  <si>
-    <t>LTR1502_2015</t>
-  </si>
-  <si>
-    <t>LTR1502</t>
-  </si>
-  <si>
-    <t>Lėvuo</t>
-  </si>
-  <si>
-    <t>LTR337_2019</t>
-  </si>
-  <si>
-    <t>LTR337</t>
-  </si>
-  <si>
-    <t>Svyla</t>
-  </si>
-  <si>
-    <t>LTR337_2022</t>
-  </si>
-  <si>
-    <t>LTR337_2016</t>
-  </si>
-  <si>
-    <t>LTR1687_2017</t>
-  </si>
-  <si>
-    <t>LTR297_2015</t>
-  </si>
-  <si>
-    <t>LTR1488_2022</t>
-  </si>
-  <si>
-    <t>LTR1488_2019</t>
-  </si>
-  <si>
-    <t>LTR1501_2016</t>
-  </si>
-  <si>
-    <t>LTR1501</t>
-  </si>
-  <si>
-    <t>LTR1447_2022</t>
-  </si>
-  <si>
-    <t>LTR1492_2016</t>
-  </si>
-  <si>
-    <t>LTR1502_2019</t>
-  </si>
-  <si>
-    <t>LTR351_2019</t>
-  </si>
-  <si>
-    <t>LTR351</t>
-  </si>
-  <si>
-    <t>Šventoji</t>
-  </si>
-  <si>
-    <t>LTR411_2022</t>
-  </si>
-  <si>
-    <t>LTR411</t>
-  </si>
-  <si>
-    <t>Šešupė</t>
-  </si>
-  <si>
-    <t>LTR86_2016</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <fonts count="2">
     <font>
       <sz val="11"/>
@@ -429,25 +59,17 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Įprastas" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -485,7 +107,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -519,7 +141,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -554,10 +175,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -730,87 +350,135 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:U47"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:21" s="1" customFormat="1">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="2" spans="1:21">
-      <c r="A2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B2" t="s">
-        <v>22</v>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>site_code</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>site_id</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>year</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>waterbody_name</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>river_type</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>EQR</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>EQC</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>LRMI</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>LRMI_raw</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>LRMI_class</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>DSFI_EQR</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ASPT_EQR</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>DEP_EQR</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>EHP_minus_CrHi_EQR</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>DSFI_pct</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>ASPT_pct</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>DEP_pct</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>EHP_minus_CrHi_pct</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>lowest_metric</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>lowest_pct</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>residual</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>LTR1492_2022</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>LTR1492</t>
+        </is>
       </c>
       <c r="C2">
         <v>2022</v>
       </c>
-      <c r="D2" t="s">
-        <v>23</v>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Mūša</t>
+        </is>
       </c>
       <c r="E2">
         <v>5</v>
@@ -818,44 +486,50 @@
       <c r="F2">
         <v>0.5</v>
       </c>
-      <c r="G2" t="s">
-        <v>24</v>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
       </c>
       <c r="H2">
         <v>0.39</v>
       </c>
       <c r="I2">
-        <v>0.39320913461538459</v>
-      </c>
-      <c r="J2" t="s">
-        <v>25</v>
+        <v>0.3932091346153846</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
       </c>
       <c r="K2">
         <v>0.5</v>
       </c>
       <c r="L2">
-        <v>0.72916666666666663</v>
+        <v>0.7291666666666666</v>
       </c>
       <c r="M2">
         <v>0.1333333333333333</v>
       </c>
       <c r="N2">
-        <v>0.21033653846153849</v>
+        <v>0.2103365384615385</v>
       </c>
       <c r="O2">
-        <v>30.161290322580641</v>
+        <v>30.16129032258064</v>
       </c>
       <c r="P2">
-        <v>47.526881720430097</v>
+        <v>47.5268817204301</v>
       </c>
       <c r="Q2">
-        <v>9.1397849462365599</v>
+        <v>9.13978494623656</v>
       </c>
       <c r="R2">
         <v>0.967741935483871</v>
       </c>
-      <c r="S2" t="s">
-        <v>26</v>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>EHP-CrHi</t>
+        </is>
       </c>
       <c r="T2">
         <v>0.967741935483871</v>
@@ -864,18 +538,24 @@
         <v>0.11</v>
       </c>
     </row>
-    <row r="3" spans="1:21">
-      <c r="A3" t="s">
-        <v>27</v>
-      </c>
-      <c r="B3" t="s">
-        <v>28</v>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>LTR163_2019</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>LTR163</t>
+        </is>
       </c>
       <c r="C3">
         <v>2019</v>
       </c>
-      <c r="D3" t="s">
-        <v>29</v>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Geluža</t>
+        </is>
       </c>
       <c r="E3">
         <v>1</v>
@@ -883,64 +563,76 @@
       <c r="F3">
         <v>0.68</v>
       </c>
-      <c r="G3" t="s">
-        <v>30</v>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
       </c>
       <c r="H3">
         <v>0.6</v>
       </c>
       <c r="I3">
-        <v>0.60109035215839013</v>
-      </c>
-      <c r="J3" t="s">
-        <v>30</v>
+        <v>0.6010903521583901</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
       </c>
       <c r="K3">
-        <v>0.83333333333333337</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="L3">
-        <v>0.78205128205128227</v>
+        <v>0.7820512820512823</v>
       </c>
       <c r="M3">
         <v>0.4</v>
       </c>
       <c r="N3">
-        <v>0.38897679324894507</v>
+        <v>0.3889767932489451</v>
       </c>
       <c r="O3">
-        <v>82.204301075268816</v>
+        <v>82.20430107526882</v>
       </c>
       <c r="P3">
-        <v>65.483870967741936</v>
+        <v>65.48387096774194</v>
       </c>
       <c r="Q3">
-        <v>51.451612903225808</v>
+        <v>51.45161290322581</v>
       </c>
       <c r="R3">
         <v>3.225806451612903</v>
       </c>
-      <c r="S3" t="s">
-        <v>26</v>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>EHP-CrHi</t>
+        </is>
       </c>
       <c r="T3">
         <v>3.225806451612903</v>
       </c>
       <c r="U3">
-        <v>8.0000000000000071E-2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:21">
-      <c r="A4" t="s">
-        <v>31</v>
-      </c>
-      <c r="B4" t="s">
-        <v>32</v>
+        <v>0.08000000000000007</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>LTR127_2015</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>LTR127</t>
+        </is>
       </c>
       <c r="C4">
         <v>2015</v>
       </c>
-      <c r="D4" t="s">
-        <v>33</v>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Skirvytė</t>
+        </is>
       </c>
       <c r="E4">
         <v>4</v>
@@ -948,8 +640,10 @@
       <c r="F4">
         <v>0.31</v>
       </c>
-      <c r="G4" t="s">
-        <v>25</v>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
       </c>
       <c r="H4">
         <v>0.25</v>
@@ -957,23 +651,25 @@
       <c r="I4">
         <v>0.2467859633393106</v>
       </c>
-      <c r="J4" t="s">
-        <v>34</v>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Bad</t>
+        </is>
       </c>
       <c r="K4">
         <v>0</v>
       </c>
       <c r="L4">
-        <v>0.45238095238095227</v>
+        <v>0.4523809523809523</v>
       </c>
       <c r="M4">
-        <v>6.6666666666666666E-2</v>
+        <v>0.06666666666666667</v>
       </c>
       <c r="N4">
-        <v>0.46809623430962338</v>
+        <v>0.4680962343096234</v>
       </c>
       <c r="O4">
-        <v>0.26881720430107531</v>
+        <v>0.2688172043010753</v>
       </c>
       <c r="P4">
         <v>2.903225806451613</v>
@@ -984,28 +680,36 @@
       <c r="R4">
         <v>5.913978494623656</v>
       </c>
-      <c r="S4" t="s">
-        <v>35</v>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>DSFI</t>
+        </is>
       </c>
       <c r="T4">
-        <v>0.26881720430107531</v>
+        <v>0.2688172043010753</v>
       </c>
       <c r="U4">
         <v>0.06</v>
       </c>
     </row>
-    <row r="5" spans="1:21">
-      <c r="A5" t="s">
-        <v>36</v>
-      </c>
-      <c r="B5" t="s">
-        <v>37</v>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>LTR386_2019</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>LTR386</t>
+        </is>
       </c>
       <c r="C5">
         <v>2019</v>
       </c>
-      <c r="D5" t="s">
-        <v>38</v>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Viešinta</t>
+        </is>
       </c>
       <c r="E5">
         <v>1</v>
@@ -1013,64 +717,76 @@
       <c r="F5">
         <v>0.66</v>
       </c>
-      <c r="G5" t="s">
-        <v>30</v>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
       </c>
       <c r="H5">
         <v>0.59</v>
       </c>
       <c r="I5">
-        <v>0.59145843155744149</v>
-      </c>
-      <c r="J5" t="s">
-        <v>24</v>
+        <v>0.5914584315574415</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
       </c>
       <c r="K5">
         <v>0.5</v>
       </c>
       <c r="L5">
-        <v>0.74603174603174605</v>
+        <v>0.746031746031746</v>
       </c>
       <c r="M5">
         <v>0.6</v>
       </c>
       <c r="N5">
-        <v>0.51980198019801982</v>
+        <v>0.5198019801980198</v>
       </c>
       <c r="O5">
-        <v>30.161290322580641</v>
+        <v>30.16129032258064</v>
       </c>
       <c r="P5">
-        <v>52.903225806451623</v>
+        <v>52.90322580645162</v>
       </c>
       <c r="Q5">
-        <v>77.688172043010752</v>
+        <v>77.68817204301075</v>
       </c>
       <c r="R5">
         <v>9.89247311827957</v>
       </c>
-      <c r="S5" t="s">
-        <v>26</v>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>EHP-CrHi</t>
+        </is>
       </c>
       <c r="T5">
         <v>9.89247311827957</v>
       </c>
       <c r="U5">
-        <v>7.0000000000000062E-2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:21">
-      <c r="A6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B6" t="s">
-        <v>40</v>
+        <v>0.07000000000000006</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>LTR1466_2019</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>LTR1466</t>
+        </is>
       </c>
       <c r="C6">
         <v>2019</v>
       </c>
-      <c r="D6" t="s">
-        <v>41</v>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Įpiltis</t>
+        </is>
       </c>
       <c r="E6">
         <v>3</v>
@@ -1078,64 +794,76 @@
       <c r="F6">
         <v>0.83</v>
       </c>
-      <c r="G6" t="s">
-        <v>42</v>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
       </c>
       <c r="H6">
         <v>0.77</v>
       </c>
       <c r="I6">
-        <v>0.77233265947888596</v>
-      </c>
-      <c r="J6" t="s">
-        <v>30</v>
+        <v>0.772332659478886</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
       </c>
       <c r="K6">
-        <v>0.83333333333333337</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="L6">
-        <v>0.72023809523809523</v>
+        <v>0.7202380952380952</v>
       </c>
       <c r="M6">
-        <v>0.93333333333333335</v>
+        <v>0.9333333333333333</v>
       </c>
       <c r="N6">
-        <v>0.60242587601078168</v>
+        <v>0.6024258760107817</v>
       </c>
       <c r="O6">
-        <v>82.204301075268816</v>
+        <v>82.20430107526882</v>
       </c>
       <c r="P6">
         <v>44.56989247311828</v>
       </c>
       <c r="Q6">
-        <v>96.935483870967744</v>
+        <v>96.93548387096774</v>
       </c>
       <c r="R6">
-        <v>23.333333333333329</v>
-      </c>
-      <c r="S6" t="s">
-        <v>26</v>
+        <v>23.33333333333333</v>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>EHP-CrHi</t>
+        </is>
       </c>
       <c r="T6">
-        <v>23.333333333333329</v>
+        <v>23.33333333333333</v>
       </c>
       <c r="U6">
-        <v>5.9999999999999942E-2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:21">
-      <c r="A7" t="s">
-        <v>43</v>
-      </c>
-      <c r="B7" t="s">
-        <v>28</v>
+        <v>0.05999999999999994</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>LTR163_2022</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>LTR163</t>
+        </is>
       </c>
       <c r="C7">
         <v>2022</v>
       </c>
-      <c r="D7" t="s">
-        <v>29</v>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Geluža</t>
+        </is>
       </c>
       <c r="E7">
         <v>1</v>
@@ -1143,64 +871,76 @@
       <c r="F7">
         <v>0.79</v>
       </c>
-      <c r="G7" t="s">
-        <v>30</v>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
       </c>
       <c r="H7">
         <v>0.73</v>
       </c>
       <c r="I7">
-        <v>0.72734465991148378</v>
-      </c>
-      <c r="J7" t="s">
-        <v>30</v>
+        <v>0.7273446599114838</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
       </c>
       <c r="K7">
-        <v>0.83333333333333337</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="L7">
-        <v>0.76543209876543206</v>
+        <v>0.7654320987654321</v>
       </c>
       <c r="M7">
         <v>0.8</v>
       </c>
       <c r="N7">
-        <v>0.51061320754716977</v>
+        <v>0.5106132075471698</v>
       </c>
       <c r="O7">
-        <v>82.204301075268816</v>
+        <v>82.20430107526882</v>
       </c>
       <c r="P7">
-        <v>59.784946236559144</v>
+        <v>59.78494623655914</v>
       </c>
       <c r="Q7">
-        <v>92.311827956989248</v>
+        <v>92.31182795698925</v>
       </c>
       <c r="R7">
-        <v>9.0322580645161299</v>
-      </c>
-      <c r="S7" t="s">
-        <v>26</v>
+        <v>9.03225806451613</v>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>EHP-CrHi</t>
+        </is>
       </c>
       <c r="T7">
-        <v>9.0322580645161299</v>
+        <v>9.03225806451613</v>
       </c>
       <c r="U7">
-        <v>6.0000000000000053E-2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:21">
-      <c r="A8" t="s">
-        <v>44</v>
-      </c>
-      <c r="B8" t="s">
-        <v>45</v>
+        <v>0.06000000000000005</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>LTR450_2015</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>LTR450</t>
+        </is>
       </c>
       <c r="C8">
         <v>2015</v>
       </c>
-      <c r="D8" t="s">
-        <v>46</v>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Ringuva</t>
+        </is>
       </c>
       <c r="E8">
         <v>2</v>
@@ -1208,29 +948,33 @@
       <c r="F8">
         <v>0.38</v>
       </c>
-      <c r="G8" t="s">
-        <v>25</v>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
       </c>
       <c r="H8">
         <v>0.32</v>
       </c>
       <c r="I8">
-        <v>0.31767453294001968</v>
-      </c>
-      <c r="J8" t="s">
-        <v>25</v>
+        <v>0.3176745329400197</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
       </c>
       <c r="K8">
-        <v>0.33333333333333331</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="L8">
-        <v>0.52777777777777779</v>
+        <v>0.5277777777777778</v>
       </c>
       <c r="M8">
-        <v>6.6666666666666666E-2</v>
+        <v>0.06666666666666667</v>
       </c>
       <c r="N8">
-        <v>0.34292035398230092</v>
+        <v>0.3429203539823009</v>
       </c>
       <c r="O8">
         <v>7.365591397849462</v>
@@ -1244,8 +988,10 @@
       <c r="R8">
         <v>1.935483870967742</v>
       </c>
-      <c r="S8" t="s">
-        <v>26</v>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>EHP-CrHi</t>
+        </is>
       </c>
       <c r="T8">
         <v>1.935483870967742</v>
@@ -1254,18 +1000,24 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="9" spans="1:21">
-      <c r="A9" t="s">
-        <v>47</v>
-      </c>
-      <c r="B9" t="s">
-        <v>32</v>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>LTR127_2017</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>LTR127</t>
+        </is>
       </c>
       <c r="C9">
         <v>2017</v>
       </c>
-      <c r="D9" t="s">
-        <v>33</v>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Skirvytė</t>
+        </is>
       </c>
       <c r="E9">
         <v>4</v>
@@ -1273,29 +1025,33 @@
       <c r="F9">
         <v>0.36</v>
       </c>
-      <c r="G9" t="s">
-        <v>25</v>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
       </c>
       <c r="H9">
         <v>0.31</v>
       </c>
       <c r="I9">
-        <v>0.31395867098865482</v>
-      </c>
-      <c r="J9" t="s">
-        <v>25</v>
+        <v>0.3139586709886548</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
       </c>
       <c r="K9">
-        <v>0.16666666666666671</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="L9">
-        <v>0.43333333333333329</v>
+        <v>0.4333333333333333</v>
       </c>
       <c r="M9">
         <v>0.2</v>
       </c>
       <c r="N9">
-        <v>0.45583468395461912</v>
+        <v>0.4558346839546191</v>
       </c>
       <c r="O9">
         <v>1.827956989247312</v>
@@ -1309,28 +1065,36 @@
       <c r="R9">
         <v>5.591397849462366</v>
       </c>
-      <c r="S9" t="s">
-        <v>35</v>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>DSFI</t>
+        </is>
       </c>
       <c r="T9">
         <v>1.827956989247312</v>
       </c>
       <c r="U9">
-        <v>4.9999999999999989E-2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:21">
-      <c r="A10" t="s">
-        <v>48</v>
-      </c>
-      <c r="B10" t="s">
-        <v>32</v>
+        <v>0.04999999999999999</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>LTR127_2020</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>LTR127</t>
+        </is>
       </c>
       <c r="C10">
         <v>2020</v>
       </c>
-      <c r="D10" t="s">
-        <v>33</v>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Skirvytė</t>
+        </is>
       </c>
       <c r="E10">
         <v>4</v>
@@ -1338,32 +1102,36 @@
       <c r="F10">
         <v>0.48</v>
       </c>
-      <c r="G10" t="s">
-        <v>24</v>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
       </c>
       <c r="H10">
         <v>0.42</v>
       </c>
       <c r="I10">
-        <v>0.42359724012027489</v>
-      </c>
-      <c r="J10" t="s">
-        <v>24</v>
+        <v>0.4235972401202749</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
       </c>
       <c r="K10">
         <v>0.5</v>
       </c>
       <c r="L10">
-        <v>0.60416666666666663</v>
+        <v>0.6041666666666666</v>
       </c>
       <c r="M10">
         <v>0.2</v>
       </c>
       <c r="N10">
-        <v>0.39022229381443302</v>
+        <v>0.390222293814433</v>
       </c>
       <c r="O10">
-        <v>30.161290322580641</v>
+        <v>30.16129032258064</v>
       </c>
       <c r="P10">
         <v>17.79569892473118</v>
@@ -1374,8 +1142,10 @@
       <c r="R10">
         <v>3.440860215053763</v>
       </c>
-      <c r="S10" t="s">
-        <v>26</v>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>EHP-CrHi</t>
+        </is>
       </c>
       <c r="T10">
         <v>3.440860215053763</v>
@@ -1384,18 +1154,24 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="11" spans="1:21">
-      <c r="A11" t="s">
-        <v>49</v>
-      </c>
-      <c r="B11" t="s">
-        <v>50</v>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>LTR625_2022</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>LTR625</t>
+        </is>
       </c>
       <c r="C11">
         <v>2022</v>
       </c>
-      <c r="D11" t="s">
-        <v>51</v>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Luoba</t>
+        </is>
       </c>
       <c r="E11">
         <v>3</v>
@@ -1403,64 +1179,76 @@
       <c r="F11">
         <v>0.83</v>
       </c>
-      <c r="G11" t="s">
-        <v>42</v>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
       </c>
       <c r="H11">
         <v>0.78</v>
       </c>
       <c r="I11">
-        <v>0.77945209350696332</v>
-      </c>
-      <c r="J11" t="s">
-        <v>30</v>
+        <v>0.7794520935069633</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
       </c>
       <c r="K11">
-        <v>0.66666666666666663</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="L11">
-        <v>0.79999999999999993</v>
+        <v>0.7999999999999999</v>
       </c>
       <c r="M11">
-        <v>1.0666666666666671</v>
+        <v>1.066666666666667</v>
       </c>
       <c r="N11">
-        <v>0.58447504069451983</v>
+        <v>0.5844750406945198</v>
       </c>
       <c r="O11">
-        <v>60.215053763440856</v>
+        <v>60.21505376344086</v>
       </c>
       <c r="P11">
-        <v>71.129032258064512</v>
+        <v>71.12903225806451</v>
       </c>
       <c r="Q11">
-        <v>98.602150537634415</v>
+        <v>98.60215053763442</v>
       </c>
       <c r="R11">
         <v>19.78494623655914</v>
       </c>
-      <c r="S11" t="s">
-        <v>26</v>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>EHP-CrHi</t>
+        </is>
       </c>
       <c r="T11">
         <v>19.78494623655914</v>
       </c>
       <c r="U11">
-        <v>4.9999999999999933E-2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:21">
-      <c r="A12" t="s">
-        <v>52</v>
-      </c>
-      <c r="B12" t="s">
-        <v>40</v>
+        <v>0.04999999999999993</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>LTR1466_2016</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>LTR1466</t>
+        </is>
       </c>
       <c r="C12">
         <v>2016</v>
       </c>
-      <c r="D12" t="s">
-        <v>41</v>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Įpiltis</t>
+        </is>
       </c>
       <c r="E12">
         <v>3</v>
@@ -1468,64 +1256,76 @@
       <c r="F12">
         <v>0.6</v>
       </c>
-      <c r="G12" t="s">
-        <v>30</v>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
       </c>
       <c r="H12">
-        <v>0.56000000000000005</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="I12">
-        <v>0.56270912849872778</v>
-      </c>
-      <c r="J12" t="s">
-        <v>24</v>
+        <v>0.5627091284987278</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
       </c>
       <c r="K12">
         <v>0.5</v>
       </c>
       <c r="L12">
-        <v>0.65333333333333332</v>
+        <v>0.6533333333333333</v>
       </c>
       <c r="M12">
-        <v>0.53333333333333333</v>
+        <v>0.5333333333333333</v>
       </c>
       <c r="N12">
-        <v>0.56416984732824427</v>
+        <v>0.5641698473282443</v>
       </c>
       <c r="O12">
-        <v>30.161290322580641</v>
+        <v>30.16129032258064</v>
       </c>
       <c r="P12">
         <v>28.06451612903226</v>
       </c>
       <c r="Q12">
-        <v>70.322580645161295</v>
+        <v>70.3225806451613</v>
       </c>
       <c r="R12">
         <v>15.6989247311828</v>
       </c>
-      <c r="S12" t="s">
-        <v>26</v>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>EHP-CrHi</t>
+        </is>
       </c>
       <c r="T12">
         <v>15.6989247311828</v>
       </c>
       <c r="U12">
-        <v>3.9999999999999918E-2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:21">
-      <c r="A13" t="s">
-        <v>53</v>
-      </c>
-      <c r="B13" t="s">
-        <v>54</v>
+        <v>0.03999999999999992</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>LTR1687_2016</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>LTR1687</t>
+        </is>
       </c>
       <c r="C13">
         <v>2016</v>
       </c>
-      <c r="D13" t="s">
-        <v>55</v>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Šalpė</t>
+        </is>
       </c>
       <c r="E13">
         <v>3</v>
@@ -1533,64 +1333,76 @@
       <c r="F13">
         <v>0.59</v>
       </c>
-      <c r="G13" t="s">
-        <v>24</v>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
       </c>
       <c r="H13">
-        <v>0.55000000000000004</v>
+        <v>0.55</v>
       </c>
       <c r="I13">
         <v>0.545704134366925</v>
       </c>
-      <c r="J13" t="s">
-        <v>24</v>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
       </c>
       <c r="K13">
         <v>0.5</v>
       </c>
       <c r="L13">
-        <v>0.77777777777777779</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="M13">
-        <v>0.33333333333333331</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="N13">
-        <v>0.57170542635658905</v>
+        <v>0.5717054263565891</v>
       </c>
       <c r="O13">
-        <v>30.161290322580641</v>
+        <v>30.16129032258064</v>
       </c>
       <c r="P13">
-        <v>63.978494623655912</v>
+        <v>63.97849462365591</v>
       </c>
       <c r="Q13">
-        <v>40.806451612903217</v>
+        <v>40.80645161290322</v>
       </c>
       <c r="R13">
-        <v>17.096774193548391</v>
-      </c>
-      <c r="S13" t="s">
-        <v>26</v>
+        <v>17.09677419354839</v>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>EHP-CrHi</t>
+        </is>
       </c>
       <c r="T13">
-        <v>17.096774193548391</v>
+        <v>17.09677419354839</v>
       </c>
       <c r="U13">
-        <v>3.9999999999999918E-2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:21">
-      <c r="A14" t="s">
-        <v>56</v>
-      </c>
-      <c r="B14" t="s">
-        <v>54</v>
+        <v>0.03999999999999992</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>LTR1687_2022</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>LTR1687</t>
+        </is>
       </c>
       <c r="C14">
         <v>2022</v>
       </c>
-      <c r="D14" t="s">
-        <v>55</v>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Šalpė</t>
+        </is>
       </c>
       <c r="E14">
         <v>3</v>
@@ -1598,64 +1410,76 @@
       <c r="F14">
         <v>0.7</v>
       </c>
-      <c r="G14" t="s">
-        <v>30</v>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
       </c>
       <c r="H14">
         <v>0.66</v>
       </c>
       <c r="I14">
-        <v>0.66081081081081083</v>
-      </c>
-      <c r="J14" t="s">
-        <v>30</v>
+        <v>0.6608108108108108</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
       </c>
       <c r="K14">
-        <v>0.66666666666666663</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="L14">
-        <v>0.96666666666666667</v>
+        <v>0.9666666666666667</v>
       </c>
       <c r="M14">
-        <v>0.26666666666666672</v>
+        <v>0.2666666666666667</v>
       </c>
       <c r="N14">
         <v>0.7432432432432432</v>
       </c>
       <c r="O14">
-        <v>60.215053763440856</v>
+        <v>60.21505376344086</v>
       </c>
       <c r="P14">
-        <v>97.311827956989248</v>
+        <v>97.31182795698925</v>
       </c>
       <c r="Q14">
         <v>29.35483870967742</v>
       </c>
       <c r="R14">
-        <v>73.870967741935488</v>
-      </c>
-      <c r="S14" t="s">
-        <v>57</v>
+        <v>73.87096774193549</v>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>DEP</t>
+        </is>
       </c>
       <c r="T14">
         <v>29.35483870967742</v>
       </c>
       <c r="U14">
-        <v>3.9999999999999918E-2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:21">
-      <c r="A15" t="s">
-        <v>58</v>
-      </c>
-      <c r="B15" t="s">
-        <v>59</v>
+        <v>0.03999999999999992</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>LTR297_2021</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>LTR297</t>
+        </is>
       </c>
       <c r="C15">
         <v>2021</v>
       </c>
-      <c r="D15" t="s">
-        <v>60</v>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Lokysta</t>
+        </is>
       </c>
       <c r="E15">
         <v>3</v>
@@ -1663,129 +1487,153 @@
       <c r="F15">
         <v>0.5</v>
       </c>
-      <c r="G15" t="s">
-        <v>24</v>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
       </c>
       <c r="H15">
         <v>0.54</v>
       </c>
       <c r="I15">
-        <v>0.54086538461538458</v>
-      </c>
-      <c r="J15" t="s">
-        <v>24</v>
+        <v>0.5408653846153846</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
       </c>
       <c r="K15">
         <v>0.5</v>
       </c>
       <c r="L15">
-        <v>0.70512820512820518</v>
+        <v>0.7051282051282052</v>
       </c>
       <c r="M15">
-        <v>0.33333333333333331</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="N15">
         <v>0.625</v>
       </c>
       <c r="O15">
-        <v>30.161290322580641</v>
+        <v>30.16129032258064</v>
       </c>
       <c r="P15">
-        <v>40.215053763440856</v>
+        <v>40.21505376344086</v>
       </c>
       <c r="Q15">
-        <v>40.806451612903217</v>
+        <v>40.80645161290322</v>
       </c>
       <c r="R15">
-        <v>31.666666666666671</v>
-      </c>
-      <c r="S15" t="s">
-        <v>35</v>
+        <v>31.66666666666667</v>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>DSFI</t>
+        </is>
       </c>
       <c r="T15">
-        <v>30.161290322580641</v>
+        <v>30.16129032258064</v>
       </c>
       <c r="U15">
-        <v>-4.0000000000000042E-2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:21">
-      <c r="A16" t="s">
-        <v>61</v>
-      </c>
-      <c r="B16" t="s">
-        <v>62</v>
+        <v>-0.04000000000000004</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>LTR1447_2015</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>LTR1447</t>
+        </is>
       </c>
       <c r="C16">
         <v>2015</v>
       </c>
-      <c r="D16" t="s">
-        <v>63</v>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Merkys</t>
+        </is>
       </c>
       <c r="E16">
         <v>5</v>
       </c>
       <c r="F16">
-        <v>0.69</v>
-      </c>
-      <c r="G16" t="s">
-        <v>30</v>
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
       </c>
       <c r="H16">
         <v>0.65</v>
       </c>
       <c r="I16">
-        <v>0.65006464798131458</v>
-      </c>
-      <c r="J16" t="s">
-        <v>30</v>
+        <v>0.6500646479813146</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
       </c>
       <c r="K16">
-        <v>0.66666666666666663</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="L16">
         <v>0.7901234567901233</v>
       </c>
       <c r="M16">
-        <v>0.46666666666666667</v>
+        <v>0.4666666666666667</v>
       </c>
       <c r="N16">
-        <v>0.67680180180180183</v>
+        <v>0.6768018018018018</v>
       </c>
       <c r="O16">
-        <v>60.215053763440856</v>
+        <v>60.21505376344086</v>
       </c>
       <c r="P16">
         <v>68.27956989247312</v>
       </c>
       <c r="Q16">
-        <v>61.021505376344088</v>
+        <v>61.02150537634409</v>
       </c>
       <c r="R16">
         <v>50.86021505376344</v>
       </c>
-      <c r="S16" t="s">
-        <v>26</v>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>EHP-CrHi</t>
+        </is>
       </c>
       <c r="T16">
         <v>50.86021505376344</v>
       </c>
       <c r="U16">
-        <v>3.9999999999999918E-2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:21">
-      <c r="A17" t="s">
-        <v>64</v>
-      </c>
-      <c r="B17" t="s">
-        <v>65</v>
+        <v>0.03999999999999992</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>LTR86_2015</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>LTR86</t>
+        </is>
       </c>
       <c r="C17">
         <v>2015</v>
       </c>
-      <c r="D17" t="s">
-        <v>23</v>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Mūša</t>
+        </is>
       </c>
       <c r="E17">
         <v>5</v>
@@ -1793,35 +1641,39 @@
       <c r="F17">
         <v>0.5</v>
       </c>
-      <c r="G17" t="s">
-        <v>24</v>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
       </c>
       <c r="H17">
         <v>0.46</v>
       </c>
       <c r="I17">
-        <v>0.45929487179487177</v>
-      </c>
-      <c r="J17" t="s">
-        <v>24</v>
+        <v>0.4592948717948718</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
       </c>
       <c r="K17">
-        <v>0.33333333333333331</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="L17">
-        <v>0.63888888888888884</v>
+        <v>0.6388888888888888</v>
       </c>
       <c r="M17">
-        <v>0.26666666666666672</v>
+        <v>0.2666666666666667</v>
       </c>
       <c r="N17">
-        <v>0.59829059829059827</v>
+        <v>0.5982905982905983</v>
       </c>
       <c r="O17">
         <v>7.365591397849462</v>
       </c>
       <c r="P17">
-        <v>24.946236559139781</v>
+        <v>24.94623655913978</v>
       </c>
       <c r="Q17">
         <v>29.35483870967742</v>
@@ -1829,28 +1681,36 @@
       <c r="R17">
         <v>22.36559139784946</v>
       </c>
-      <c r="S17" t="s">
-        <v>35</v>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>DSFI</t>
+        </is>
       </c>
       <c r="T17">
         <v>7.365591397849462</v>
       </c>
       <c r="U17">
-        <v>3.999999999999998E-2</v>
-      </c>
-    </row>
-    <row r="18" spans="1:21">
-      <c r="A18" t="s">
-        <v>66</v>
-      </c>
-      <c r="B18" t="s">
-        <v>67</v>
+        <v>0.03999999999999998</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>LTR1461_2022</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>LTR1461</t>
+        </is>
       </c>
       <c r="C18">
         <v>2022</v>
       </c>
-      <c r="D18" t="s">
-        <v>68</v>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Nemunėlis</t>
+        </is>
       </c>
       <c r="E18">
         <v>1</v>
@@ -1858,8 +1718,10 @@
       <c r="F18">
         <v>0.54</v>
       </c>
-      <c r="G18" t="s">
-        <v>24</v>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
       </c>
       <c r="H18">
         <v>0.51</v>
@@ -1867,55 +1729,65 @@
       <c r="I18">
         <v>0.5133803291958986</v>
       </c>
-      <c r="J18" t="s">
-        <v>24</v>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
       </c>
       <c r="K18">
         <v>0.5</v>
       </c>
       <c r="L18">
-        <v>0.62745098039215685</v>
+        <v>0.6274509803921569</v>
       </c>
       <c r="M18">
-        <v>0.26666666666666672</v>
+        <v>0.2666666666666667</v>
       </c>
       <c r="N18">
-        <v>0.65940366972477071</v>
+        <v>0.6594036697247707</v>
       </c>
       <c r="O18">
-        <v>30.161290322580641</v>
+        <v>30.16129032258064</v>
       </c>
       <c r="P18">
-        <v>21.827956989247308</v>
+        <v>21.82795698924731</v>
       </c>
       <c r="Q18">
         <v>29.35483870967742</v>
       </c>
       <c r="R18">
-        <v>44.516129032258057</v>
-      </c>
-      <c r="S18" t="s">
-        <v>69</v>
+        <v>44.51612903225806</v>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>ASPT</t>
+        </is>
       </c>
       <c r="T18">
-        <v>21.827956989247308</v>
+        <v>21.82795698924731</v>
       </c>
       <c r="U18">
-        <v>3.000000000000003E-2</v>
-      </c>
-    </row>
-    <row r="19" spans="1:21">
-      <c r="A19" t="s">
-        <v>70</v>
-      </c>
-      <c r="B19" t="s">
-        <v>67</v>
+        <v>0.03000000000000003</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>LTR1461_2016</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>LTR1461</t>
+        </is>
       </c>
       <c r="C19">
         <v>2016</v>
       </c>
-      <c r="D19" t="s">
-        <v>68</v>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Nemunėlis</t>
+        </is>
       </c>
       <c r="E19">
         <v>1</v>
@@ -1923,64 +1795,76 @@
       <c r="F19">
         <v>0.64</v>
       </c>
-      <c r="G19" t="s">
-        <v>30</v>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
       </c>
       <c r="H19">
         <v>0.67</v>
       </c>
       <c r="I19">
-        <v>0.67363000755857905</v>
-      </c>
-      <c r="J19" t="s">
-        <v>30</v>
+        <v>0.673630007558579</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
       </c>
       <c r="K19">
-        <v>0.83333333333333337</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="L19">
-        <v>0.87037037037037035</v>
+        <v>0.8703703703703703</v>
       </c>
       <c r="M19">
         <v>0.2</v>
       </c>
       <c r="N19">
-        <v>0.79081632653061229</v>
+        <v>0.7908163265306123</v>
       </c>
       <c r="O19">
-        <v>82.204301075268816</v>
+        <v>82.20430107526882</v>
       </c>
       <c r="P19">
-        <v>87.258064516129039</v>
+        <v>87.25806451612904</v>
       </c>
       <c r="Q19">
         <v>18.44086021505376</v>
       </c>
       <c r="R19">
-        <v>84.086021505376351</v>
-      </c>
-      <c r="S19" t="s">
-        <v>57</v>
+        <v>84.08602150537635</v>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>DEP</t>
+        </is>
       </c>
       <c r="T19">
         <v>18.44086021505376</v>
       </c>
       <c r="U19">
-        <v>-3.000000000000003E-2</v>
-      </c>
-    </row>
-    <row r="20" spans="1:21">
-      <c r="A20" t="s">
-        <v>71</v>
-      </c>
-      <c r="B20" t="s">
-        <v>67</v>
+        <v>-0.03000000000000003</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>LTR1461_2019</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>LTR1461</t>
+        </is>
       </c>
       <c r="C20">
         <v>2019</v>
       </c>
-      <c r="D20" t="s">
-        <v>68</v>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Nemunėlis</t>
+        </is>
       </c>
       <c r="E20">
         <v>1</v>
@@ -1988,64 +1872,76 @@
       <c r="F20">
         <v>0.66</v>
       </c>
-      <c r="G20" t="s">
-        <v>30</v>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
       </c>
       <c r="H20">
         <v>0.63</v>
       </c>
       <c r="I20">
-        <v>0.63075831665698368</v>
-      </c>
-      <c r="J20" t="s">
-        <v>30</v>
+        <v>0.6307583166569837</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
       </c>
       <c r="K20">
         <v>0.5</v>
       </c>
       <c r="L20">
-        <v>0.75595238095238093</v>
+        <v>0.7559523809523809</v>
       </c>
       <c r="M20">
         <v>0.6</v>
       </c>
       <c r="N20">
-        <v>0.66708088567555357</v>
+        <v>0.6670808856755536</v>
       </c>
       <c r="O20">
-        <v>30.161290322580641</v>
+        <v>30.16129032258064</v>
       </c>
       <c r="P20">
-        <v>56.612903225806448</v>
+        <v>56.61290322580645</v>
       </c>
       <c r="Q20">
-        <v>77.688172043010752</v>
+        <v>77.68817204301075</v>
       </c>
       <c r="R20">
         <v>47.41935483870968</v>
       </c>
-      <c r="S20" t="s">
-        <v>35</v>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>DSFI</t>
+        </is>
       </c>
       <c r="T20">
-        <v>30.161290322580641</v>
+        <v>30.16129032258064</v>
       </c>
       <c r="U20">
-        <v>3.000000000000003E-2</v>
-      </c>
-    </row>
-    <row r="21" spans="1:21">
-      <c r="A21" t="s">
-        <v>72</v>
-      </c>
-      <c r="B21" t="s">
-        <v>40</v>
+        <v>0.03000000000000003</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>LTR1466_2022</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>LTR1466</t>
+        </is>
       </c>
       <c r="C21">
         <v>2022</v>
       </c>
-      <c r="D21" t="s">
-        <v>41</v>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Įpiltis</t>
+        </is>
       </c>
       <c r="E21">
         <v>3</v>
@@ -2053,129 +1949,153 @@
       <c r="F21">
         <v>0.52</v>
       </c>
-      <c r="G21" t="s">
-        <v>24</v>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
       </c>
       <c r="H21">
         <v>0.49</v>
       </c>
       <c r="I21">
-        <v>0.49125072891610178</v>
-      </c>
-      <c r="J21" t="s">
-        <v>24</v>
+        <v>0.4912507289161018</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
       </c>
       <c r="K21">
         <v>0.5</v>
       </c>
       <c r="L21">
-        <v>0.56862745098039225</v>
+        <v>0.5686274509803922</v>
       </c>
       <c r="M21">
-        <v>0.33333333333333331</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="N21">
-        <v>0.56304213135068149</v>
+        <v>0.5630421313506815</v>
       </c>
       <c r="O21">
-        <v>30.161290322580641</v>
+        <v>30.16129032258064</v>
       </c>
       <c r="P21">
         <v>12.41935483870968</v>
       </c>
       <c r="Q21">
-        <v>40.806451612903217</v>
+        <v>40.80645161290322</v>
       </c>
       <c r="R21">
-        <v>15.268817204301079</v>
-      </c>
-      <c r="S21" t="s">
-        <v>69</v>
+        <v>15.26881720430108</v>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>ASPT</t>
+        </is>
       </c>
       <c r="T21">
         <v>12.41935483870968</v>
       </c>
       <c r="U21">
-        <v>3.000000000000003E-2</v>
-      </c>
-    </row>
-    <row r="22" spans="1:21">
-      <c r="A22" t="s">
-        <v>73</v>
-      </c>
-      <c r="B22" t="s">
-        <v>37</v>
+        <v>0.03000000000000003</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>LTR386_2016</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>LTR386</t>
+        </is>
       </c>
       <c r="C22">
         <v>2016</v>
       </c>
-      <c r="D22" t="s">
-        <v>38</v>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Viešinta</t>
+        </is>
       </c>
       <c r="E22">
         <v>1</v>
       </c>
       <c r="F22">
-        <v>0.69</v>
-      </c>
-      <c r="G22" t="s">
-        <v>30</v>
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
       </c>
       <c r="H22">
         <v>0.72</v>
       </c>
       <c r="I22">
-        <v>0.72275191708602926</v>
-      </c>
-      <c r="J22" t="s">
-        <v>30</v>
+        <v>0.7227519170860293</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
       </c>
       <c r="K22">
-        <v>0.83333333333333337</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="L22">
-        <v>0.78205128205128227</v>
+        <v>0.7820512820512823</v>
       </c>
       <c r="M22">
         <v>0.6</v>
       </c>
       <c r="N22">
-        <v>0.67562305295950154</v>
+        <v>0.6756230529595015</v>
       </c>
       <c r="O22">
-        <v>82.204301075268816</v>
+        <v>82.20430107526882</v>
       </c>
       <c r="P22">
-        <v>65.483870967741936</v>
+        <v>65.48387096774194</v>
       </c>
       <c r="Q22">
-        <v>77.688172043010752</v>
+        <v>77.68817204301075</v>
       </c>
       <c r="R22">
         <v>50.43010752688172</v>
       </c>
-      <c r="S22" t="s">
-        <v>26</v>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>EHP-CrHi</t>
+        </is>
       </c>
       <c r="T22">
         <v>50.43010752688172</v>
       </c>
       <c r="U22">
-        <v>-3.000000000000003E-2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:21">
-      <c r="A23" t="s">
-        <v>74</v>
-      </c>
-      <c r="B23" t="s">
-        <v>37</v>
+        <v>-0.03000000000000003</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>LTR386_2022</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>LTR386</t>
+        </is>
       </c>
       <c r="C23">
         <v>2022</v>
       </c>
-      <c r="D23" t="s">
-        <v>38</v>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Viešinta</t>
+        </is>
       </c>
       <c r="E23">
         <v>1</v>
@@ -2183,64 +2103,76 @@
       <c r="F23">
         <v>0.74</v>
       </c>
-      <c r="G23" t="s">
-        <v>30</v>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
       </c>
       <c r="H23">
         <v>0.71</v>
       </c>
       <c r="I23">
-        <v>0.70544954877112143</v>
-      </c>
-      <c r="J23" t="s">
-        <v>30</v>
+        <v>0.7054495487711214</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
       </c>
       <c r="K23">
-        <v>0.83333333333333337</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="L23">
-        <v>0.81182795698924737</v>
+        <v>0.8118279569892474</v>
       </c>
       <c r="M23">
         <v>0.6</v>
       </c>
       <c r="N23">
-        <v>0.57663690476190477</v>
+        <v>0.5766369047619048</v>
       </c>
       <c r="O23">
-        <v>82.204301075268816</v>
+        <v>82.20430107526882</v>
       </c>
       <c r="P23">
         <v>74.3010752688172</v>
       </c>
       <c r="Q23">
-        <v>77.688172043010752</v>
+        <v>77.68817204301075</v>
       </c>
       <c r="R23">
-        <v>17.956989247311832</v>
-      </c>
-      <c r="S23" t="s">
-        <v>26</v>
+        <v>17.95698924731183</v>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>EHP-CrHi</t>
+        </is>
       </c>
       <c r="T23">
-        <v>17.956989247311832</v>
+        <v>17.95698924731183</v>
       </c>
       <c r="U23">
-        <v>3.000000000000003E-2</v>
-      </c>
-    </row>
-    <row r="24" spans="1:21">
-      <c r="A24" t="s">
-        <v>75</v>
-      </c>
-      <c r="B24" t="s">
-        <v>76</v>
+        <v>0.03000000000000003</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>LTR1488_2015</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>LTR1488</t>
+        </is>
       </c>
       <c r="C24">
         <v>2015</v>
       </c>
-      <c r="D24" t="s">
-        <v>77</v>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Neris</t>
+        </is>
       </c>
       <c r="E24">
         <v>4</v>
@@ -2248,64 +2180,76 @@
       <c r="F24">
         <v>0.62</v>
       </c>
-      <c r="G24" t="s">
-        <v>30</v>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
       </c>
       <c r="H24">
         <v>0.59</v>
       </c>
       <c r="I24">
-        <v>0.59245595911265769</v>
-      </c>
-      <c r="J24" t="s">
-        <v>24</v>
+        <v>0.5924559591126577</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
       </c>
       <c r="K24">
         <v>0.5</v>
       </c>
       <c r="L24">
-        <v>0.71052631578947356</v>
+        <v>0.7105263157894736</v>
       </c>
       <c r="M24">
         <v>0.4</v>
       </c>
       <c r="N24">
-        <v>0.75929752066115697</v>
+        <v>0.759297520661157</v>
       </c>
       <c r="O24">
-        <v>30.161290322580641</v>
+        <v>30.16129032258064</v>
       </c>
       <c r="P24">
         <v>41.55913978494624</v>
       </c>
       <c r="Q24">
-        <v>51.451612903225808</v>
+        <v>51.45161290322581</v>
       </c>
       <c r="R24">
         <v>77.41935483870968</v>
       </c>
-      <c r="S24" t="s">
-        <v>35</v>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>DSFI</t>
+        </is>
       </c>
       <c r="T24">
-        <v>30.161290322580641</v>
+        <v>30.16129032258064</v>
       </c>
       <c r="U24">
-        <v>3.000000000000003E-2</v>
-      </c>
-    </row>
-    <row r="25" spans="1:21">
-      <c r="A25" t="s">
-        <v>78</v>
-      </c>
-      <c r="B25" t="s">
-        <v>79</v>
+        <v>0.03000000000000003</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>LTR1063_2021</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>LTR1063</t>
+        </is>
       </c>
       <c r="C25">
         <v>2021</v>
       </c>
-      <c r="D25" t="s">
-        <v>80</v>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>PentaII</t>
+        </is>
       </c>
       <c r="E25">
         <v>1</v>
@@ -2313,29 +2257,33 @@
       <c r="F25">
         <v>0.35</v>
       </c>
-      <c r="G25" t="s">
-        <v>25</v>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
       </c>
       <c r="H25">
         <v>0.33</v>
       </c>
       <c r="I25">
-        <v>0.33241770462633452</v>
-      </c>
-      <c r="J25" t="s">
-        <v>25</v>
+        <v>0.3324177046263345</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
       </c>
       <c r="K25">
-        <v>0.16666666666666671</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="L25">
-        <v>0.39583333333333331</v>
+        <v>0.3958333333333333</v>
       </c>
       <c r="M25">
         <v>0.2</v>
       </c>
       <c r="N25">
-        <v>0.56717081850533801</v>
+        <v>0.567170818505338</v>
       </c>
       <c r="O25">
         <v>1.827956989247312</v>
@@ -2347,30 +2295,38 @@
         <v>18.44086021505376</v>
       </c>
       <c r="R25">
-        <v>16.236559139784951</v>
-      </c>
-      <c r="S25" t="s">
-        <v>69</v>
+        <v>16.23655913978495</v>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>ASPT</t>
+        </is>
       </c>
       <c r="T25">
         <v>1.021505376344086</v>
       </c>
       <c r="U25">
-        <v>1.9999999999999959E-2</v>
-      </c>
-    </row>
-    <row r="26" spans="1:21">
-      <c r="A26" t="s">
-        <v>81</v>
-      </c>
-      <c r="B26" t="s">
-        <v>28</v>
+        <v>0.01999999999999996</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>LTR163_2016</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>LTR163</t>
+        </is>
       </c>
       <c r="C26">
         <v>2016</v>
       </c>
-      <c r="D26" t="s">
-        <v>29</v>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Geluža</t>
+        </is>
       </c>
       <c r="E26">
         <v>1</v>
@@ -2378,64 +2334,76 @@
       <c r="F26">
         <v>0.88</v>
       </c>
-      <c r="G26" t="s">
-        <v>42</v>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
       </c>
       <c r="H26">
         <v>0.86</v>
       </c>
       <c r="I26">
-        <v>0.86324494130694251</v>
-      </c>
-      <c r="J26" t="s">
-        <v>42</v>
+        <v>0.8632449413069425</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
       </c>
       <c r="K26">
         <v>1</v>
       </c>
       <c r="L26">
-        <v>0.79885057471264365</v>
+        <v>0.7988505747126436</v>
       </c>
       <c r="M26">
         <v>1</v>
       </c>
       <c r="N26">
-        <v>0.65412919051512664</v>
+        <v>0.6541291905151266</v>
       </c>
       <c r="O26">
-        <v>96.344086021505376</v>
+        <v>96.34408602150538</v>
       </c>
       <c r="P26">
-        <v>70.752688172043008</v>
+        <v>70.75268817204301</v>
       </c>
       <c r="Q26">
-        <v>97.849462365591393</v>
+        <v>97.84946236559139</v>
       </c>
       <c r="R26">
-        <v>43.118279569892472</v>
-      </c>
-      <c r="S26" t="s">
-        <v>26</v>
+        <v>43.11827956989247</v>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>EHP-CrHi</t>
+        </is>
       </c>
       <c r="T26">
-        <v>43.118279569892472</v>
+        <v>43.11827956989247</v>
       </c>
       <c r="U26">
-        <v>2.0000000000000021E-2</v>
-      </c>
-    </row>
-    <row r="27" spans="1:21">
-      <c r="A27" t="s">
-        <v>82</v>
-      </c>
-      <c r="B27" t="s">
-        <v>83</v>
+        <v>0.02000000000000002</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>LTR308_2018</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>LTR308</t>
+        </is>
       </c>
       <c r="C27">
         <v>2018</v>
       </c>
-      <c r="D27" t="s">
-        <v>84</v>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Eketė</t>
+        </is>
       </c>
       <c r="E27">
         <v>1</v>
@@ -2443,29 +2411,33 @@
       <c r="F27">
         <v>0.36</v>
       </c>
-      <c r="G27" t="s">
-        <v>25</v>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
       </c>
       <c r="H27">
         <v>0.34</v>
       </c>
       <c r="I27">
-        <v>0.33831018518518519</v>
-      </c>
-      <c r="J27" t="s">
-        <v>25</v>
+        <v>0.3383101851851852</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
       </c>
       <c r="K27">
-        <v>0.33333333333333331</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="L27">
-        <v>0.35416666666666669</v>
+        <v>0.3541666666666667</v>
       </c>
       <c r="M27">
         <v>0.1333333333333333</v>
       </c>
       <c r="N27">
-        <v>0.53240740740740733</v>
+        <v>0.5324074074074073</v>
       </c>
       <c r="O27">
         <v>7.365591397849462</v>
@@ -2474,33 +2446,41 @@
         <v>0.4838709677419355</v>
       </c>
       <c r="Q27">
-        <v>9.1397849462365599</v>
+        <v>9.13978494623656</v>
       </c>
       <c r="R27">
         <v>11.0752688172043</v>
       </c>
-      <c r="S27" t="s">
-        <v>69</v>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>ASPT</t>
+        </is>
       </c>
       <c r="T27">
         <v>0.4838709677419355</v>
       </c>
       <c r="U27">
-        <v>1.9999999999999959E-2</v>
-      </c>
-    </row>
-    <row r="28" spans="1:21">
-      <c r="A28" t="s">
-        <v>85</v>
-      </c>
-      <c r="B28" t="s">
-        <v>45</v>
+        <v>0.01999999999999996</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>LTR450_2020</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>LTR450</t>
+        </is>
       </c>
       <c r="C28">
         <v>2020</v>
       </c>
-      <c r="D28" t="s">
-        <v>46</v>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Ringuva</t>
+        </is>
       </c>
       <c r="E28">
         <v>2</v>
@@ -2508,20 +2488,24 @@
       <c r="F28">
         <v>0.38</v>
       </c>
-      <c r="G28" t="s">
-        <v>25</v>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
       </c>
       <c r="H28">
         <v>0.36</v>
       </c>
       <c r="I28">
-        <v>0.35912399598393568</v>
-      </c>
-      <c r="J28" t="s">
-        <v>25</v>
+        <v>0.3591239959839357</v>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
       </c>
       <c r="K28">
-        <v>0.33333333333333331</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="L28">
         <v>0.5625</v>
@@ -2530,7 +2514,7 @@
         <v>0</v>
       </c>
       <c r="N28">
-        <v>0.54066265060240959</v>
+        <v>0.5406626506024096</v>
       </c>
       <c r="O28">
         <v>7.365591397849462</v>
@@ -2544,28 +2528,36 @@
       <c r="R28">
         <v>11.93548387096774</v>
       </c>
-      <c r="S28" t="s">
-        <v>57</v>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>DEP</t>
+        </is>
       </c>
       <c r="T28">
         <v>0.4838709677419355</v>
       </c>
       <c r="U28">
-        <v>2.0000000000000021E-2</v>
-      </c>
-    </row>
-    <row r="29" spans="1:21">
-      <c r="A29" t="s">
-        <v>86</v>
-      </c>
-      <c r="B29" t="s">
-        <v>59</v>
+        <v>0.02000000000000002</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>LTR297_2018</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>LTR297</t>
+        </is>
       </c>
       <c r="C29">
         <v>2018</v>
       </c>
-      <c r="D29" t="s">
-        <v>60</v>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Lokysta</t>
+        </is>
       </c>
       <c r="E29">
         <v>3</v>
@@ -2573,29 +2565,33 @@
       <c r="F29">
         <v>0.39</v>
       </c>
-      <c r="G29" t="s">
-        <v>25</v>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
       </c>
       <c r="H29">
         <v>0.37</v>
       </c>
       <c r="I29">
-        <v>0.36613924050632912</v>
-      </c>
-      <c r="J29" t="s">
-        <v>25</v>
+        <v>0.3661392405063291</v>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
       </c>
       <c r="K29">
-        <v>0.16666666666666671</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="L29">
-        <v>0.43333333333333329</v>
+        <v>0.4333333333333333</v>
       </c>
       <c r="M29">
         <v>0.2</v>
       </c>
       <c r="N29">
-        <v>0.66455696202531633</v>
+        <v>0.6645569620253163</v>
       </c>
       <c r="O29">
         <v>1.827956989247312</v>
@@ -2607,30 +2603,38 @@
         <v>18.44086021505376</v>
       </c>
       <c r="R29">
-        <v>46.774193548387103</v>
-      </c>
-      <c r="S29" t="s">
-        <v>35</v>
+        <v>46.7741935483871</v>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>DSFI</t>
+        </is>
       </c>
       <c r="T29">
         <v>1.827956989247312</v>
       </c>
       <c r="U29">
-        <v>2.0000000000000021E-2</v>
-      </c>
-    </row>
-    <row r="30" spans="1:21">
-      <c r="A30" t="s">
-        <v>87</v>
-      </c>
-      <c r="B30" t="s">
-        <v>88</v>
+        <v>0.02000000000000002</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>LTR706_2015</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>LTR706</t>
+        </is>
       </c>
       <c r="C30">
         <v>2015</v>
       </c>
-      <c r="D30" t="s">
-        <v>89</v>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Liaudė</t>
+        </is>
       </c>
       <c r="E30">
         <v>3</v>
@@ -2638,29 +2642,33 @@
       <c r="F30">
         <v>0.39</v>
       </c>
-      <c r="G30" t="s">
-        <v>25</v>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
       </c>
       <c r="H30">
         <v>0.37</v>
       </c>
       <c r="I30">
-        <v>0.37006978993919287</v>
-      </c>
-      <c r="J30" t="s">
-        <v>25</v>
+        <v>0.3700697899391929</v>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
       </c>
       <c r="K30">
-        <v>0.33333333333333331</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="L30">
-        <v>0.42592592592592582</v>
+        <v>0.4259259259259258</v>
       </c>
       <c r="M30">
         <v>0.1333333333333333</v>
       </c>
       <c r="N30">
-        <v>0.58768656716417911</v>
+        <v>0.5876865671641791</v>
       </c>
       <c r="O30">
         <v>7.365591397849462</v>
@@ -2669,33 +2677,41 @@
         <v>1.612903225806452</v>
       </c>
       <c r="Q30">
-        <v>9.1397849462365599</v>
+        <v>9.13978494623656</v>
       </c>
       <c r="R30">
-        <v>20.107526881720428</v>
-      </c>
-      <c r="S30" t="s">
-        <v>69</v>
+        <v>20.10752688172043</v>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>ASPT</t>
+        </is>
       </c>
       <c r="T30">
         <v>1.612903225806452</v>
       </c>
       <c r="U30">
-        <v>2.0000000000000021E-2</v>
-      </c>
-    </row>
-    <row r="31" spans="1:21">
-      <c r="A31" t="s">
-        <v>90</v>
-      </c>
-      <c r="B31" t="s">
-        <v>76</v>
+        <v>0.02000000000000002</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>LTR1488_2016</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>LTR1488</t>
+        </is>
       </c>
       <c r="C31">
         <v>2016</v>
       </c>
-      <c r="D31" t="s">
-        <v>77</v>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Neris</t>
+        </is>
       </c>
       <c r="E31">
         <v>4</v>
@@ -2703,64 +2719,76 @@
       <c r="F31">
         <v>0.68</v>
       </c>
-      <c r="G31" t="s">
-        <v>30</v>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
       </c>
       <c r="H31">
         <v>0.66</v>
       </c>
       <c r="I31">
-        <v>0.66475997506234408</v>
-      </c>
-      <c r="J31" t="s">
-        <v>30</v>
+        <v>0.6647599750623441</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
       </c>
       <c r="K31">
-        <v>0.66666666666666663</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="L31">
-        <v>0.83333333333333337</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="M31">
         <v>0.4</v>
       </c>
       <c r="N31">
-        <v>0.75903990024937651</v>
+        <v>0.7590399002493765</v>
       </c>
       <c r="O31">
-        <v>60.215053763440856</v>
+        <v>60.21505376344086</v>
       </c>
       <c r="P31">
-        <v>79.623655913978496</v>
+        <v>79.6236559139785</v>
       </c>
       <c r="Q31">
-        <v>51.451612903225808</v>
+        <v>51.45161290322581</v>
       </c>
       <c r="R31">
-        <v>77.204301075268816</v>
-      </c>
-      <c r="S31" t="s">
-        <v>57</v>
+        <v>77.20430107526882</v>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>DEP</t>
+        </is>
       </c>
       <c r="T31">
-        <v>51.451612903225808</v>
+        <v>51.45161290322581</v>
       </c>
       <c r="U31">
-        <v>2.0000000000000021E-2</v>
-      </c>
-    </row>
-    <row r="32" spans="1:21">
-      <c r="A32" t="s">
-        <v>91</v>
-      </c>
-      <c r="B32" t="s">
-        <v>22</v>
+        <v>0.02000000000000002</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>LTR1492_2019</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>LTR1492</t>
+        </is>
       </c>
       <c r="C32">
         <v>2019</v>
       </c>
-      <c r="D32" t="s">
-        <v>23</v>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Mūša</t>
+        </is>
       </c>
       <c r="E32">
         <v>5</v>
@@ -2768,23 +2796,27 @@
       <c r="F32">
         <v>0.49</v>
       </c>
-      <c r="G32" t="s">
-        <v>24</v>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
       </c>
       <c r="H32">
         <v>0.47</v>
       </c>
       <c r="I32">
-        <v>0.46923145408722328</v>
-      </c>
-      <c r="J32" t="s">
-        <v>24</v>
+        <v>0.4692314540872233</v>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
       </c>
       <c r="K32">
         <v>0.5</v>
       </c>
       <c r="L32">
-        <v>0.60185185185185175</v>
+        <v>0.6018518518518517</v>
       </c>
       <c r="M32">
         <v>0.2</v>
@@ -2793,7 +2825,7 @@
         <v>0.5750739644970414</v>
       </c>
       <c r="O32">
-        <v>30.161290322580641</v>
+        <v>30.16129032258064</v>
       </c>
       <c r="P32">
         <v>16.93548387096774</v>
@@ -2802,30 +2834,38 @@
         <v>18.44086021505376</v>
       </c>
       <c r="R32">
-        <v>17.526881720430111</v>
-      </c>
-      <c r="S32" t="s">
-        <v>69</v>
+        <v>17.52688172043011</v>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>ASPT</t>
+        </is>
       </c>
       <c r="T32">
         <v>16.93548387096774</v>
       </c>
       <c r="U32">
-        <v>2.0000000000000021E-2</v>
-      </c>
-    </row>
-    <row r="33" spans="1:21">
-      <c r="A33" t="s">
-        <v>92</v>
-      </c>
-      <c r="B33" t="s">
-        <v>93</v>
+        <v>0.02000000000000002</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>LTR1502_2015</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>LTR1502</t>
+        </is>
       </c>
       <c r="C33">
         <v>2015</v>
       </c>
-      <c r="D33" t="s">
-        <v>94</v>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Lėvuo</t>
+        </is>
       </c>
       <c r="E33">
         <v>5</v>
@@ -2833,100 +2873,116 @@
       <c r="F33">
         <v>0.72</v>
       </c>
-      <c r="G33" t="s">
-        <v>30</v>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
       </c>
       <c r="H33">
         <v>0.7</v>
       </c>
       <c r="I33">
-        <v>0.70239158163265314</v>
-      </c>
-      <c r="J33" t="s">
-        <v>30</v>
+        <v>0.7023915816326531</v>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
       </c>
       <c r="K33">
-        <v>0.83333333333333337</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="L33">
         <v>0.875</v>
       </c>
       <c r="M33">
-        <v>0.46666666666666667</v>
+        <v>0.4666666666666667</v>
       </c>
       <c r="N33">
-        <v>0.63456632653061229</v>
+        <v>0.6345663265306123</v>
       </c>
       <c r="O33">
-        <v>82.204301075268816</v>
+        <v>82.20430107526882</v>
       </c>
       <c r="P33">
-        <v>88.387096774193552</v>
+        <v>88.38709677419355</v>
       </c>
       <c r="Q33">
-        <v>61.021505376344088</v>
+        <v>61.02150537634409</v>
       </c>
       <c r="R33">
-        <v>35.161290322580648</v>
-      </c>
-      <c r="S33" t="s">
-        <v>26</v>
+        <v>35.16129032258065</v>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>EHP-CrHi</t>
+        </is>
       </c>
       <c r="T33">
-        <v>35.161290322580648</v>
+        <v>35.16129032258065</v>
       </c>
       <c r="U33">
-        <v>2.0000000000000021E-2</v>
-      </c>
-    </row>
-    <row r="34" spans="1:21">
-      <c r="A34" t="s">
-        <v>95</v>
-      </c>
-      <c r="B34" t="s">
-        <v>96</v>
+        <v>0.02000000000000002</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>LTR337_2019</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>LTR337</t>
+        </is>
       </c>
       <c r="C34">
         <v>2019</v>
       </c>
-      <c r="D34" t="s">
-        <v>97</v>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Svyla</t>
+        </is>
       </c>
       <c r="E34">
         <v>1</v>
       </c>
       <c r="F34">
-        <v>0.56999999999999995</v>
-      </c>
-      <c r="G34" t="s">
-        <v>24</v>
+        <v>0.57</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
       </c>
       <c r="H34">
-        <v>0.56000000000000005</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="I34">
-        <v>0.55838312246173072</v>
-      </c>
-      <c r="J34" t="s">
-        <v>24</v>
+        <v>0.5583831224617307</v>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
       </c>
       <c r="K34">
-        <v>0.66666666666666663</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="L34">
-        <v>0.65909090909090906</v>
+        <v>0.6590909090909091</v>
       </c>
       <c r="M34">
-        <v>0.26666666666666672</v>
+        <v>0.2666666666666667</v>
       </c>
       <c r="N34">
-        <v>0.64110824742268036</v>
+        <v>0.6411082474226804</v>
       </c>
       <c r="O34">
-        <v>60.215053763440856</v>
+        <v>60.21505376344086</v>
       </c>
       <c r="P34">
-        <v>29.462365591397852</v>
+        <v>29.46236559139785</v>
       </c>
       <c r="Q34">
         <v>29.35483870967742</v>
@@ -2934,28 +2990,36 @@
       <c r="R34">
         <v>38.27956989247312</v>
       </c>
-      <c r="S34" t="s">
-        <v>57</v>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>DEP</t>
+        </is>
       </c>
       <c r="T34">
         <v>29.35483870967742</v>
       </c>
       <c r="U34">
-        <v>9.9999999999998979E-3</v>
-      </c>
-    </row>
-    <row r="35" spans="1:21">
-      <c r="A35" t="s">
-        <v>98</v>
-      </c>
-      <c r="B35" t="s">
-        <v>96</v>
+        <v>0.009999999999999898</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>LTR337_2022</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>LTR337</t>
+        </is>
       </c>
       <c r="C35">
         <v>2022</v>
       </c>
-      <c r="D35" t="s">
-        <v>97</v>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Svyla</t>
+        </is>
       </c>
       <c r="E35">
         <v>1</v>
@@ -2963,64 +3027,76 @@
       <c r="F35">
         <v>0.74</v>
       </c>
-      <c r="G35" t="s">
-        <v>30</v>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
       </c>
       <c r="H35">
         <v>0.75</v>
       </c>
       <c r="I35">
-        <v>0.74951451734539976</v>
-      </c>
-      <c r="J35" t="s">
-        <v>30</v>
+        <v>0.7495145173453998</v>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
       </c>
       <c r="K35">
-        <v>0.83333333333333337</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="L35">
-        <v>0.71568627450980393</v>
+        <v>0.7156862745098039</v>
       </c>
       <c r="M35">
         <v>0.8</v>
       </c>
       <c r="N35">
-        <v>0.64903846153846156</v>
+        <v>0.6490384615384616</v>
       </c>
       <c r="O35">
-        <v>82.204301075268816</v>
+        <v>82.20430107526882</v>
       </c>
       <c r="P35">
-        <v>42.741935483870968</v>
+        <v>42.74193548387097</v>
       </c>
       <c r="Q35">
-        <v>92.311827956989248</v>
+        <v>92.31182795698925</v>
       </c>
       <c r="R35">
-        <v>41.182795698924728</v>
-      </c>
-      <c r="S35" t="s">
-        <v>26</v>
+        <v>41.18279569892473</v>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>EHP-CrHi</t>
+        </is>
       </c>
       <c r="T35">
-        <v>41.182795698924728</v>
+        <v>41.18279569892473</v>
       </c>
       <c r="U35">
-        <v>-1.0000000000000011E-2</v>
-      </c>
-    </row>
-    <row r="36" spans="1:21">
-      <c r="A36" t="s">
-        <v>99</v>
-      </c>
-      <c r="B36" t="s">
-        <v>96</v>
+        <v>-0.01000000000000001</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>LTR337_2016</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>LTR337</t>
+        </is>
       </c>
       <c r="C36">
         <v>2016</v>
       </c>
-      <c r="D36" t="s">
-        <v>97</v>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Svyla</t>
+        </is>
       </c>
       <c r="E36">
         <v>1</v>
@@ -3028,64 +3104,76 @@
       <c r="F36">
         <v>0.78</v>
       </c>
-      <c r="G36" t="s">
-        <v>30</v>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
       </c>
       <c r="H36">
         <v>0.77</v>
       </c>
       <c r="I36">
-        <v>0.77287881779884149</v>
-      </c>
-      <c r="J36" t="s">
-        <v>30</v>
+        <v>0.7728788177988415</v>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
       </c>
       <c r="K36">
-        <v>0.83333333333333337</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="L36">
-        <v>0.73888888888888893</v>
+        <v>0.7388888888888889</v>
       </c>
       <c r="M36">
         <v>0.8</v>
       </c>
       <c r="N36">
-        <v>0.71929304897314372</v>
+        <v>0.7192930489731437</v>
       </c>
       <c r="O36">
-        <v>82.204301075268816</v>
+        <v>82.20430107526882</v>
       </c>
       <c r="P36">
-        <v>50.537634408602152</v>
+        <v>50.53763440860215</v>
       </c>
       <c r="Q36">
-        <v>92.311827956989248</v>
+        <v>92.31182795698925</v>
       </c>
       <c r="R36">
-        <v>65.591397849462368</v>
-      </c>
-      <c r="S36" t="s">
-        <v>69</v>
+        <v>65.59139784946237</v>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>ASPT</t>
+        </is>
       </c>
       <c r="T36">
-        <v>50.537634408602152</v>
+        <v>50.53763440860215</v>
       </c>
       <c r="U36">
-        <v>1.0000000000000011E-2</v>
-      </c>
-    </row>
-    <row r="37" spans="1:21">
-      <c r="A37" t="s">
-        <v>100</v>
-      </c>
-      <c r="B37" t="s">
-        <v>54</v>
+        <v>0.01000000000000001</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>LTR1687_2017</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>LTR1687</t>
+        </is>
       </c>
       <c r="C37">
         <v>2017</v>
       </c>
-      <c r="D37" t="s">
-        <v>55</v>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Šalpė</t>
+        </is>
       </c>
       <c r="E37">
         <v>3</v>
@@ -3093,23 +3181,27 @@
       <c r="F37">
         <v>0.54</v>
       </c>
-      <c r="G37" t="s">
-        <v>24</v>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
       </c>
       <c r="H37">
         <v>0.53</v>
       </c>
       <c r="I37">
-        <v>0.52548076923076925</v>
-      </c>
-      <c r="J37" t="s">
-        <v>24</v>
+        <v>0.5254807692307693</v>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
       </c>
       <c r="K37">
         <v>0.5</v>
       </c>
       <c r="L37">
-        <v>0.57692307692307698</v>
+        <v>0.576923076923077</v>
       </c>
       <c r="M37">
         <v>0.4</v>
@@ -3118,39 +3210,47 @@
         <v>0.625</v>
       </c>
       <c r="O37">
-        <v>30.161290322580641</v>
+        <v>30.16129032258064</v>
       </c>
       <c r="P37">
         <v>13.33333333333333</v>
       </c>
       <c r="Q37">
-        <v>51.451612903225808</v>
+        <v>51.45161290322581</v>
       </c>
       <c r="R37">
-        <v>31.666666666666671</v>
-      </c>
-      <c r="S37" t="s">
-        <v>69</v>
+        <v>31.66666666666667</v>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>ASPT</t>
+        </is>
       </c>
       <c r="T37">
         <v>13.33333333333333</v>
       </c>
       <c r="U37">
-        <v>1.0000000000000011E-2</v>
-      </c>
-    </row>
-    <row r="38" spans="1:21">
-      <c r="A38" t="s">
-        <v>101</v>
-      </c>
-      <c r="B38" t="s">
-        <v>59</v>
+        <v>0.01000000000000001</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>LTR297_2015</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>LTR297</t>
+        </is>
       </c>
       <c r="C38">
         <v>2015</v>
       </c>
-      <c r="D38" t="s">
-        <v>60</v>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Lokysta</t>
+        </is>
       </c>
       <c r="E38">
         <v>3</v>
@@ -3158,29 +3258,33 @@
       <c r="F38">
         <v>0.36</v>
       </c>
-      <c r="G38" t="s">
-        <v>25</v>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
       </c>
       <c r="H38">
         <v>0.35</v>
       </c>
       <c r="I38">
-        <v>0.34890710382513662</v>
-      </c>
-      <c r="J38" t="s">
-        <v>25</v>
+        <v>0.3489071038251366</v>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
       </c>
       <c r="K38">
-        <v>0.33333333333333331</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="L38">
-        <v>0.41666666666666669</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="M38">
         <v>0.1333333333333333</v>
       </c>
       <c r="N38">
-        <v>0.51229508196721307</v>
+        <v>0.5122950819672131</v>
       </c>
       <c r="O38">
         <v>7.365591397849462</v>
@@ -3189,33 +3293,41 @@
         <v>1.290322580645161</v>
       </c>
       <c r="Q38">
-        <v>9.1397849462365599</v>
+        <v>9.13978494623656</v>
       </c>
       <c r="R38">
-        <v>9.2473118279569899</v>
-      </c>
-      <c r="S38" t="s">
-        <v>69</v>
+        <v>9.24731182795699</v>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>ASPT</t>
+        </is>
       </c>
       <c r="T38">
         <v>1.290322580645161</v>
       </c>
       <c r="U38">
-        <v>1.0000000000000011E-2</v>
-      </c>
-    </row>
-    <row r="39" spans="1:21">
-      <c r="A39" t="s">
-        <v>102</v>
-      </c>
-      <c r="B39" t="s">
-        <v>76</v>
+        <v>0.01000000000000001</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>LTR1488_2022</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>LTR1488</t>
+        </is>
       </c>
       <c r="C39">
         <v>2022</v>
       </c>
-      <c r="D39" t="s">
-        <v>77</v>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Neris</t>
+        </is>
       </c>
       <c r="E39">
         <v>4</v>
@@ -3223,64 +3335,76 @@
       <c r="F39">
         <v>0.42</v>
       </c>
-      <c r="G39" t="s">
-        <v>24</v>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
       </c>
       <c r="H39">
         <v>0.41</v>
       </c>
       <c r="I39">
-        <v>0.41101294157193491</v>
-      </c>
-      <c r="J39" t="s">
-        <v>24</v>
+        <v>0.4110129415719349</v>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
       </c>
       <c r="K39">
-        <v>0.33333333333333331</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="L39">
-        <v>0.58641975308641969</v>
+        <v>0.5864197530864197</v>
       </c>
       <c r="M39">
         <v>0.1333333333333333</v>
       </c>
       <c r="N39">
-        <v>0.59096534653465338</v>
+        <v>0.5909653465346534</v>
       </c>
       <c r="O39">
         <v>7.365591397849462</v>
       </c>
       <c r="P39">
-        <v>14.731182795698921</v>
+        <v>14.73118279569892</v>
       </c>
       <c r="Q39">
-        <v>9.1397849462365599</v>
+        <v>9.13978494623656</v>
       </c>
       <c r="R39">
         <v>21.29032258064516</v>
       </c>
-      <c r="S39" t="s">
-        <v>35</v>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>DSFI</t>
+        </is>
       </c>
       <c r="T39">
         <v>7.365591397849462</v>
       </c>
       <c r="U39">
-        <v>1.0000000000000011E-2</v>
-      </c>
-    </row>
-    <row r="40" spans="1:21">
-      <c r="A40" t="s">
-        <v>103</v>
-      </c>
-      <c r="B40" t="s">
-        <v>76</v>
+        <v>0.01000000000000001</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>LTR1488_2019</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>LTR1488</t>
+        </is>
       </c>
       <c r="C40">
         <v>2019</v>
       </c>
-      <c r="D40" t="s">
-        <v>77</v>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Neris</t>
+        </is>
       </c>
       <c r="E40">
         <v>4</v>
@@ -3288,64 +3412,76 @@
       <c r="F40">
         <v>0.51</v>
       </c>
-      <c r="G40" t="s">
-        <v>24</v>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
       </c>
       <c r="H40">
         <v>0.52</v>
       </c>
       <c r="I40">
-        <v>0.52081370647455438</v>
-      </c>
-      <c r="J40" t="s">
-        <v>24</v>
+        <v>0.5208137064745544</v>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
       </c>
       <c r="K40">
         <v>0.5</v>
       </c>
       <c r="L40">
-        <v>0.70370370370370372</v>
+        <v>0.7037037037037037</v>
       </c>
       <c r="M40">
         <v>0.2</v>
       </c>
       <c r="N40">
-        <v>0.67955112219451363</v>
+        <v>0.6795511221945136</v>
       </c>
       <c r="O40">
-        <v>30.161290322580641</v>
+        <v>30.16129032258064</v>
       </c>
       <c r="P40">
-        <v>39.462365591397848</v>
+        <v>39.46236559139785</v>
       </c>
       <c r="Q40">
         <v>18.44086021505376</v>
       </c>
       <c r="R40">
-        <v>52.258064516129032</v>
-      </c>
-      <c r="S40" t="s">
-        <v>57</v>
+        <v>52.25806451612903</v>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>DEP</t>
+        </is>
       </c>
       <c r="T40">
         <v>18.44086021505376</v>
       </c>
       <c r="U40">
-        <v>-1.0000000000000011E-2</v>
-      </c>
-    </row>
-    <row r="41" spans="1:21">
-      <c r="A41" t="s">
-        <v>104</v>
-      </c>
-      <c r="B41" t="s">
-        <v>105</v>
+        <v>-0.01000000000000001</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>LTR1501_2016</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>LTR1501</t>
+        </is>
       </c>
       <c r="C41">
         <v>2016</v>
       </c>
-      <c r="D41" t="s">
-        <v>23</v>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Mūša</t>
+        </is>
       </c>
       <c r="E41">
         <v>4</v>
@@ -3353,8 +3489,10 @@
       <c r="F41">
         <v>0.46</v>
       </c>
-      <c r="G41" t="s">
-        <v>24</v>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
       </c>
       <c r="H41">
         <v>0.45</v>
@@ -3362,55 +3500,65 @@
       <c r="I41">
         <v>0.449387600616866</v>
       </c>
-      <c r="J41" t="s">
-        <v>24</v>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
       </c>
       <c r="K41">
         <v>0.5</v>
       </c>
       <c r="L41">
-        <v>0.75396825396825395</v>
+        <v>0.753968253968254</v>
       </c>
       <c r="M41">
         <v>0.1333333333333333</v>
       </c>
       <c r="N41">
-        <v>0.41024881516587669</v>
+        <v>0.4102488151658767</v>
       </c>
       <c r="O41">
-        <v>30.161290322580641</v>
+        <v>30.16129032258064</v>
       </c>
       <c r="P41">
-        <v>55.967741935483872</v>
+        <v>55.96774193548387</v>
       </c>
       <c r="Q41">
-        <v>9.1397849462365599</v>
+        <v>9.13978494623656</v>
       </c>
       <c r="R41">
         <v>3.978494623655914</v>
       </c>
-      <c r="S41" t="s">
-        <v>26</v>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>EHP-CrHi</t>
+        </is>
       </c>
       <c r="T41">
         <v>3.978494623655914</v>
       </c>
       <c r="U41">
-        <v>1.0000000000000011E-2</v>
-      </c>
-    </row>
-    <row r="42" spans="1:21">
-      <c r="A42" t="s">
-        <v>106</v>
-      </c>
-      <c r="B42" t="s">
-        <v>62</v>
+        <v>0.01000000000000001</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>LTR1447_2022</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>LTR1447</t>
+        </is>
       </c>
       <c r="C42">
         <v>2022</v>
       </c>
-      <c r="D42" t="s">
-        <v>63</v>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Merkys</t>
+        </is>
       </c>
       <c r="E42">
         <v>5</v>
@@ -3418,64 +3566,76 @@
       <c r="F42">
         <v>0.78</v>
       </c>
-      <c r="G42" t="s">
-        <v>30</v>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
       </c>
       <c r="H42">
         <v>0.77</v>
       </c>
       <c r="I42">
-        <v>0.77337177814674252</v>
-      </c>
-      <c r="J42" t="s">
-        <v>30</v>
+        <v>0.7733717781467425</v>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
       </c>
       <c r="K42">
-        <v>0.66666666666666663</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="L42">
-        <v>0.78431372549019607</v>
+        <v>0.7843137254901961</v>
       </c>
       <c r="M42">
         <v>0.6</v>
       </c>
       <c r="N42">
-        <v>1.0425067204301079</v>
+        <v>1.042506720430108</v>
       </c>
       <c r="O42">
-        <v>60.215053763440856</v>
+        <v>60.21505376344086</v>
       </c>
       <c r="P42">
-        <v>66.182795698924735</v>
+        <v>66.18279569892474</v>
       </c>
       <c r="Q42">
-        <v>77.688172043010752</v>
+        <v>77.68817204301075</v>
       </c>
       <c r="R42">
-        <v>99.247311827956992</v>
-      </c>
-      <c r="S42" t="s">
-        <v>35</v>
+        <v>99.24731182795699</v>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>DSFI</t>
+        </is>
       </c>
       <c r="T42">
-        <v>60.215053763440856</v>
+        <v>60.21505376344086</v>
       </c>
       <c r="U42">
-        <v>1.0000000000000011E-2</v>
-      </c>
-    </row>
-    <row r="43" spans="1:21">
-      <c r="A43" t="s">
-        <v>107</v>
-      </c>
-      <c r="B43" t="s">
-        <v>22</v>
+        <v>0.01000000000000001</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>LTR1492_2016</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>LTR1492</t>
+        </is>
       </c>
       <c r="C43">
         <v>2016</v>
       </c>
-      <c r="D43" t="s">
-        <v>23</v>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Mūša</t>
+        </is>
       </c>
       <c r="E43">
         <v>5</v>
@@ -3483,97 +3643,113 @@
       <c r="F43">
         <v>0.45</v>
       </c>
-      <c r="G43" t="s">
-        <v>24</v>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
       </c>
       <c r="H43">
         <v>0.44</v>
       </c>
       <c r="I43">
-        <v>0.44466455091455093</v>
-      </c>
-      <c r="J43" t="s">
-        <v>24</v>
+        <v>0.4446645509145509</v>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
       </c>
       <c r="K43">
-        <v>0.33333333333333331</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="L43">
-        <v>0.61111111111111116</v>
+        <v>0.6111111111111112</v>
       </c>
       <c r="M43">
         <v>0.2</v>
       </c>
       <c r="N43">
-        <v>0.63421375921375922</v>
+        <v>0.6342137592137592</v>
       </c>
       <c r="O43">
         <v>7.365591397849462</v>
       </c>
       <c r="P43">
-        <v>19.247311827956992</v>
+        <v>19.24731182795699</v>
       </c>
       <c r="Q43">
         <v>18.44086021505376</v>
       </c>
       <c r="R43">
-        <v>35.053763440860223</v>
-      </c>
-      <c r="S43" t="s">
-        <v>35</v>
+        <v>35.05376344086022</v>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>DSFI</t>
+        </is>
       </c>
       <c r="T43">
         <v>7.365591397849462</v>
       </c>
       <c r="U43">
-        <v>1.0000000000000011E-2</v>
-      </c>
-    </row>
-    <row r="44" spans="1:21">
-      <c r="A44" t="s">
-        <v>108</v>
-      </c>
-      <c r="B44" t="s">
-        <v>93</v>
+        <v>0.01000000000000001</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>LTR1502_2019</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>LTR1502</t>
+        </is>
       </c>
       <c r="C44">
         <v>2019</v>
       </c>
-      <c r="D44" t="s">
-        <v>94</v>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Lėvuo</t>
+        </is>
       </c>
       <c r="E44">
         <v>5</v>
       </c>
       <c r="F44">
-        <v>0.56999999999999995</v>
-      </c>
-      <c r="G44" t="s">
-        <v>24</v>
+        <v>0.57</v>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
       </c>
       <c r="H44">
-        <v>0.56000000000000005</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="I44">
-        <v>0.55817901234567902</v>
-      </c>
-      <c r="J44" t="s">
-        <v>24</v>
+        <v>0.558179012345679</v>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
       </c>
       <c r="K44">
-        <v>0.66666666666666663</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="L44">
-        <v>0.66666666666666663</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="M44">
-        <v>0.26666666666666672</v>
+        <v>0.2666666666666667</v>
       </c>
       <c r="N44">
-        <v>0.63271604938271608</v>
+        <v>0.6327160493827161</v>
       </c>
       <c r="O44">
-        <v>60.215053763440856</v>
+        <v>60.21505376344086</v>
       </c>
       <c r="P44">
         <v>31.12903225806452</v>
@@ -3582,30 +3758,38 @@
         <v>29.35483870967742</v>
       </c>
       <c r="R44">
-        <v>34.301075268817208</v>
-      </c>
-      <c r="S44" t="s">
-        <v>57</v>
+        <v>34.30107526881721</v>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>DEP</t>
+        </is>
       </c>
       <c r="T44">
         <v>29.35483870967742</v>
       </c>
       <c r="U44">
-        <v>9.9999999999998979E-3</v>
-      </c>
-    </row>
-    <row r="45" spans="1:21">
-      <c r="A45" t="s">
-        <v>109</v>
-      </c>
-      <c r="B45" t="s">
-        <v>110</v>
+        <v>0.009999999999999898</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>LTR351_2019</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>LTR351</t>
+        </is>
       </c>
       <c r="C45">
         <v>2019</v>
       </c>
-      <c r="D45" t="s">
-        <v>111</v>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Šventoji</t>
+        </is>
       </c>
       <c r="E45">
         <v>5</v>
@@ -3613,17 +3797,21 @@
       <c r="F45">
         <v>0.54</v>
       </c>
-      <c r="G45" t="s">
-        <v>24</v>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
       </c>
       <c r="H45">
         <v>0.53</v>
       </c>
       <c r="I45">
-        <v>0.53454743328810495</v>
-      </c>
-      <c r="J45" t="s">
-        <v>24</v>
+        <v>0.5345474332881049</v>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
       </c>
       <c r="K45">
         <v>0.5</v>
@@ -3632,45 +3820,53 @@
         <v>0.7045454545454547</v>
       </c>
       <c r="M45">
-        <v>0.26666666666666672</v>
+        <v>0.2666666666666667</v>
       </c>
       <c r="N45">
-        <v>0.66697761194029848</v>
+        <v>0.6669776119402985</v>
       </c>
       <c r="O45">
-        <v>30.161290322580641</v>
+        <v>30.16129032258064</v>
       </c>
       <c r="P45">
-        <v>39.892473118279568</v>
+        <v>39.89247311827957</v>
       </c>
       <c r="Q45">
         <v>29.35483870967742</v>
       </c>
       <c r="R45">
-        <v>47.311827956989248</v>
-      </c>
-      <c r="S45" t="s">
-        <v>57</v>
+        <v>47.31182795698925</v>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>DEP</t>
+        </is>
       </c>
       <c r="T45">
         <v>29.35483870967742</v>
       </c>
       <c r="U45">
-        <v>1.0000000000000011E-2</v>
-      </c>
-    </row>
-    <row r="46" spans="1:21">
-      <c r="A46" t="s">
-        <v>112</v>
-      </c>
-      <c r="B46" t="s">
-        <v>113</v>
+        <v>0.01000000000000001</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>LTR411_2022</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>LTR411</t>
+        </is>
       </c>
       <c r="C46">
         <v>2022</v>
       </c>
-      <c r="D46" t="s">
-        <v>114</v>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Šešupė</t>
+        </is>
       </c>
       <c r="E46">
         <v>5</v>
@@ -3678,64 +3874,76 @@
       <c r="F46">
         <v>0.75</v>
       </c>
-      <c r="G46" t="s">
-        <v>30</v>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
       </c>
       <c r="H46">
         <v>0.74</v>
       </c>
       <c r="I46">
-        <v>0.74191126855600542</v>
-      </c>
-      <c r="J46" t="s">
-        <v>30</v>
+        <v>0.7419112685560054</v>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
       </c>
       <c r="K46">
-        <v>0.66666666666666663</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="L46">
-        <v>0.84615384615384615</v>
+        <v>0.8461538461538461</v>
       </c>
       <c r="M46">
-        <v>0.73333333333333328</v>
+        <v>0.7333333333333333</v>
       </c>
       <c r="N46">
-        <v>0.72149122807017541</v>
+        <v>0.7214912280701754</v>
       </c>
       <c r="O46">
-        <v>60.215053763440856</v>
+        <v>60.21505376344086</v>
       </c>
       <c r="P46">
-        <v>82.473118279569889</v>
+        <v>82.47311827956989</v>
       </c>
       <c r="Q46">
-        <v>87.849462365591393</v>
+        <v>87.84946236559139</v>
       </c>
       <c r="R46">
-        <v>66.236559139784944</v>
-      </c>
-      <c r="S46" t="s">
-        <v>35</v>
+        <v>66.23655913978494</v>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>DSFI</t>
+        </is>
       </c>
       <c r="T46">
-        <v>60.215053763440856</v>
+        <v>60.21505376344086</v>
       </c>
       <c r="U46">
-        <v>1.0000000000000011E-2</v>
-      </c>
-    </row>
-    <row r="47" spans="1:21">
-      <c r="A47" t="s">
-        <v>115</v>
-      </c>
-      <c r="B47" t="s">
-        <v>65</v>
+        <v>0.01000000000000001</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>LTR86_2016</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>LTR86</t>
+        </is>
       </c>
       <c r="C47">
         <v>2016</v>
       </c>
-      <c r="D47" t="s">
-        <v>23</v>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Mūša</t>
+        </is>
       </c>
       <c r="E47">
         <v>5</v>
@@ -3743,50 +3951,56 @@
       <c r="F47">
         <v>0.48</v>
       </c>
-      <c r="G47" t="s">
-        <v>24</v>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
       </c>
       <c r="H47">
         <v>0.5</v>
       </c>
       <c r="I47">
-        <v>0.49949463225216989</v>
-      </c>
-      <c r="J47" t="s">
-        <v>24</v>
+        <v>0.4994946322521699</v>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
       </c>
       <c r="K47">
         <v>0.5</v>
       </c>
       <c r="L47">
-        <v>0.68939393939393945</v>
+        <v>0.6893939393939394</v>
       </c>
       <c r="M47">
         <v>0.1333333333333333</v>
       </c>
       <c r="N47">
-        <v>0.67525125628140692</v>
+        <v>0.6752512562814069</v>
       </c>
       <c r="O47">
-        <v>30.161290322580641</v>
+        <v>30.16129032258064</v>
       </c>
       <c r="P47">
-        <v>35.645161290322577</v>
+        <v>35.64516129032258</v>
       </c>
       <c r="Q47">
-        <v>9.1397849462365599</v>
+        <v>9.13978494623656</v>
       </c>
       <c r="R47">
-        <v>50.215053763440856</v>
-      </c>
-      <c r="S47" t="s">
-        <v>57</v>
+        <v>50.21505376344086</v>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>DEP</t>
+        </is>
       </c>
       <c r="T47">
-        <v>9.1397849462365599</v>
+        <v>9.13978494623656</v>
       </c>
       <c r="U47">
-        <v>-2.0000000000000021E-2</v>
+        <v>-0.02000000000000002</v>
       </c>
     </row>
   </sheetData>
